--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -967,18 +967,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The CRUD finding on the send itself is not the issue — setSaveAsActivity(false) is set and no record is written — but tracing it exposed a missing record-access check: the staff 'send portal link' and 'show portal code' actions accept a Contact Id and resolve its email in system mode inside a without-sharing service, without first confirming the running user can see that Contact. The remediation, to land before submission, is a user-mode visibility check on the donor record in both actions before any code is minted or any address is returned, so a user who cannot see the donor receives 'not found'. The Person Account path already read in user mode and is unchanged.</t>
+          <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. Tracing it at scan time exposed that the staff 'send portal link' and 'show portal code' actions accepted a Contact Id and resolved its email in system mode without confirming the running user could see that Contact. That was fixed before submission: both staff twins now re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>DonorPortalAdminController.cls:27 sendPortalLink, :32 createPortalLink — doValidate only requireNotNull(recordId); doExecute passes recordId straight to the service
-DonorPortalService.cls: `public without sharing class`; issueAccessCodeForDonor :462-479, createAccessCodeForDonor :486-494, buildDonorAccessCode :509-534 (code.email returned; code.code returned when forEmail=false)
-DonorPortalService.cls:538-543 resolveDonorEmail -&gt; ContactsSelector.selectEmailsByIdSystem (SYSTEM_MODE) for the Contact arm; :549 AccountsSelector.selectPersonDonorById (USER_MODE) for the PA arm
-ContactsSelector.selectEmailsByIdSystem (~:202) comment claims ReceiptController-only use
-Permission sets: DonorPortalAdminController classAccess in Fundraising_User and Fundraising_Admin
-issueCodeRow supersedes the donor's outstanding Issued codes — a staff user can also repeatedly invalidate an unseen donor's valid code (minor availability impact)
-TESTONLY note: fflib_IDGenerator source is test-only; the two DonorPortalAdminController sources are real.</t>
+          <t>HEAD DonorPortalService.cls:30-47 - class header: the staff twins re-read the donor in the STAFF user's mode (resolveStaffDonorEmail) and refuse a donor that user cannot see
+HEAD DonorPortalAdminController.cls:57 SendPortalLinkAction, :78 CreatePortalLinkAction, :141 ContactsSelector.selectById (USER_MODE), :160 AccountsSelector.selectPersonDonorById (USER_MODE)
+DonorPortalService_Test / DonorPortalAdminController_Test: a Fundraising_User who cannot see the Contact gets 'not found' and no Portal_Access_Token__c row is created
+docs/security/appexchange-security-review-readiness.md F-10 (donor-portal IDOR closed 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -990,7 +987,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1015,16 +1012,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>This is a read-only count of the site guest user's permission-set assignments, run from an administrator-only setup console to report whether the payment credential is granted to that guest user; it returns a yes/no verdict and no record data. It runs in system mode because PermissionSetAssignment is setup data that the running administrator can read only with 'View Setup and Configuration', which the package's admin permission set does not grant, and without it the console would falsely report the grant as missing. Only users holding the administrator permission set can reach it.</t>
+          <t>This is a read-only count of the site guest user's permission-set assignments, run from the administrator-only setup console to report whether the payment credential is granted to that guest user; it returns a yes/no verdict and no record data. It runs in system mode because PermissionSetAssignment is setup data that the running administrator can read only with 'View Setup and Configuration', which the package's admin permission set does not grant, and without it the console would falsely report the grant as missing. Only users holding the administrator permission set can reach it. Since the scan the site carries its own SYSTEM_MODE comment saying so, as does every other setup-object read in the class.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CommunityService.cls:458-462 WITH SYSTEM_MODE, no adjacent reason
-CommunityService.cls:6-8 header: without-sharing rationale only
-python3 scripts/lint/system-mode-inventory.py --verbose -&gt; 'header-only setup/service/CommunityService.cls:461' (0 unjustified overall)
-SetupController.cls:325 checkGuestPermissionSet; SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no userPermissions (no ViewSetup)
-Same file queryGuestCampaignRead / queryGuestUserExternalCredentialAccess run the same PSA read WITH SYSTEM_MODE under a doc comment that explains the two-channel lookup but not the mode</t>
+          <t>HEAD CommunityService.cls:489-494 - `// SYSTEM_MODE: the guest user's assignments ... a count only, for the Fundraising_Admin-only Settings console.` above the query
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites (header-only count now excludes this file's reads)
+SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no ViewSetup userPermission</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1077,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1107,21 +1102,15 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>This call creates the public download link for the single file attached to a campaign 'Document' post, which is rendered on the public campaign page; it runs only in internal-user triggers (post save, or file upload onto a post) and never from a guest context. ContentDistribution is a standard object a second-generation package permission set cannot grant, so the insert runs in system mode and is scoped to the ContentVersion Ids resolved from the post's own ContentDocumentLinks. We are tightening the gate so a link is minted only for a Document-type post the running user can edit (UserRecordAccess.HasEditAccess) and whose parent Campaign the user can see, and only when the user holds the org's public-link permission; otherwise the post saves without a URL and the reason is logged.</t>
+          <t>At scan time this call created the public download link for a campaign 'Document' post's file with `insert as system`, justified by ContentDistribution being a standard object a 2GP permission set cannot grant. Since the scan the public link is the one write in this class that is NOT system mode: ContentDistribution is inserted with Database.insert(..., AccessLevel.USER_MODE), so the platform's own 'Create Public Links' permission and object CRUD decide whether the running user may publish a file; a failed row simply gets no URL and the reason is logged. A link is minted only for a Document-type post the running user can edit (RecordAccess.editableIds) whose parent Campaign the user can see (CampaignsSelector.selectIdsVisibleToUser), and never from a guest context. The flagged `as system` statement no longer exists at this site.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/campaign/service/CampaignPostService.cls:23 - class is `with sharing`, but the insert is `as system`
-base/main/default/classes/campaign/service/CampaignPostService.cls:14-21 - header justifies SYSTEM_MODE as 'standard object, package cannot grant'; true for the grant, but it does not address the 'Create Public Links' user permission that governs who may publish a file
-base/main/default/classes/campaign/service/CampaignPostService.cls:188-205 - applyFileDetails filters to DOCUMENT_TYPE posts
-base/main/default/classes/campaign/service/CampaignPostService.cls:212-264 - stampFromVersions does NOT filter on Type__c or Is_Published__c: any file uploaded onto any post (Update-type, or an unpublished draft) gets a live public ContentDistribution
-base/main/default/classes/campaign/service/CampaignPostService.cls:358-400 - publicUrls: no check of Campaign visibility, file ownership, record edit access, or the PermissionsCreatePublicLinks user permission before insert
-base/main/default/classes/campaign/service/CampaignPostService.cls:153 - the render path (not the mint path) is what checks Is_Published__c + DOCUMENT_TYPE; the URL exists regardless
-base/main/default/classes/campaign/service/CampaignPostService.cls:309 and :135 - related: `delete as system` on every other ContentDocument linked to the post (replace/delete), including files owned by other users that are merely linked to it - a delete-other-users'-file path worth gating on ContentDocument.OwnerId or UserRecordAccess in the same change
-base/main/default/classes/setup/service/SettingsService.cls (createLogoDistribution) - the admin logo upload creates ContentVersion + ContentDistribution in USER_MODE, showing USER_MODE is viable for a staff file flow
-base/main/default/objects/Campaign_Post__c - Lookup (not master-detail) to Campaign, OWD ReadWrite: a user who cannot see the Campaign can still edit the post
-Scope limit: the file must already be linked to a post, which requires the user to have access to the file; exposure is 'staff with post Edit can publish a file they can see', not a guest IDOR - hence fixable, not real_issue</t>
+          <t>HEAD CampaignPostService.cls:23-25 - header: the public link is inserted in USER_MODE so 'Create Public Links' decides
+HEAD CampaignPostService.cls:624-625 - `// USER_MODE: minting a public link is the uploader's act` then Database.insert(toCreate, false, AccessLevel.USER_MODE)
+HEAD CampaignPostService.cls:328 RecordAccess.editableIds(postIds); :344 CampaignsSelector.selectIdsVisibleToUser(campaignIds); :347 Document-type filter
+docs-site/docs/guides/campaign-posts.md 'Who can publish a file'; docs/security/appexchange-security-review-readiness.md F-10</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1208,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1244,19 +1233,18 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>This upsert is shared by the package install handler, which runs as the package's system user with no permission set, and by the settings console controller, which is granted only in the Fundraising_Admin permission set; that set grants edit on all 106 Settings__c fields, and no guest or non-admin permission set can reach the controller. System mode is kept because the install path has no FLS to enforce and because DML on a custom setting in user mode appears to require Customize Application, which a fundraising administrator need not hold. After the proposed change, the console path also checks an explicit package permission before any save, rather than relying only on Apex class access, which a subscriber can grant to other users.</t>
+          <t>This upsert is shared by the package install handler, which runs as the package's system user with no permission set, and by the settings console controller, which is granted only in the Fundraising_Admin permission set. System mode is kept because the install path has no FLS to enforce and because DML on a Hierarchy Custom Setting in user mode requires Customize Application, a system permission no packaged permission set can carry. Since the scan, the console path no longer relies on Apex class access alone: every controller action that reaches this write (SaveGeneralSettings, DetectOrgFeatures, ResetToDefaults, SaveExperienceSite) first checks the packaged custom permission Manage_Fundraising_Settings, granted only in Fundraising_Admin, and refuses the save with a generic error when the running user does not hold it. The site now carries a SYSTEM_MODE comment naming that gate.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/SettingsService.cls:56-74 saveSettings normalises two URL fields then `upsert as system settings`
-base/main/default/permissionsets/Fundraising_Admin.permissionset-meta.xml:553 is the only &lt;classAccesses&gt; for SetupController; Fundraising_User.permissionset-meta.xml:509 and Fundraising_ReadOnly:503 carry doc comments that it must stay absent; Fundraising_GuestDonor has no Settings__c grant at all
-Settings__c fieldPermissions: Admin 106/106 editable, User 0/106 editable, ReadOnly 0/106 editable; no permission set declares customSettingAccesses or userPermissions
-base/main/default/classes/shared/ControllerAction.cls: run() = doValidate -&gt; doExecute with envelope + AppLogger; NO permission check. None of the SetupController inner actions (SaveGeneralSettings:1274, UploadOrgLogo:1532, RemoveOrgLogo:1556, DetectOrgFeatures:2109, ResetToDefaults:2145, SaveExperienceSite:2205, SaveRecordTypeMapping:1155, FixHealthCheckItem:492) performs an explicit permission/FLS check - the only gate is Apex class access
-Apex class access on a managed class is subscriber-configurable (a subscriber admin can add SetupController to any profile/permission set), so 'only Fundraising_Admin has it' is a shipped default, not an enforced invariant
-Settings__c: customSettingsType Hierarchy, visibility Public, 106 fields; SaveGeneralSettings writes ~95 of them from an LWC-supplied Map (hex colours validated by normalizeHex, campaign-type picklist and task-owner user validated in doValidate)
-Install-context caller cannot use USER_MODE: the per-package system user holds no permission set (see PostInstallHandler.cls:66-70)
-Community source (github patronmanager/apex-dml-manager#2): custom settings are editable only by users with Customize Application -&gt; switching the console path to USER_MODE would probably break saves for Fundraising_Admin users who are not full admins. Whether USER_MODE DML on a custom setting honours permission-set FLS alone or also requires Customize Application is UNVERIFIED against official docs (developer.salesforce.com atlas pages returned 403 / cookie wall)</t>
+          <t>HEAD SettingsService.cls:74-81 - `// SYSTEM_MODE:` reason naming the Manage_Fundraising_Settings gate, then `upsert as system settings`
+HEAD SetupController.cls:1401-1406 - SettingsWriteAction.requireSettingsPermission(): FeatureManagement.checkPermission('Manage_Fundraising_Settings') else addError(SETTINGS_NOT_AUTHORIZED)
+HEAD SetupController.cls:1409/1418 SaveGeneralSettings, :2270-2271 DetectOrgFeatures, :2306-2307 ResetToDefaults, :2366/2375 SaveExperienceSite - each doValidate() starts with requireSettingsPermission()
+base/main/default/customPermissions/Manage_Fundraising_Settings.customPermission-meta.xml; Fundraising_Admin.permissionset-meta.xml grants it; Fundraising_User / Fundraising_ReadOnly / Fundraising_GuestDonor do not
+SetupController_Test: five deny tests (bare Standard User), one deny test (Fundraising_User), one allow test (Fundraising_Admin); 312 tests pass, SetupController 96%, SettingsService 98%
+PostInstallHandler.onInstall -&gt; seedRecordTypeMappings / ensureDefaultLogoSeeded still reach this write with no permission check: install context, no running user to check
+docs/security/appexchange-security-review-readiness.md F-13</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1743,16 +1731,16 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>This writes one of two scheduling-interval fields on the org-default Settings__c row; the family is checked against two fixed names and the interval against a fixed allow-list before the write. It is reached only from the settings console controller, which is granted only in the Fundraising_Admin permission set, and that set holds edit access on both fields. System mode is retained because DML on a custom setting in user mode appears to require Customize Application; after the proposed change the console action also checks an explicit package permission before writing.</t>
+          <t>This writes one of two scheduling-interval fields on the org-default Settings__c row; the family is checked against two fixed names and the interval against a fixed allow-list before the write. It is reached only from the settings console controller's ScheduleJobFamily action, which is granted only in the Fundraising_Admin permission set. System mode is retained because DML on a Hierarchy Custom Setting in user mode requires Customize Application, which a packaged permission set cannot grant. Since the scan, ScheduleJobFamily.doValidate() first checks the packaged custom permission Manage_Fundraising_Settings (granted only in Fundraising_Admin) and refuses the save when the running user does not hold it; the site carries a SYSTEM_MODE comment naming that gate.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/SettingsService.cls:656-677 validates ALLOWED_JOB_INTERVAL_MINUTES, reads getOrgDefaults(), sets Finalizer_Interval_Minutes__c or Heartbeat_Interval_Minutes__c, else throws 'Unknown job family'
-SetupController.ScheduleJobFamily (:1676) validates family in {Finalizer, ReconciliationHeartbeat}, aborts via CronTrigger query WITH USER_MODE, then System.schedule
-Fundraising_Admin is the only permission set with SetupController classAccess and holds editable FLS on both interval fields
-No explicit permission check in ControllerAction or the action; gate is class access only (subscriber-configurable)
-USER_MODE DML on a custom setting: community source says Customize Application is required; UNVERIFIED against official docs</t>
+          <t>HEAD SettingsService.cls:684-688 - `// SYSTEM_MODE:` reason naming the ScheduleJobFamily gate, then `upsert as system s`
+HEAD SetupController.cls:1812-1821 - ScheduleJobFamily extends SettingsWriteAction; doValidate() calls requireSettingsPermission() before the family / interval checks
+SetupController_Test.test_scheduleJobFamily_userWithoutSettingsPermission_isRefused
+Fundraising_Admin is the only permission set with SetupController classAccess and the only one carrying Manage_Fundraising_Settings
+docs/security/appexchange-security-review-readiness.md F-13</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3229,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3266,17 +3254,15 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>This is a read-only diagnostic in the admin setup console. It checks whether the site's guest user has been assigned the package's guest permission set and returns only a boolean and a remediation message. The guest user Id is resolved on the server from the selected site, not taken from the client. No record data is returned, and the read is wrapped in a try/catch that degrades to "could not verify". PermissionSetAssignment is a setup object whose visibility is governed by View Setup and Configuration, Assign Permission Sets or Manage User Fields rather than record sharing.</t>
+          <t>This is a read-only diagnostic in the admin setup console. It checks whether the site's guest user has been assigned the package's guest permission set and returns only a boolean and a remediation message. The guest user Id is resolved on the server from the selected site, not taken from the client. No record data is returned, and the read is wrapped in a try/catch that degrades to 'could not verify'. PermissionSetAssignment is a setup object whose visibility is governed by View Setup and Configuration rather than record sharing, which the package's admin permission set does not grant; the read stays in system mode so an administrator without it gets a true answer. Since the scan the site carries its own SYSTEM_MODE comment stating this.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/CommunityService.cls:262-288 - checkGuestPermissionSet: try/catch, result map of booleans/messages only
-base/main/default/classes/setup/service/CommunityService.cls:275-280 - WITH SYSTEM_MODE, no per-site comment
-base/main/default/classes/setup/controller/SetupController.cls:320,325 - saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller
-base/main/default/permissionsets - only Fundraising_Admin grants classAccess to SetupController; Fundraising_User/ReadOnly deliberately omit it
-base/main/default/classes/setup/service/CommunityService.cls:6-8 - public virtual without sharing; header rationale covers Network/User/PSA/BackgroundOperation only
-https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm - special access rules: requires View Setup and Configuration, Assign Permission Sets, or Manage User Fields</t>
+          <t>HEAD CommunityService.cls:307-313 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
+docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3274,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3313,16 +3299,15 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>This read-only check verifies that the site guest user has read/create on User External Credential. That is a standard-object grant the admin must add by hand, because a 2GP permission set cannot carry it. The method returns only a boolean for the setup console checklist. The guest user Id is derived on the server, the read never runs as or for a guest request, and failures degrade to a "check manually" message.</t>
+          <t>This read-only check verifies that the site guest user has read/create on User External Credential, a standard-object grant the admin must add by hand because a 2GP permission set cannot carry it. The method returns only a boolean for the setup console checklist. The guest user Id is derived on the server, the read never runs as or for a guest request, and failures degrade to a 'check manually' message. The reads are setup data governed by View Setup and Configuration, so they stay in system mode; since the scan each carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/CommunityService.cls:514-533 - PSA then ObjectPermissions COUNT, WITH SYSTEM_MODE; returns Boolean
-base/main/default/classes/setup/controller/SetupController.cls:320,325 - saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller
-base/main/default/permissionsets - only Fundraising_Admin grants classAccess to SetupController; Fundraising_User/ReadOnly deliberately omit it
-base/main/default/classes/setup/service/CommunityService.cls:6-8 - public virtual without sharing; header rationale covers Network/User/PSA/BackgroundOperation only
-https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm - special access rules for PermissionSetAssignment</t>
+          <t>HEAD CommunityService.cls:551-568 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
+docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3319,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3359,17 +3344,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>This read-only check finds which permission sets grant access to the Stripe external credential's principal. The setup console can then tell the admin whether the guest user can make the payment callout. It returns only permission-set Ids used for an in-memory set intersection, never record data. SetupEntityAccess is a setup object whose visibility is governed by View Setup and Configuration. The inputs are resolved on the server, and the call is reachable only from the admin-only setup controller.</t>
+          <t>This read-only check finds which permission sets grant access to the Stripe external credential's principal, so the setup console can tell the admin whether the guest user can make the payment callout. It returns only permission-set Ids used for an in-memory set intersection, never record data. SetupEntityAccess is a setup object whose visibility is governed by View Setup and Configuration, which the admin permission set does not grant, so the read stays in system mode. The inputs are resolved on the server, the call is reachable only from the admin-only setup controller, and since the scan the site carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/CommunityService.cls:549-557 - SetupEntityAccess WITH SYSTEM_MODE; returns Set&lt;Id&gt;
-base/main/default/classes/setup/service/CommunityService.cls:567-569 - sibling doc cites queryGrantingPermSetIds for a SYSTEM_MODE reason that is not stated there
-base/main/default/classes/setup/controller/SetupController.cls:320,325 - saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller
-base/main/default/permissionsets - only Fundraising_Admin grants classAccess to SetupController; Fundraising_User/ReadOnly deliberately omit it
-base/main/default/classes/setup/service/CommunityService.cls:6-8 - public virtual without sharing; header rationale covers Network/User/PSA/BackgroundOperation only
-https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_setupentityaccess.htm - special access rules: requires View Setup and Configuration</t>
+          <t>HEAD CommunityService.cls:590-596 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
+docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3364,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3406,16 +3389,15 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>This read-only check powers the setup console's "guest user can read Campaign" step. It reads the guest user's permission-set assignments and counts ObjectPermissions rows granting Campaign read. It returns only a boolean, so the admin knows whether the documented manual grant is done. A managed package cannot ship that grant on a standard object. No record data leaves the method, and the user Id is derived on the server.</t>
+          <t>This read-only check powers the setup console's 'guest user can read Campaign' step. It reads the guest user's permission-set assignments and counts ObjectPermissions rows granting Campaign read, returning only a boolean so the admin knows whether the documented manual grant is done (a managed package cannot ship that grant on a standard object). No record data leaves the method and the user Id is derived on the server. Both reads are setup data governed by View Setup and Configuration, which the admin permission set does not grant, so they stay in system mode; since the scan each carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/service/CommunityService.cls:355-369 - PSA then ObjectPermissions COUNT, both WITH SYSTEM_MODE; returns Boolean
-base/main/default/classes/setup/controller/SetupController.cls:320,325 - saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller
-base/main/default/permissionsets - only Fundraising_Admin grants classAccess to SetupController; Fundraising_User/ReadOnly deliberately omit it
-base/main/default/classes/setup/service/CommunityService.cls:6-8 - public virtual without sharing; header rationale covers Network/User/PSA/BackgroundOperation only
-https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm - PSA requires View Setup and Configuration (or Assign Permission Sets / Manage User Fields)</t>
+          <t>HEAD CommunityService.cls:384-398 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
+docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4070,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4113,14 +4095,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>UserModeDML has no keyword and extends SimpleDML, which is `without sharing`. Per the Apex Developer Guide it therefore adopts `without sharing`. Its DML defaults to AccessLevel.USER_MODE, which re-applies the running user's record sharing and CRUD/FLS whatever the class's own mode. So its default behavior enforces sharing. The constructor also accepts SYSTEM_MODE, in which case the inherited `without sharing` would apply. We will declare the keyword explicitly so the resulting mode is visible at the declaration.</t>
+          <t>At scan time UserModeDML had no keyword and extended SimpleDML, which is `without sharing`, so it adopted `without sharing`. Its DML defaults to AccessLevel.USER_MODE, which re-applies the running user's record sharing and CRUD/FLS whatever the class's own mode, so its default behavior already enforced sharing; only an instance built with an explicit SYSTEM_MODE would have inherited the parent's mode. Since the scan the class declares `inherited sharing`, so such an instance follows its caller's sharing. No production code constructs UserModeDML; the local change is recorded in the fflib fork log in DEPENDENCIES.md.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:191-210 - declaration, default USER_MODE, AccessLevel constructor
-Apex Dev Guide: 'If an Apex class without an explicit sharing declaration extends from a parent class, then it adopts the same sharing mode as the parent class.'
-Apex Dev Guide: 'User mode reapplies the record sharing rules of the current user'
+          <t>HEAD fflib_SObjectUnitOfWork.cls:195-199 - `// doc:` rationale and `public virtual inherited sharing class UserModeDML extends SimpleDML`
+DEPENDENCIES.md fork log row for fflib_SObjectUnitOfWork.cls UserModeDML
 grep: no non-test reference to UserModeDML</t>
         </is>
       </c>
@@ -4177,7 +4158,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4202,15 +4183,14 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>CreateTicketIntent has no keyword and extends GuestAction, which is `inherited sharing`, so it adopts inherited sharing. It is invoked from the `without sharing` guest controller, so it runs `without sharing`. That is required for a guest to create a ticket order against a Campaign it cannot see under sharing. Record visibility is decided by explicit predicates: the campaign must be active, published and open for sales. We will add the keyword explicitly so the mode is readable at the declaration.</t>
+          <t>At scan time the inner class had no sharing keyword. It extends GuestAction, which is `inherited sharing`, so it adopted inherited sharing and, invoked from the `without sharing` guest controller, ran without sharing. That is required for a guest to create a ticket order against a Campaign it cannot see under sharing; record visibility is decided by explicit predicates (the campaign must be active, published and open for sales). Since the scan the class declares `inherited sharing` explicitly, so the effective mode is readable at the declaration and unchanged.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fundraising/controller/EventRegistrationController.cls:4 - outer `without sharing`
-base/main/default/classes/shared/GuestAction.cls:29-30 - `public abstract inherited sharing class GuestAction extends ControllerAction`
-base/main/default/classes/fundraising/controller/EventRegistrationController.cls:193,583-590 - requireOpenCampaign gate
-Apex Dev Guide: inner classes do not adopt the container's mode; a keyword-less subclass adopts the parent's mode; inherited sharing 'runs as without sharing only when explicitly called from an already established without sharing context'</t>
+          <t>HEAD EventRegistrationController.cls:164 - `private inherited sharing class CreateTicketIntent extends GuestAction`
+EventRegistrationController.cls requireOpenCampaign gate (active, published, open for sales)
+docs/security/appexchange-security-review-readiness.md F-3</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4333,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4378,17 +4358,14 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>The inner class has no keyword, but it extends ControllerAction, which is `inherited sharing`. Per the Apex Developer Guide, a class with no declaration that extends a parent 'adopts the same sharing mode as the parent class', and inherited sharing runs `with sharing` unless called from an established `without sharing` context. Here the caller is the `with sharing` outer controller, so the action runs with sharing. We will declare `inherited sharing` on the inner class explicitly. This changes no behavior and removes the ambiguity.</t>
+          <t>At scan time the inner class had no sharing keyword. It extends ControllerAction, which is `inherited sharing`, and per the Apex Developer Guide a class with no declaration that extends a parent adopts the parent's sharing mode; the caller is the `with sharing` outer controller, so the action already ran with sharing. Since the scan the class declares `inherited sharing` explicitly, which changes no behavior and removes the ambiguity the rule flags.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donation/controller/DonationMonitorController.cls:7 - outer class `public with sharing`
-base/main/default/classes/shared/ControllerAction.cls:31-32 - `public abstract inherited sharing class ControllerAction`
-base/main/default/classes/donation/controller/DonationMonitorController.cls:72-75 - selectNonTerminalForAdmin (SYSTEM_MODE, commented at DonationStagingSelector.cls:245-249)
-base/main/default/classes/donation/controller/DonationMonitorController.cls:127-134 - inline CronTrigger COUNT() WITH USER_MODE inside the inner class
-Apex Dev Guide (sharing keywords): 'Inner classes don't adopt the sharing mode of the container class.' / 'If an Apex class without an explicit sharing declaration extends from a parent class, then it adopts the same sharing mode as the parent class.'
-Class apiVersion 67.0 (DonationMonitorController.cls-meta.xml)</t>
+          <t>HEAD DonationMonitorController.cls:65 - `private inherited sharing class GetStuckDonations extends ControllerAction`
+base/main/default/classes/shared/ControllerAction.cls - `public abstract inherited sharing class ControllerAction`
+docs/security/appexchange-security-review-readiness.md F-3 sharing census (re-counted 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4725,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4773,15 +4750,15 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The scheduler's only work is to start DonorSummaryRollupBatch, the head of the renewal chain. Its only query is a CronTrigger lookup by job name. The batches that read and charge recurring donations declare their own sharing (DonorSummaryRollupBatch is `without sharing` with its own rationale). Per the guide, a method's sharing mode is set where it is defined, so this class's keyword does not reach them. We will change it to `with sharing` and correct the comment, because it performs no record access that sharing would govern.</t>
+          <t>The scheduler's only work is to start DonorSummaryRollupBatch, the head of the renewal chain, and its only query is a CronTrigger lookup by job name. The batches that read and charge recurring donations declare their own sharing (DonorSummaryRollupBatch is `without sharing` with its own rationale), and per the Apex Developer Guide a method's sharing mode is set where it is defined, so this class's keyword never reached them. At scan time the class was `without sharing` with a stale comment; since the scan it is `with sharing`, with a comment stating that it touches no shared records and that scheduled Apex runs as the user who scheduled it.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/recurring/async/RecurringDonationScheduler.cls:22-30 - execute() only calls Database.executeBatch(new DonorSummaryRollupBatch(CONTACT, true))
-base/main/default/classes/recurring/async/RecurringDonationScheduler.cls:45-50 - CronTrigger SOQL WITH SYSTEM_MODE (setup object)
-base/main/default/classes/donation/async/DonorSummaryRollupBatch.cls:13 - `public without sharing class DonorSummaryRollupBatch`
-Apex Dev Guide: 'the sharing mode of a method is determined by where the method is defined, not where it's called from'</t>
+          <t>HEAD RecurringDonationScheduler.cls:15-19 - `// with sharing:` rationale and `public with sharing class RecurringDonationScheduler implements Schedulable`
+HEAD RecurringDonationScheduler.cls execute() only calls Database.executeBatch(new DonorSummaryRollupBatch(...))
+base/main/default/classes/donation/async/DonorSummaryRollupBatch.cls - `public without sharing class` with its own rationale
+docs/security/appexchange-security-review-readiness.md F-3</t>
         </is>
       </c>
     </row>
@@ -5017,7 +4994,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5042,16 +5019,18 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>SimpleDML is the Unit of Work's DML strategy. The keyword is needed for guest and background writes that carry lookups to records the guest licence cannot see, such as a Private campaign. Under SYSTEM_MODE, record sharing follows the class's own declaration. For internal staff, record-level authorization is done in the controller and service layer before the write, by a user-mode read of the target record. We acknowledge that a read gate proves read access, not edit access. We will give staff write paths a sharing-enforcing DML strategy so edit rights are enforced by the platform, not only by the read gate.</t>
+          <t>At scan time SimpleDML, the Unit of Work's default DML strategy, was declared `without sharing`, so every commit in the package bypassed record-level sharing. Since the scan, fflib_SObjectUnitOfWork and SimpleDML are declared `inherited sharing` (the declaration upstream fflib accepted in issue #530): a Unit of Work committed from a `with sharing` controller or service now runs with sharing, and the platform enforces the running user's record access on the write. The guest, batch, platform-event-subscriber and trigger-rollup writes that must bypass sharing opt in explicitly by constructing their Unit of Work with SystemDML, a package-authored `without sharing` subclass whose four DML statements pin AccessLevel.SYSTEM_MODE and carry the reason; each of the 24 construction sites states which family it belongs to. Object and field permissions are enforced one layer up, in the FFLib Selectors and by Security.stripInaccessible, and staff update/delete paths additionally filter through RecordAccess before registering the write. SystemDML_Test proves, with a Minimum Access user, that the default commit on an unshared row is refused and the SystemDML commit succeeds.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:123-139 - rationale + declaration; DML pinned to AccessLevel.SYSTEM_MODE (:147-166)
-grep: `new fflib_SObjectUnitOfWork.UserModeDML` / UserModeDML appears only in *_Test classes
-base/main/default/classes/event/controller/EventCheckInController.cls:105 - example staff write: read-gated via selector, then registerDirty(new Event_Attendee__c(Id=...)) committed through SimpleDML
-Apex Dev Guide trigger example: WITH SYSTEM_MODE leaves 'Record sharing ... governed by the ... own without sharing context'; user mode 'reapplies the record sharing rules of the current user'
-unverified: that a `with sharing` class blocks DML update on a record the user can read but not edit (INSUFFICIENT_ACCESS) was not re-confirmed on developer.salesforce.com in this pass</t>
+          <t>HEAD fflib_SObjectUnitOfWork.cls:64 - `public virtual inherited sharing class fflib_SObjectUnitOfWork`
+HEAD fflib_SObjectUnitOfWork.cls:154 - `public inherited sharing virtual class SimpleDML implements IDML, IDMLUpsertable`, with the `// doc:` rationale above it
+HEAD base/main/default/classes/shared/SystemDML.cls - `public without sharing class SystemDML extends fflib_SObjectUnitOfWork.SimpleDML`, rationale and family list at the declaration
+grep: `new SystemDML()` at 24 production sites, each preceded by a `// SystemDML: guest|job|rollup` comment; none in a staff controller
+base/main/default/classes/shared/SystemDML_Test.cls - Minimum Access user: SimpleDML commit on an unshared Log__c throws, SystemDML commit lands
+DEPENDENCIES.md fork log row for fflib_SObjectUnitOfWork.cls :64/:154; docs/security/appexchange-security-review-readiness.md F-10 item 13 and FP-3 family 4
+https://github.com/apex-enterprise-patterns/fflib-apex-common/issues/530 - upstream proposal for the same `inherited sharing` declarations</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5087,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5133,20 +5112,14 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>The guest-facing methods are correctly authorized by possession of an access code or portal session, which is why the class is `without sharing`. However, the class also contains two staff methods, issueAccessCodeForDonor and createAccessCodeForDonor, which take a Contact Id from a Lightning component. For a Contact, the donor's email is read in SYSTEM_MODE and the access-code row is inserted in SYSTEM_MODE, and nothing checks that the staff user can see that Contact. A Fundraising_User can therefore mint a donor-portal code for a Contact outside their sharing. The 'create' variant shows that code and the donor's email on screen. We will add a user-mode visibility check on the Contact/Account before either staff method runs, and move the staff methods out of the `without sharing` class.</t>
+          <t>The class is `without sharing` so the Experience Cloud guest user, which has no sharing on Contact, Account or Portal_Access_Token__c, can resolve a donor from an access code and mint a portal session; every guest method is authorized by possession of the code or session it produces and trusts no client-supplied record Id. The class also holds two staff methods, issueAccessCodeForDonor and createAccessCodeForDonor, which take a record Id from a Lightning component. At scan time nothing checked that the staff user could see that record. Since the scan, both staff methods re-read the donor in the staff user's mode (USER_MODE selectors, resolveStaffDonorEmail) and refuse a donor the user cannot see before anything is minted or returned, and the class header states that its `without sharing` must not become a way to reach records outside the caller's access.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donor/controller/DonorPortalAdminController.cls:12-13 - doc claims `with sharing` means 'a staff member can only issue a code for a donor they can already see'
-base/main/default/classes/donor/controller/DonorPortalAdminController.cls:54-68,75-89 - Send/Create actions: only requireNotNull, then call the service with the raw recordId
-base/main/default/classes/donor/controller/DonorPortalAdminController.cls:138 - only the read-only PortalLinkContextAction does a USER_MODE ContactsSelector.selectById
-base/main/default/classes/donor/service/DonorPortalService.cls:538-541 - resolveDonorEmail Contact arm uses ContactsSelector.selectEmailsByIdSystem (SYSTEM_MODE) inside a without-sharing class
-base/main/default/classes/donor/service/DonorPortalService.cls:345 - issueCodeRow inserts Portal_Access_Token__c in SYSTEM_MODE
-base/main/default/classes/donor/selector/ContactsSelector.cls:199-202 - comment says selectEmailsByIdSystem is 'used ONLY by the token-authorized public receipt (ReceiptController)': false
-base/main/default/permissionsets/Fundraising_User.permissionset-meta.xml:561 - DonorPortalAdminController granted to Fundraising_User
-Person Account arm (AccountsSelector.selectPersonDonorById) is USER_MODE, so it is gated. Only the Contact arm is exposed.
-Apex Dev Guide: 'the sharing mode of a method is determined by where the method is defined, not where it's called from', so the with-sharing controller does not make the service's reads sharing-aware</t>
+          <t>HEAD DonorPortalService.cls:38-47 - header rationale for `without sharing` and the staff-twin exception; :48 declaration
+HEAD DonorPortalAdminController.cls:141 / :160 - USER_MODE reads of the Contact / Person Account before the service is called
+docs/security/appexchange-security-review-readiness.md F-10; FP-3 sharing census</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5868,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6000,7 +5973,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6218,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6288,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6638,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6743,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6778,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6813,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7408,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8388,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8423,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8563,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9228,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9403,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9438,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9473,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9508,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9543,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9648,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9683,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9718,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9753,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9788,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9823,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9858,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9893,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9928,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9963,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10025,7 +9998,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10033,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10068,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10103,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10138,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10173,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10208,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10243,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10278,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10313,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10348,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10383,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10418,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10453,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10488,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10523,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10558,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10593,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10628,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10663,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10698,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10733,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10768,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10803,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10838,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10873,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10908,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10943,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11005,7 +10978,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11013,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11048,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11083,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11145,7 +11118,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11153,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11215,7 +11188,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11223,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11258,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11293,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11328,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11363,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11398,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11433,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11468,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11503,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11538,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11573,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11608,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11643,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11678,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11713,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11748,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11783,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11818,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11853,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11915,7 +11888,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11923,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -11985,7 +11958,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12020,7 +11993,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12028,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12063,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12098,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12133,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12168,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12203,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12265,7 +12238,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12273,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12335,7 +12308,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12343,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12378,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12413,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12448,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12483,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12518,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12588,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12623,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12658,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12693,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12728,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12798,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12833,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12903,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13113,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13183,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14023,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15003,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15038,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15213,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15248,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15283,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15318,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15353,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15388,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15450,7 +15423,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15458,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15520,7 +15493,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15528,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15563,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15598,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15633,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15668,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15703,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15738,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15773,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15835,7 +15808,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15843,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15878,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15913,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -15975,7 +15948,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16010,7 +15983,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16045,7 +16018,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16053,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16088,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16123,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16158,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16193,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16255,7 +16228,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16263,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16298,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16333,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16395,7 +16368,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16403,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16438,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16473,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16508,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16543,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16578,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16613,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16675,7 +16648,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16683,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16718,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16753,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16788,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16823,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16858,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16893,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16928,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -16990,7 +16963,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17025,7 +16998,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17033,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17095,7 +17068,7 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17103,7 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17138,7 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17200,7 +17173,7 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17235,7 +17208,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17270,7 +17243,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17305,7 +17278,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17313,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17348,7 @@
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17383,7 @@
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17445,7 +17418,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17453,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17515,7 +17488,7 @@
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17550,7 +17523,7 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17558,7 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17620,7 +17593,7 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17628,7 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17663,7 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17725,7 +17698,7 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17733,7 @@
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17768,7 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17803,7 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17838,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17873,7 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17908,7 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -17970,7 +17943,7 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18005,7 +17978,7 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18040,7 +18013,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18048,7 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18083,7 @@
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18118,7 @@
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18180,7 +18153,7 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18188,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18223,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18285,7 +18258,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18425,7 +18398,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18460,7 +18433,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18573,7 @@
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18705,7 +18678,7 @@
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18783,7 @@
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18888,7 @@
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20000,7 +19973,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20078,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20113,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20175,7 +20148,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20210,7 +20183,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20218,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20253,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20288,7 @@
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20350,7 +20323,7 @@
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -20770,7 +20743,7 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21050,7 +21023,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21093,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21260,7 +21233,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21575,7 +21548,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21785,7 +21758,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>False positive — hardening before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21828,7 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>Confirmed — fix before submission</t>
+          <t>False positive</t>
         </is>
       </c>
     </row>
@@ -22141,7 +22114,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>f37ab088</t>
+          <t>ffaf4703</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -5287,17 +5287,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL; no merge field, parameter or stored value contributes to the src, so it is not a dynamically constructed resource. Stripe's documentation requires Stripe.js to be loaded directly from https://js.stripe.com and not bundled or self-hosted, so it cannot be moved into a static resource; js.stripe.com is shipped as a packaged CSP Trusted Site. The page exists precisely to keep Stripe.js out of the LWC runtime: the LWC frames this Visualforce page and talks to it by origin-checked postMessage, Stripe Elements tokenizes card data in Stripe's own nested iframe, and only a payment-method id is returned to Apex. The only server value rendered into the page's script is `{!allowedOrigin}`, the org's own domain from System.URL.getOrgDomainUrl().</t>
+          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL; no merge field, parameter or stored value contributes to the src, so it is not a dynamically constructed resource. Stripe's documentation requires Stripe.js to be loaded directly from https://js.stripe.com and not bundled or self-hosted, so it cannot be moved into a static resource; js.stripe.com is shipped as a packaged CSP Trusted Site. The page exists precisely to keep Stripe.js out of the LWC runtime: the LWC frames this Visualforce page by relative URL and talks to it by postMessage, Stripe Elements tokenizes card data in Stripe's own nested iframe, and only a payment-method id is returned to Apex. The page has no Apex controller and renders no server value into its script: the postMessage peer is the page's own origin (window.location.origin), and inbound messages are accepted only from that origin and from window.parent.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/pages/stripePayment.page:39-40 - justification comment + static script tag
-base/main/default/pages/stripePayment.page:81 - the only merge field in the page: var fallback = '{!allowedOrigin}';
-base/main/default/classes/payment/stripe/StripePaymentPageController.cls - getAllowedOrigin() returns System.URL.getOrgDomainUrl().toExternalForm(); no user input
-base/main/default/pages/stripePayment.page:126-131 - message listener drops any event whose origin !== PARENT_ORIGIN
-base/main/default/pages/stripePayment.page:159-165 - returnUrl built with encodeURIComponent on publishableKey and stagingId
-base/main/default/lwc/dfForm/dfForm.js:411 - parent side checks event.origin === ALLOWED_ORIGIN (window.location.origin)
+          <t>base/main/default/pages/stripePayment.page:48-53 - justification comment + static script tag (line 40 in the 2026-09-16 scan)
+base/main/default/pages/stripePayment.page:1-7 - &lt;apex:page&gt; declares no controller; the page contains no {!...} merge field
+base/main/default/pages/stripePayment.page:89 - var PARENT_ORIGIN = window.location.origin; (the page is always framed same-origin)
+base/main/default/pages/stripePayment.page:139 - message listener drops any event whose origin !== PARENT_ORIGIN or whose source !== window.parent
+base/main/default/pages/stripePayment.page:169-174 - returnUrl built with encodeURIComponent on publishableKey and stagingId
+base/main/default/lwc/dfForm/dfForm.js:441 - parent side checks event.origin === ALLOWED_ORIGIN (window.location.origin)
 https://docs.stripe.com/js/including - 'it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself'
 https://docs.stripe.com/security/guide - Stripe.js CSP directives: script-src https://*.js.stripe.com, https://js.stripe.com; frame-src https://*.js.stripe.com, https://js.stripe.com, https://hooks.stripe.com; connect-src https://api.stripe.com
 base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml - endpointUrl https://js.stripe.com, isActive true, connect-src + frame-src, context All (CspTrustedSite metadata has no script-src flag)
@@ -5338,17 +5338,17 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL, the second of the two Stripe.js loads in the package; nothing dynamic contributes to the src. Stripe redirects the donor here after an off-site authentication step (3D Secure, bank redirect), and the page needs Stripe.js to call retrievePaymentIntent/retrieveSetupIntent; Stripe's documentation requires Stripe.js to be loaded from js.stripe.com rather than self-hosted, which is why it is not a static resource. URL parameters read by the page (pk, the Stripe intent client secret, opp) are passed only to Stripe.js calls or written with textContent; the receipt link is built as '/receipt?id=' + value, so it cannot become a script URL. The only server merge field is `{!allowedOrigin}`, the org's own domain.</t>
+          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL, the second of the two Stripe.js loads in the package; nothing dynamic contributes to the src. Stripe redirects the donor here after an off-site authentication step (3D Secure, bank redirect), and the page needs Stripe.js to call retrievePaymentIntent/retrieveSetupIntent; Stripe's documentation requires Stripe.js to be loaded from js.stripe.com rather than self-hosted, which is why it is not a static resource. URL parameters read by the page (pk and the Stripe intent client secret) are passed only to Stripe.js calls, and status text is written with textContent. The page has no Apex controller. Its only server-rendered value is the 'Return to the site' link, whose href is the org's saved Experience site URL read through a $Setup merge field, rendered only when it begins with https://, and never taken from the query string.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/pages/stripePaymentReturn.page:27-28 - justification comment + static script tag
-base/main/default/pages/stripePaymentReturn.page:100 - only merge field: return '{!allowedOrigin}';
-base/main/default/classes/payment/stripe/StripePaymentReturnController.cls - getAllowedOrigin() = System.URL.getOrgDomainUrl().toExternalForm()
-base/main/default/pages/stripePaymentReturn.page:83-89 - pk/opp/client secrets read from URLSearchParams; pk only passed to Stripe(pk)
-base/main/default/pages/stripePaymentReturn.page:109-125 - showStatus writes title/message/icon via textContent; receipt anchor href = '/receipt?id=' + oppId (fixed same-origin path prefix)
-base/main/default/pages/stripePayment.page:159-165 - buildReturnUrl never sets an 'opp' parameter, so the View Receipt link is unreachable in the normal flow (dead code, harmless)
+          <t>base/main/default/pages/stripePaymentReturn.page:35-40 - justification comment + static script tag (line 28 in the 2026-09-16 scan)
+base/main/default/pages/stripePaymentReturn.page:1-7 - &lt;apex:page&gt; declares no controller
+base/main/default/pages/stripePaymentReturn.page:82-87 - only merge fields: the return link, rendered only when $Setup.Settings__c.Experience_Site_URL__c BEGINS 'https://', value from the same setting (never from a URL parameter)
+base/main/default/pages/stripePaymentReturn.page:91-96 - pk and intent client secrets read from URLSearchParams; pk only passed to Stripe(pk); the opp parameter is never read
+base/main/default/pages/stripePaymentReturn.page:109-113 - PARENT_ORIGIN = window.location.origin; postMessage targets only that origin
+base/main/default/pages/stripePaymentReturn.page:119-123 - showStatus writes title/message/icon via textContent
 https://docs.stripe.com/js/including - 'it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself'
 https://docs.stripe.com/security/guide - Stripe.js CSP directives: script-src https://*.js.stripe.com, https://js.stripe.com; frame-src https://*.js.stripe.com, https://js.stripe.com, https://hooks.stripe.com; connect-src https://api.stripe.com
 base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml - endpointUrl https://js.stripe.com, isActive true, connect-src + frame-src, context All (CspTrustedSite metadata has no script-src flag)
@@ -22114,7 +22114,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ffaf4703</t>
+          <t>75a4dabe</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>The event-ticket receipt is sent to the purchaser's own Contact after the purchase is finalized; setSaveAsActivity(false) means the send creates no activity record, so there is no create/read/update/delete for a CRUD check to guard. The recipient Id comes from the purchase record, not from any request parameter. The only reported source is the SOQL builder class, which is a helper rather than an entry point.</t>
+          <t>The event-ticket receipt is sent to the purchaser's own Contact after the purchase is finalized; setSaveAsActivity(false) means the send creates no activity record, so there is no create/read/update/delete for a CRUD check to guard. The recipient Id comes from the purchase record, not from any request parameter. The only reported source is the SOQL builder class, which is a helper rather than an entry point. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>This is an internal alert sent by a scheduled reconciliation job to the owner of a disputed gift and the configured reply-to address; it uses explicit addresses, no target record, and setSaveAsActivity(false), so it performs no DML. No user- or guest-reachable code path reaches it; the reported sources are a test-only fake-Id generator and the SOQL builder's parameter methods.</t>
+          <t>This is an internal alert sent by a scheduled reconciliation job to the owner of a disputed gift and the configured reply-to address; it uses explicit addresses, no target record, and setSaveAsActivity(false), so it performs no DML. No user- or guest-reachable code path reaches it; the reported sources are a test-only fake-Id generator and the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Every source reported for this sink is test-support framework code (the mocking library's mock/verify methods and its fake-Id generator), which is only called from test classes. In production the method runs from a platform-event subscriber after a gift is finalized and emails matching-gift instructions to that gift's own donor Contact. setSaveAsActivity(false) is set, so no activity record is written and there is no DML to check.</t>
+          <t>Every source reported for this sink is test-support framework code (the mocking library's mock/verify methods and its fake-Id generator), which is only called from test classes. In production the method runs from a platform-event subscriber after a gift is finalized and emails matching-gift instructions to that gift's own donor Contact. setSaveAsActivity(false) is set, so no activity record is written and there is no DML to check. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>This sink sends a template receipt to the donor Contact of the gift that was just finalized; setTargetObjectId and setWhatId select the recipient and the merge-field sources, and setSaveAsActivity(false) is set, so the send writes no Task/activity record and performs no DML the user could be denied. The recipient is derived from the Opportunity, never from caller input. The only interactive reach is a staff retry of a stuck donation (a permission-set-granted console action), which re-runs the same scheduled finalization and sends the receipt only on first creation of the gift. The QueryFactory 'source' is the SOQL builder, not an entry point.</t>
+          <t>This sink sends a template receipt to the donor Contact of the gift that was just finalized; setTargetObjectId and setWhatId select the recipient and the merge-field sources, and setSaveAsActivity(false) is set, so the send writes no Task/activity record and performs no DML the user could be denied. The recipient is derived from the Opportunity, never from caller input. The only interactive reach is a staff retry of a stuck donation (a permission-set-granted console action), which re-runs the same scheduled finalization and sends the receipt only on first creation of the gift. The QueryFactory 'source' is the SOQL builder, not an entry point. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>The tribute notice is a one-time email to the honoree address the donor entered with their gift, sent during server-side finalization on first creation and only when the donor opted in. It has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing. The reported sources are a test-only fake-Id generator and the SOQL builder.</t>
+          <t>The tribute notice is a one-time email to the honoree address the donor entered with their gift, sent during server-side finalization on first creation and only when the donor opted in. It has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing. The reported sources are a test-only fake-Id generator and the SOQL builder. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. The staff 'send portal link' and 'show portal code' actions accept a Contact Id, so both staff twins re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged.</t>
+          <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. The staff 'send portal link' and 'show portal code' actions accept a Contact Id, so both staff twins re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>This sends a one-time sign-in code to a donor's own address after a guest asks for it; the address must match an existing donor, the request is rate-limited, and the response is the same whether or not it matched. The message uses explicit addresses with no target record and setSaveAsActivity(false), so no record is created. The staff controller methods listed as sources reach a different send site (the staff twin) and share only the message-building helper; the fake-Id generator source is test-only.</t>
+          <t>This sends a one-time sign-in code to a donor's own address after a guest asks for it; the address must match an existing donor, the request is rate-limited, and the response is the same whether or not it matched. The message uses explicit addresses with no target record and setSaveAsActivity(false), so no record is created. The staff controller methods listed as sources reach a different send site (the staff twin) and share only the message-building helper; the fake-Id generator source is test-only. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Recurring-gift notices (confirmation, failed payment, dunning, re-authorization) are sent by the finalize path and a scheduled renewal job to the schedule's own donor Contact, with setSaveAsActivity(false), so the send writes no record. No user- or guest-callable entry point reaches this method. The reported sources are the SOQL builder's parameter methods.</t>
+          <t>Recurring-gift notices (confirmation, failed payment, dunning, re-authorization) are sent by the finalize path and a scheduled renewal job to the schedule's own donor Contact, with setSaveAsActivity(false), so the send writes no record. No user- or guest-callable entry point reaches this method. The reported sources are the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>This notifies staff that a donor asked for a refund through the donor portal; the gift Id was checked against the authenticated donor's own giving history when the request was recorded, and the message goes to that gift's owner and the configured reply-to address, never to a caller-supplied address. It is plain text with explicit addresses and setSaveAsActivity(false), so it writes no record. The reported sources are the SOQL builder's parameter methods, not entry points.</t>
+          <t>This notifies staff that a donor asked for a refund through the donor portal; the gift Id was checked against the authenticated donor's own giving history when the request was recorded, and the message goes to that gift's owner and the configured reply-to address, never to a caller-supplied address. It is plain text with explicit addresses and setSaveAsActivity(false), so it writes no record. The reported sources are the SOQL builder's parameter methods, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>The refund notice is sent only after a refund has been processed, to the refunded gift's own donor Contact, with setSaveAsActivity(false), so the send itself writes no record. The interactive path requires a dedicated custom permission checked in the controller before any work, and the controller declares with sharing, which the service inherits. Two of the reported sources are test-only mocking framework methods; the third is that permission-gated controller.</t>
+          <t>The refund notice is sent only after a refund has been processed, to the refunded gift's own donor Contact, with setSaveAsActivity(false), so the send itself writes no record. The interactive path requires a dedicated custom permission checked in the controller before any work, and the controller declares with sharing, which the service inherits. Two of the reported sources are test-only mocking framework methods; the third is that permission-gated controller. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Resending a receipt is a staff action whose record access is enforced before the message is built: the gift and the donor Contact are read in user mode (object, field and sharing checks of the running user), so a user who cannot see either gets nothing to send. The recipient is always the gift's own donor Contact, not a caller-supplied address, and setSaveAsActivity(false) means the send writes no record. The other two sources reported are the SOQL builder's parameters, not entry points.</t>
+          <t>Resending a receipt is a staff action whose record access is enforced before the message is built: the gift and the donor Contact are read in user mode (object, field and sharing checks of the running user), so a user who cannot see either gets nothing to send. The recipient is always the gift's own donor Contact, not a caller-supplied address, and setSaveAsActivity(false) means the send writes no record. The other two sources reported are the SOQL builder's parameters, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>This delete revokes the public ContentDistribution link a campaign post served, after staff have deleted the post or replaced its file. It runs only after an action the user was already authorised for: deleting a post first passes requireDeletable on Campaign_Post__c and commits the delete through a user-mode Unit of Work, so the platform refuses it without delete access; replacing a file first filters the posts through RecordAccess.editableIds. The revocation set is narrow: planRevocations keeps any link that another post still serves, so only the link the released post exposed is removed. ContentDistribution is a standard object a second-generation package permission set cannot grant, so a user-mode delete would depend on a manual admin step. The path is never reachable by a guest, and revoking a public link reduces exposure; it never widens it.</t>
+          <t>This delete revokes the public ContentDistribution link a campaign post served, after staff have deleted the post or replaced its file. It runs only after an action the user was already authorised for: deleting a post first passes requireDeletable on Campaign_Post__c and commits the delete through a user-mode Unit of Work, so the platform refuses it without delete access; replacing a file first filters the posts through RecordAccess.editableIds. The revocation set is narrow: planRevocations keeps any link that another post still serves, so only the link the released post exposed is removed. ContentDistribution is a standard object a second-generation package permission set cannot grant, so a user-mode delete would depend on a manual admin step. The path is never reachable by a guest, and revoking a public link reduces exposure; it never widens it. Converting this delete to user mode was tested and rejected because it breaks the feature for the users it is built for. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: deleting a ContentDistribution created by another staff member with `Database.delete(rows, AccessLevel.USER_MODE)` fails with `INSUFFICIENT_ACCESS_OR_READONLY`. In user mode the public link of a post one colleague published could not be revoked when another colleague deletes that post, and the file would stay publicly reachable. System mode is what guarantees the link is withdrawn.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test.</t>
+          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test.</t>
+          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>AppLogger persists diagnostic entries from catch blocks in every context, including guest controllers whose users cannot hold Create on any internal object; no permission set grants Create on Log__c by design, so logs are writable only through this class. Values are truncated to field length, Log__c is Private with read granted only to internal staff sets, and no client-callable method takes a log payload - the message text comes from server-side exceptions and developer-written strings. The class-level comment documents why it is `without sharing` and bypasses the Unit of Work.</t>
+          <t>AppLogger persists diagnostic entries from catch blocks in every context, including guest controllers whose users cannot hold Create on any internal object; no permission set grants Create on Log__c by design, so logs are writable only through this class. Values are truncated to field length, Log__c is Private with read granted only to internal staff sets, and no client-callable method takes a log payload - the message text comes from server-side exceptions and developer-written strings. The class-level comment documents why it is `without sharing` and bypasses the Unit of Work. Converting this insert to user mode was tested and rejected. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `insert as user new Log__c(...)` throws `System.TypeException: DML operation INSERT not allowed on Log__c`, because no permission set grants Create on the log object - by design, so that no user can author or forge diagnostic rows. A user-mode insert would therefore lose every log entry, including the ones that record security-relevant failures.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>This upsert is shared by the package install handler, which runs as the package's system user with no permission set, and by the settings console controller, which is granted only in the Fundraising_Admin permission set. System mode is kept because the install path has no FLS to enforce and because DML on a Hierarchy Custom Setting in user mode requires Customize Application, a system permission no packaged permission set can carry. The console path does not rely on Apex class access alone: every controller action that reaches this write (SaveGeneralSettings, DetectOrgFeatures, ResetToDefaults, SaveExperienceSite) first checks the packaged custom permission Manage_Fundraising_Settings, granted only in Fundraising_Admin, and refuses the save with a generic error when the running user does not hold it. The site carries a SYSTEM_MODE comment naming that gate.</t>
+          <t>This upsert is shared by the package install handler, which runs as the package's system user with no permission set, and by the settings console controller, which is granted only in the Fundraising_Admin permission set. System mode is kept because the install path has no FLS to enforce and because DML on a Hierarchy Custom Setting in user mode requires Customize Application, a system permission no packaged permission set can carry. The console path does not rely on Apex class access alone: every controller action that reaches this write (SaveGeneralSettings, DetectOrgFeatures, ResetToDefaults, SaveExperienceSite) first checks the packaged custom permission Manage_Fundraising_Settings, granted only in Fundraising_Admin, and refuses the save with a generic error when the running user does not hold it. The site carries a SYSTEM_MODE comment naming that gate. The user-mode alternative was tested and does not work for the people who use this screen. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Schema.sObjectType.Settings__c` reports isCreateable, isUpdateable and isAccessible all false, and `upsert as user` on the settings row throws `System.SecurityException: Access to entity 'Settings__c' denied`. The platform ties custom-setting DML to Customize Application, which is a system permission the fundraising administrator is not expected to hold, so a user-mode write would lock every non-system-administrator out of the settings console. The custom-permission check before the write is the access control; it is enforced in Apex on every action that reaches this line.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1328,12 +1328,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The flagged source is the donor's own portal session token read from sessionStorage; it is passed as an Apex parameter to DonorPortalController.getGivingStatement and is never written into the DOM. The value rendered at base/main/default/lwc/pfGivingStatement/pfGivingStatement.html:34 is either the `error` string of the controller's response envelope or a package-authored literal. The controller's action classes extend GuestAction, whose callerSafeMessage returns an AppException message (every one on this path is a constant: the invalid-session message, 'Choose a tax year.', 'That tax year is not available.', 'A donor is required to build a giving statement.') or one fixed generic sentence for any other exception - no record field, request parameter or token is echoed. Finally, the sink is an LWC `{expression}` text binding, which the framework renders as a text node, not HTML; neither pfGivingStatement nor publicDonorDashboard uses innerHTML, lwc:inner-html or lwc:dom="manual".</t>
+          <t>The flagged source is the donor's own portal session token read from sessionStorage; it is passed as an Apex parameter to DonorPortalController.getGivingStatement and is never written into the DOM. The value rendered at base/main/default/lwc/pfGivingStatement/pfGivingStatement.html:34 is either the `error` string of the controller's response envelope or a package-authored literal. The controller's action classes extend GuestAction, whose callerSafeMessage returns an AppException message (every one on this path is a constant: the invalid-session message, 'Choose a tax year.', 'That tax year is not available.', 'A donor is required to build a giving statement.') or one fixed generic sentence for any other exception - no record field, request parameter or token is echoed. Finally, the sink is an LWC `{expression}` text binding, which the framework renders as a text node, not HTML; neither pfGivingStatement nor publicDonorDashboard uses innerHTML, lwc:inner-html or lwc:dom="manual". Since the scan the flagged source has also been hardened: the value read from sessionStorage is accepted only when it matches the exact shape of a session token the server issues (64 lowercase hexadecimal characters); anything else is discarded and removed from storage before it reaches component state or an Apex call. The finding remains a false positive - the value was never rendered - but storage content that the component did not write can no longer enter it at all.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.js:310-318 - stored = window.sessionStorage.getItem(SESSION_KEY) (SESSION_KEY = 'pf-donor-portal-session', :41); assigned to this.token then loadDashboard(); not bound into markup
+          <t>base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.js:314-331 - stored = window.sessionStorage.getItem(SESSION_KEY) (SESSION_KEY = 'pf-donor-portal-session', :41); assigned to this.token then loadDashboard(); not bound into markup
+base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.js:45 and :320-330 - `SESSION_TOKEN_SHAPE = /^[0-9a-f]{64}$/`; a stored value that fails the test is removed and the sign-in form is shown
+base/main/default/classes/donor/service/DonorPortalService.cls:809-811 - generateToken() returns EncodingUtil.convertToHex(Crypto.generateAesKey(256)), i.e. 64 lowercase hex characters
 base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.html:389 - token={token} passed as a component property only; the only other {token} use is if:false={token} (line 47), a boolean
 base/main/default/lwc/pfGivingStatement/pfGivingStatement.js:96-104 and :115-121 - errorMessage = res?.error || literal, or the printStatement() return value
 base/main/default/lwc/uiStatementPrint/uiStatementPrint.js:249 - printStatement returns only the literal 'Pop-up blocked. Allow pop-ups ...' or null; the statement document itself is built with createElement/textContent (el() helper :31-35), never innerHTML
@@ -1354,7 +1356,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1369,7 +1371,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib/fflib_SObjectUnitOfWork.cls:313</t>
+          <t>classes/fflib/fflib_SObjectUnitOfWork.cls:294 (corrected since scan)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1379,14 +1381,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>This is the user-mode delete in the FFLib Unit of Work's UserModeDML strategy; the access level passed is AccessLevel.USER_MODE by default, so the platform itself enforces the running user's delete permission, sharing and FLS. The scanner cannot see an isDeletable() call because enforcement is done by the Database method's access-level argument. Every staff-only Unit of Work commit in the package is built with this strategy: 14 construction sites, each marked `// UserModeDML: staff`.</t>
+          <t>Fixed. The delete now reads `System.Database.delete(objList, AccessLevel.USER_MODE)`: the access level is a literal at the statement, no longer a field that a constructor could set to system mode. The platform enforces the running user's delete permission and record sharing on every row; a row the user may not delete fails the commit. The constructor that accepted another AccessLevel has been removed and the class is declared `with sharing`.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:272-282 - UserModeDML extends SimpleDML; m_accessLevel defaults to AccessLevel.USER_MODE
-base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:313 - `System.Database.delete(objList,m_accessLevel)`
-grep: `new fflib_SObjectUnitOfWork.UserModeDML()` at 14 production sites, each preceded by `// UserModeDML: staff`</t>
+          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:293-295 - `dmlDelete`: `System.Database.delete(objList, AccessLevel.USER_MODE);`
+base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:283 - `with sharing` declaration; no constructor takes an AccessLevel
+fflib_SObjectUnitOfWorkTest.userModeDML_When_InsertUpdateDelete_Expect_RowsWrittenInUserMode drives insert, update and delete through the class; test run 2026-10-01, 518 of 518 passing</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1694,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>This writes one of two scheduling-interval fields on the org-default Settings__c row; the family is checked against two fixed names and the interval against a fixed allow-list before the write. It is reached only from the settings console controller's ScheduleJobFamily action, which is granted only in the Fundraising_Admin permission set. System mode is retained because DML on a Hierarchy Custom Setting in user mode requires Customize Application, which a packaged permission set cannot grant. ScheduleJobFamily.doValidate() first checks the packaged custom permission Manage_Fundraising_Settings (granted only in Fundraising_Admin) and refuses the save when the running user does not hold it; the site carries a SYSTEM_MODE comment naming that gate.</t>
+          <t>This writes one of two scheduling-interval fields on the org-default Settings__c row; the family is checked against two fixed names and the interval against a fixed allow-list before the write. It is reached only from the settings console controller's ScheduleJobFamily action, which is granted only in the Fundraising_Admin permission set. System mode is retained because DML on a Hierarchy Custom Setting in user mode requires Customize Application, which a packaged permission set cannot grant. ScheduleJobFamily.doValidate() first checks the packaged custom permission Manage_Fundraising_Settings (granted only in Fundraising_Admin) and refuses the save when the running user does not hold it; the site carries a SYSTEM_MODE comment naming that gate. The user-mode alternative was tested and does not work for the people who use this screen. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Schema.sObjectType.Settings__c` reports isCreateable, isUpdateable and isAccessible all false, and `upsert as user` on the settings row throws `System.SecurityException: Access to entity 'Settings__c' denied`. The platform ties custom-setting DML to Customize Application, which is a system permission the fundraising administrator is not expected to hold, so a user-mode write would lock every non-system-administrator out of the settings console. The custom-permission check before the write is the access control; it is enforced in Apex on every action that reaches this line.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2687,7 +2689,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2702,7 +2704,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>classes/setup/controller/PostInstallHandler_Test.cls:1557</t>
+          <t>classes/setup/controller/PostInstallHandler_Test.cls:1557 (corrected since scan)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2712,14 +2714,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>This is an assertion inside an @IsTest class. It verifies that the post-install handler seeded the Custom_Question content templates. It runs only during Apex test execution with SeeAllData=false, so it can only count rows the test created. There is no runtime caller and no user-supplied input.</t>
+          <t>Fixed. The COUNT() assertion now carries `WITH USER_MODE`. It verifies that the post-install handler seeded the Custom_Question content templates and runs only during Apex test execution with SeeAllData=false.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
-base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1554 - the source is Content_Template__c.getRecordTypeInfosByDeveloperName().get('Custom_Question') describe
-base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1557 - an assertion that the post-install seed created Custom_Question templates; the COUNT() only reads rows the test itself caused to be inserted (SeeAllData=false)</t>
+          <t>base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1557 - `[SELECT COUNT() FROM Content_Template__c WHERE RecordTypeId = :... WITH USER_MODE]`
+Test run 2026-10-01: PostInstallHandler_Test passing</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2732,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2746,7 +2747,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>classes/setup/controller/PostInstallHandler_Test.cls:1559</t>
+          <t>classes/setup/controller/PostInstallHandler_Test.cls:1559 (corrected since scan)</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2756,14 +2757,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>This is an assertion inside an @IsTest class. It verifies that the post-install handler seeded the FAQ content templates. It runs only during Apex test execution with SeeAllData=false, so it can only count rows the test created. There is no runtime caller and no user-supplied input.</t>
+          <t>Fixed. The COUNT() assertion now carries `WITH USER_MODE`. It verifies that the post-install handler seeded the FAQ content templates and runs only during Apex test execution with SeeAllData=false.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
-base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1556 - the source is Content_Template__c.getRecordTypeInfosByDeveloperName().get('FAQ') describe
-base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1559 - an assertion that the post-install seed created FAQ templates; the COUNT() only reads rows the test itself caused to be inserted (SeeAllData=false)</t>
+          <t>base/main/default/classes/setup/controller/PostInstallHandler_Test.cls:1559 - `[SELECT COUNT() FROM Content_Template__c WHERE RecordTypeId = :... WITH USER_MODE]`
+Test run 2026-10-01: PostInstallHandler_Test passing</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>classes/campaign/service/CampaignService_Test.cls:222</t>
+          <t>classes/campaign/service/CampaignService_Test.cls:181 (corrected since scan)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2844,14 +2844,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>This is a test helper in an @IsTest class. It builds a minimum-access user so the test can assert, under System.runAs, that the code under test refuses a caller without the needed permissions. The Profile lookup is fixture setup and is never executed at runtime; since the scan it carries `WITH USER_MODE`. The helper exists to test the access controls, not to bypass them.</t>
+          <t>Fixed. The `Profile` lookup in this test helper now carries `WITH USER_MODE`. The helper builds a minimum-access user so the test can assert, under System.runAs, that the code under test refuses a caller without the needed permissions; it runs only in Apex test execution.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/campaign/service/CampaignService_Test.cls:1 - class annotated @IsTest
-base/main/default/classes/campaign/service/CampaignService_Test.cls:181 - fundraiserWithoutContactEdit() queries the 'Minimum Access - Salesforce' Profile Id `WITH USER_MODE` to build a low-privilege test user
-base/main/default/classes/campaign/service/CampaignService_Test.cls:222 - returns the inserted test user; used with System.runAs to prove a user without grants is refused</t>
+          <t>base/main/default/classes/campaign/service/CampaignService_Test.cls:181 - `[SELECT Id FROM Profile WHERE Name = 'Minimum Access - Salesforce' WITH USER_MODE LIMIT 1]`</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2861,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2878,7 +2876,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>classes/campaign/controller/CampaignPostController_Test.cls:454</t>
+          <t>classes/campaign/controller/CampaignPostController_Test.cls:426 (corrected since scan)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2888,14 +2886,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>This is a test helper in an @IsTest class. It builds a minimum-access user so the test can assert, under System.runAs, that the code under test refuses a caller without the needed permissions. The Profile lookup is fixture setup and is never executed at runtime; since the scan it carries `WITH USER_MODE`. The helper exists to test the access controls, not to bypass them.</t>
+          <t>Fixed. The `Profile` lookup in this test helper now carries `WITH USER_MODE`. The helper builds a minimum-access user so the test can assert, under System.runAs, that the code under test refuses a caller without the needed permissions; it runs only in Apex test execution.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/campaign/controller/CampaignPostController_Test.cls:1 - class annotated @IsTest
-base/main/default/classes/campaign/controller/CampaignPostController_Test.cls:426 - staffUser() queries the 'Minimum Access - Salesforce' Profile Id `WITH USER_MODE` to build a low-privilege test user
-base/main/default/classes/campaign/controller/CampaignPostController_Test.cls:454 - returns the inserted test user; used with System.runAs to prove a user without grants is refused</t>
+          <t>base/main/default/classes/campaign/controller/CampaignPostController_Test.cls:426 - `[SELECT Id FROM Profile WHERE Name = 'Minimum Access - Salesforce' WITH USER_MODE LIMIT 1]`</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2928,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>This query already runs in user mode: it is executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), which enforces object permissions, field-level security and sharing for the running user. The scanner only recognises the literal WITH USER_MODE clause and does not read the AccessLevel argument. The caller, DonorDetailController.requireDonor, uses this user-mode, sharing-enforced read as its IDOR gate: if the record Id supplied by the component is not visible to the user, zero rows come back and the controller throws "Donor not found" before any related data is read.</t>
+          <t>This query already runs in user mode: it is executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), which enforces object permissions, field-level security and sharing for the running user. The scanner only recognises the literal WITH USER_MODE clause and does not read the AccessLevel argument. The caller, DonorDetailController.requireDonor, uses this user-mode, sharing-enforced read as its IDOR gate: if the record Id supplied by the component is not visible to the user, zero rows come back and the controller throws "Donor not found" before any related data is read. A literal `WITH USER_MODE` clause cannot be added to satisfy the pattern: the query is built by the FFLib query factory as a dynamic string, and the platform rejects a dynamic query that carries both the clause and an AccessLevel argument. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Database.queryWithBinds('SELECT Id FROM Account WITH USER_MODE', binds, AccessLevel.USER_MODE)` throws `System.SecurityException: Cannot use the WITH AccessLevel clause in dynamic queries that also specify an access level.` The AccessLevel argument is the documented way to run a dynamic query in user mode.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2978,7 +2974,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>The SOQL string is built by the query factory and executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), so object permissions, FLS and sharing are enforced for the running user. The factory is also constructed with CRUD enforcement on. The scanner does not recognise the AccessLevel argument. The only caller that passes a client-supplied Id is DonorDetailController.requireDonor, which throws "Donor not found" when this user-mode read returns nothing, so a user cannot reach another donor's gifts, recurring plans or requests by guessing an Id.</t>
+          <t>The SOQL string is built by the query factory and executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), so object permissions, FLS and sharing are enforced for the running user. The factory is also constructed with CRUD enforcement on. The scanner does not recognise the AccessLevel argument. The only caller that passes a client-supplied Id is DonorDetailController.requireDonor, which throws "Donor not found" when this user-mode read returns nothing, so a user cannot reach another donor's gifts, recurring plans or requests by guessing an Id. A literal `WITH USER_MODE` clause cannot be added to satisfy the pattern: the query is built by the FFLib query factory as a dynamic string, and the platform rejects a dynamic query that carries both the clause and an AccessLevel argument. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Database.queryWithBinds('SELECT Id FROM Account WITH USER_MODE', binds, AccessLevel.USER_MODE)` throws `System.SecurityException: Cannot use the WITH AccessLevel clause in dynamic queries that also specify an access level.` The AccessLevel argument is the documented way to run a dynamic query in user mode.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3045,7 +3041,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3060,7 +3056,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>classes/guestrequest/controller/GuestRequestController_Test.cls:76</t>
+          <t>classes/guestrequest/controller/GuestRequestController_Test.cls:32 (corrected since scan)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3070,15 +3066,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>This is a test helper in an @IsTest class. It builds a minimum-access user so the test can assert, under System.runAs, that the controller refuses a caller without the needed permissions. The Profile lookup is fixture setup and is never executed at runtime. The helper exists to test the access controls, not to bypass them. The Profile query itself carries `WITH USER_MODE`.</t>
+          <t>Fixed. The `Profile` lookup in this test helper now carries `WITH USER_MODE`. The helper builds a minimum-access user so the test can assert, under System.runAs, that the code under test refuses a caller without the needed permissions; it runs only in Apex test execution.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/guestrequest/controller/GuestRequestController_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
-base/main/default/classes/guestrequest/controller/GuestRequestController_Test.cls:32 - outsider() fixture queries the 'Minimum Access - Salesforce' Profile Id to build a low-privilege test user
-base/main/default/classes/guestrequest/controller/GuestRequestController_Test.cls:76 - returns the inserted test user; used with System.runAs to prove a user without grants is refused
-base/main/default/classes/guestrequest/controller/GuestRequestController_Test.cls:32 - the Profile query carries `WITH USER_MODE`</t>
+          <t>base/main/default/classes/guestrequest/controller/GuestRequestController_Test.cls:32 - `[SELECT Id FROM Profile WHERE Name = 'Minimum Access - Salesforce' WITH USER_MODE LIMIT 1]`</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3288,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>This line is in an @IsTest class (FundraiserAdminController_Test). It seeds the hierarchy custom setting org defaults as test setup before the code under test runs. Test classes cannot be invoked by users at runtime. The flagged statement is a DML fixture write, not a query, and the dataflow source is a picklist describe, not user input.</t>
+          <t>This line is in an @IsTest class (FundraiserAdminController_Test). It seeds the hierarchy custom setting org defaults as test setup before the code under test runs. Test classes cannot be invoked by users at runtime. The flagged statement is a DML fixture write, not a query, and the dataflow source is a picklist describe, not user input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (Customize Application, which user-mode DML on a custom setting requires). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3339,7 +3332,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3383,7 +3376,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3427,7 +3420,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3471,7 +3464,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3515,7 +3508,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3559,7 +3552,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input.</t>
+          <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3603,7 +3596,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>This line is a test-fixture update inside an @IsTest class. It prepares a ticket product so the controller method under test sees a particular state. It cannot run outside Apex test execution. The dataflow source is a schema describe.</t>
+          <t>This line is a test-fixture update inside an @IsTest class. It prepares a ticket product so the controller method under test sees a particular state. It cannot run outside Apex test execution. The dataflow source is a schema describe. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3931,7 +3924,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3946,7 +3939,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib/fflib_SObjectUnitOfWork.cls:282</t>
+          <t>classes/fflib/fflib_SObjectUnitOfWork.cls:283 (corrected since scan)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3956,15 +3949,16 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>UserModeDML runs every insert, update and delete with AccessLevel.USER_MODE by default, which applies the running user's record sharing, object permissions and field-level security on the write whatever the class's own sharing keyword says. It declares `inherited sharing`, so an instance built with an explicit SYSTEM_MODE would still follow its caller's sharing rather than bypass it. Every staff-only Unit of Work commit in the package uses this strategy: 14 construction sites, each marked `// UserModeDML: staff` with its reason.</t>
+          <t>Fixed. UserModeDML now declares `with sharing`, and the constructor that accepted a caller-chosen AccessLevel has been removed: every statement in the class passes the literal `AccessLevel.USER_MODE`. The class can no longer be built in any mode other than user mode, so the platform applies the running user's record sharing, object permissions and field-level security on every insert, update, upsert and delete it performs. The 14 staff-only Unit of Work commits in the package use this strategy, each marked `// UserModeDML: staff` with its reason; their test classes pass unchanged.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:272-282 - rationale and `public virtual inherited sharing class UserModeDML extends SimpleDML`
-grep: `new fflib_SObjectUnitOfWork.UserModeDML()` at 14 production sites, each preceded by `// UserModeDML: staff`
-DEPENDENCIES.md fork log row for fflib_SObjectUnitOfWork.cls UserModeDML
-https://github.com/apex-enterprise-patterns/fflib-apex-common/issues/530 - upstream proposal for the same declaration</t>
+          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:283 - `public virtual with sharing class UserModeDML extends SimpleDML`
+base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:288 - the only constructor takes no argument
+base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:286-299 - `System.Database.insert/update/delete/upsert(..., AccessLevel.USER_MODE)`
+DEPENDENCIES.md fork log row for fflib_SObjectUnitOfWork.cls UserModeDML (2026-10-01)
+Test run 2026-10-01: fflib_SObjectUnitOfWorkTest and the staff-commit test classes (SetupController_Test, FundraiserAdminController_Test, CampaignPostService_Test, CampaignStoryController_Test, EventCheckInController_Test and others) - 518 of 518 passing</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4134,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>This is a stateless helper that stamps the org's configured sender identity onto outbound donor email. It is never a transaction entry point, and it takes the sharing mode of the service that builds the message. It reads only org email configuration.</t>
+          <t>This is a stateless helper that stamps the org's configured sender identity onto outbound donor email. It is never a transaction entry point, and it takes the sharing mode of the service that builds the message. It reads only org email configuration. The keyword was reviewed for a change to `with sharing` on 2026-10-01 and kept: the class is called from the guest donation path and from the platform-event subscriber as well as from staff actions, and `inherited sharing` is the declaration that lets each of those run in its caller's mode instead of forcing one mode on all of them.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4202,7 +4196,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4217,7 +4211,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>classes/donation/controller/DonationMonitorController.cls:81</t>
+          <t>classes/donation/controller/DonationMonitorController.cls:81 (corrected since scan)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4227,15 +4221,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>At scan time this inner class declared `inherited sharing`. It extends ControllerAction, which is also `inherited sharing`, and its only caller is the `with sharing` outer controller, so the action already ran with sharing. The scanner reads the keyword alone and cannot prove the caller, so since the scan the class declares `with sharing` outright. Behavior is unchanged. The action reads non-terminal donation staging rows through the FFLib selector and returns them to the staff monitor page; it writes nothing.</t>
+          <t>Fixed. At scan time this inner action declared `inherited sharing`; it now declares `with sharing`. Runtime behaviour is unchanged, because its only caller is the `with sharing` outer controller, but the declaration no longer depends on the caller. The action reads non-terminal donation staging rows through the FFLib selector for the staff monitor page and writes nothing.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donation/controller/DonationMonitorController.cls:77-81 - rationale and `private with sharing class GetStuckDonations extends ControllerAction`
-base/main/default/classes/donation/controller/DonationMonitorController.cls:7 - `public with sharing class DonationMonitorController`
-base/main/default/classes/donation/controller/DonationMonitorController.cls:47 - the only construction site, `new GetStuckDonations().run()`
-base/main/default/classes/shared/ControllerAction.cls:32 - `public abstract inherited sharing class ControllerAction`</t>
+          <t>base/main/default/classes/donation/controller/DonationMonitorController.cls:81 - `private with sharing class GetStuckDonations extends ControllerAction`
+DonationMonitorController_Test passes with the new keyword</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4701,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>PricebookService only creates and looks up the package's event price book and its PricebookEntry rows for ticket products. It runs during install, when an admin saves ticket tiers, and during a guest ticket purchase. None of those contexts can rely on the running user's price-book sharing. It handles no donor data, and it only receives Product2 Ids that its callers have read from records they already gated.</t>
+          <t>PricebookService only creates and looks up the package's event price book and its PricebookEntry rows for ticket products. It runs during install, when an admin saves ticket tiers, and during a guest ticket purchase. None of those contexts can rely on the running user's price-book sharing. It handles no donor data, and it only receives Product2 Ids that its callers have read from records they already gated. `with sharing` is not an option here: in the package install context a `with sharing` class cannot resolve the standard price book, which made the install-time seed fail when it was tried (2026-08-09).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5109,7 +5101,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL; no merge field, parameter or stored value contributes to the src, so it is not a dynamically constructed resource. Stripe's documentation requires Stripe.js to be loaded directly from https://js.stripe.com and not bundled or self-hosted, so it cannot be moved into a static resource; js.stripe.com is shipped as a packaged CSP Trusted Site. The page exists precisely to keep Stripe.js out of the LWC runtime: the LWC frames this Visualforce page by relative URL and talks to it by postMessage, Stripe Elements tokenizes card data in Stripe's own nested iframe, and only a payment-method id is returned to Apex. The page has no Apex controller and renders no server value into its script: the postMessage peer is the page's own origin (window.location.origin), and inbound messages are accepted only from that origin and from window.parent.</t>
+          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL; no merge field, parameter or stored value contributes to the src, so it is not a dynamically constructed resource. Stripe's documentation requires Stripe.js to be loaded directly from https://js.stripe.com and not bundled or self-hosted, so it cannot be moved into a static resource; js.stripe.com is shipped as a packaged CSP Trusted Site. The page exists precisely to keep Stripe.js out of the LWC runtime: the LWC frames this Visualforce page by relative URL and talks to it by postMessage, Stripe Elements tokenizes card data in Stripe's own nested iframe, and only a payment-method id is returned to Apex. The page has no Apex controller and renders no server value into its script: the postMessage peer is the page's own origin (window.location.origin), and inbound messages are accepted only from that origin and from window.parent. Moving the script into a static resource was reviewed again on 2026-10-01 and is not permitted: Stripe's integration guidance states that Stripe.js must always be loaded directly from js.stripe.com and must not be included in a bundle or self-hosted, as a condition of PCI compliance.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5160,7 +5152,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL, the second of the two Stripe.js loads in the package; nothing dynamic contributes to the src. Stripe redirects the donor here after an off-site authentication step (3D Secure, bank redirect), and the page needs Stripe.js to call retrievePaymentIntent/retrieveSetupIntent; Stripe's documentation requires Stripe.js to be loaded from js.stripe.com rather than self-hosted, which is why it is not a static resource. URL parameters read by the page (pk and the Stripe intent client secret) are passed only to Stripe.js calls, and status text is written with textContent. The page has no Apex controller. Its only server-rendered value is the 'Return to the site' link, whose href is the org's saved Experience site URL read through a $Setup merge field, rendered only when it begins with https://, and never taken from the query string.</t>
+          <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL, the second of the two Stripe.js loads in the package; nothing dynamic contributes to the src. Stripe redirects the donor here after an off-site authentication step (3D Secure, bank redirect), and the page needs Stripe.js to call retrievePaymentIntent/retrieveSetupIntent; Stripe's documentation requires Stripe.js to be loaded from js.stripe.com rather than self-hosted, which is why it is not a static resource. URL parameters read by the page (pk and the Stripe intent client secret) are passed only to Stripe.js calls, and status text is written with textContent. The page has no Apex controller. Its only server-rendered value is the 'Return to the site' link, whose href is the org's saved Experience site URL read through a $Setup merge field, rendered only when it begins with https://, and never taken from the query string. Moving the script into a static resource was reviewed again on 2026-10-01 and is not permitted: Stripe's integration guidance states that Stripe.js must always be loaded directly from js.stripe.com and must not be included in a bundle or self-hosted, as a condition of PCI compliance.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6600,7 +6592,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12962,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -13005,7 +12997,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13067,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13102,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13347,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14362,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14572,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15418,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>cefc11c2</t>
+          <t>f94a4fbb</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Scan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$H$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$K$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All paths'!$A$1:$G$280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -439,8 +439,11 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,12 +479,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Scanner's claim</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Why the claim is false</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting detail</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Evidence</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sources</t>
         </is>
       </c>
     </row>
@@ -518,10 +536,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the flagged line is a regular-expression match on a string already in memory, not a query or DML statement, so no CRUD operation exists to check; the string was read with WITH USER_MODE, so the running administrator's permissions were already enforced.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>The flagged line is a regular-expression match on a string already in memory; it is not a query or DML statement. The data it examines was read with WITH USER_MODE, so the running administrator's object and field permissions were already enforced, and only credential and parameter names are retained for a setup checklist. The path is reachable only by the administrator permission set; the fake-Id generator source is test-only and the other is the SOQL builder.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/payment/service/PaymentSetupGuideService.cls:1917 Matcher m = MERGE_FORMULA.matcher(...); if (m.find())
 queryNamedCredentials (:1583) and queryCustomHeaders (:1607) WITH USER_MODE
@@ -530,6 +558,11 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -564,10 +597,20 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The claim that a CRUD check is missing before a create/update/delete is false because Messaging.sendEmail is not a DML statement: with setSaveAsActivity(false) it writes no record at all, so there is nothing for isCreateable() to guard. The recipient and merge-field source are the just-finalized gift's own donor Contact, not a request parameter.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>This sink sends a template receipt to the donor Contact of the gift that was just finalized; setTargetObjectId and setWhatId select the recipient and the merge-field sources, and setSaveAsActivity(false) is set, so the send writes no Task/activity record and performs no DML the user could be denied. The recipient is derived from the Opportunity, never from caller input. The only interactive reach is a staff retry of a stuck donation (a permission-set-granted console action), which re-runs the same scheduled finalization and sends the receipt only on first creation of the gift. The QueryFactory 'source' is the SOQL builder, not an entry point. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:94-103 — setTemplateId, setTargetObjectId(targetContactId), setWhatId(opportunityId), setSaveAsActivity(false), applySender, sendEmail
 base/main/default/classes/donation/service/DonationService.cls:399 — sendDonationReceipt called on first creation only
@@ -576,6 +619,12 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -610,10 +659,20 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing; it fires once during server-side finalization, to the honoree address the donor supplied with their own gift, and only when the donor opted in.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>The tribute notice is a one-time email to the honoree address the donor entered with their gift, sent during server-side finalization on first creation and only when the donor opted in. It has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing. The reported sources are a test-only fake-Id generator and the SOQL builder. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:702-704 setTargetObjectId(null), setToAddresses(honoree), setSaveAsActivity(false)
 base/main/default/classes/donation/service/DonationService.cls:404 caller
@@ -621,6 +680,11 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -655,16 +719,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send writes no record (setSaveAsActivity(false)), is reached only from the finalize path and a scheduled renewal job, and addresses the recurring schedule's own donor Contact; no user- or guest-callable entry point selects the recipient.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>Recurring-gift notices (confirmation, failed payment, dunning, re-authorization) are sent by the finalize path and a scheduled renewal job to the schedule's own donor Contact, with setSaveAsActivity(false), so the send writes no record. No user- or guest-callable entry point reaches this method. The reported sources are the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:709-734
 base/main/default/classes/recurring/async/RecurringRenewalBatch.cls:197-202; base/main/default/classes/recurring/service/RecurringDonationService.cls:956
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -699,16 +778,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because Messaging.sendEmail with setSaveAsActivity(false) performs no create, read, update or delete on any sObject, so no CRUD check applies; the recipient Contact Id is read from the finalized ticket order, not from a caller.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>The event-ticket receipt is sent to the purchaser's own Contact after the purchase is finalized; setSaveAsActivity(false) means the send creates no activity record, so there is no create/read/update/delete for a CRUD check to guard. The recipient Id comes from the purchase record, not from any request parameter. The only reported source is the SOQL builder class, which is a helper rather than an entry point. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:143-149 — setTargetObjectId, setWhatId, setSaveAsActivity(false), sendEmail
 base/main/default/classes/event/service/EventPurchaseService.cls:533 caller (sendTicketReceiptQuietly, :1281)
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -743,10 +837,20 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is an internal alert from a scheduled job using explicit addresses, no target record and setSaveAsActivity(false); it performs no DML and no user- or guest-reachable path leads to it.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>This is an internal alert sent by a scheduled reconciliation job to the owner of a disputed gift and the configured reply-to address; it uses explicit addresses, no target record, and setSaveAsActivity(false), so it performs no DML. No user- or guest-reachable code path reaches it; the reported sources are a test-only fake-Id generator and the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:575-579 setToAddresses + setSaveAsActivity(false)
 base/main/default/classes/donation/async/RefundReconciliationBatch.cls:726 sole caller
@@ -755,6 +859,11 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -789,16 +898,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because every reported dataflow source is test-support framework code reachable only from test classes, and the sink is an email send with setSaveAsActivity(false) that creates no record; in production the method runs from the platform-event subscriber after a gift is finalized, to that gift's own donor.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Every source reported for this sink is test-support framework code (the mocking library's mock/verify methods and its fake-Id generator), which is only called from test classes. In production the method runs from a platform-event subscriber after a gift is finalized and emails matching-gift instructions to that gift's own donor Contact. setSaveAsActivity(false) is set, so no activity record is written and there is no DML to check. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:313-327 — loop builds messages, setSaveAsActivity(false)
 base/main/default/classes/donation/service/CompanyMatchService.cls:65 sole production caller
 fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -833,10 +957,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send itself performs no DML (setSaveAsActivity(false)); the staff actions that reach it re-read the donor Contact in user mode, so the running user's CRUD, FLS and sharing have already been enforced on the only record involved.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. The staff 'send portal link' and 'show portal code' actions accept a Contact Id, so both staff twins re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:30-47 - class header: the staff twins re-read the donor in the STAFF user's mode (resolveStaffDonorEmail) and refuse a donor that user cannot see
 base/main/default/classes/donor/controller/DonorPortalAdminController.cls:72 SendPortalLinkAction, :93 CreatePortalLinkAction, :156 ContactsSelector.selectById (USER_MODE), :175 AccountsSelector.selectPersonDonorById (USER_MODE)
@@ -844,6 +978,13 @@
 docs/security/appexchange-security-review-readiness.md F-10 (donor-portal IDOR closed 2026-09-25)</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -878,16 +1019,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because Messaging.sendEmail with explicit addresses and setSaveAsActivity(false) writes no record, so there is no DML to guard; the address must already belong to an existing donor, the request is rate-limited, and the response is identical whether or not it matched.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>This sends a one-time sign-in code to a donor's own address after a guest asks for it; the address must match an existing donor, the request is rate-limited, and the response is the same whether or not it matched. The message uses explicit addresses with no target record and setSaveAsActivity(false), so no record is created. The staff controller methods listed as sources reach a different send site (the staff twin) and share only the message-building helper; the fake-Id generator source is test-only. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:481-490 sendCodeEmail
 buildCodeEmail: setToAddresses, setSaveAsActivity(false)
 fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -922,16 +1078,32 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.
+USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a read-only COUNT() of PermissionSetAssignment, a setup object with no sharing model, returning a yes/no verdict and no record data; it is reachable only from the administrator-only setup console, and a user-mode read of setup objects requires View Setup and Configuration, which the package's admin permission set cannot assume every administrator holds.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>This is a read-only count of the site guest user's permission-set assignments, run from the administrator-only setup console to report whether the payment credential is granted to that guest user; it returns a yes/no verdict and no record data. It runs in system mode because PermissionSetAssignment is setup data that the running administrator can read only with 'View Setup and Configuration', which the package's admin permission set does not grant, and without it the console would falsely report the grant as missing. Only users holding the administrator permission set can reach it. The site carries its own SYSTEM_MODE comment saying so, as does every other setup-object read in the class.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:511-516 - `// SYSTEM_MODE: the guest user's assignments ... a count only, for the Fundraising_Admin-only Settings console.` above the query
 python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites (header-only count now excludes this file's reads)
 SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no ViewSetup userPermission</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -966,10 +1138,20 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send writes no record (setSaveAsActivity(false)), it runs only after a refund has already been processed under the Process_Refunds custom permission or by the reconciliation job, and the recipient is the refunded gift's own donor Contact.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>The refund notice is sent only after a refund has been processed, to the refunded gift's own donor Contact, with setSaveAsActivity(false), so the send itself writes no record. The interactive path requires a dedicated custom permission checked in the controller before any work, and the controller declares with sharing, which the service inherits. Two of the reported sources are test-only mocking framework methods; the third is that permission-gated controller. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/controller/RefundController.cls:22 refundDonation; doValidate checks FeatureManagement.checkPermission('Process_Refunds')
 base/main/default/classes/donation/service/RefundService.cls:15 `public inherited sharing class RefundService`; :328-334 sendRefundNotification after commit
@@ -979,6 +1161,13 @@
 base/main/default/classes/donation/async/RefundReconciliationBatch.cls:734 batch caller (sendRefundNotifications, ReceiptService:380)</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1013,10 +1202,20 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send writes no record (setSaveAsActivity(false)), and the only records involved, the gift and its donor Contact, are read in user mode before the message is built, so a staff user who cannot see them gets nothing to send.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>Resending a receipt is a staff action whose record access is enforced before the message is built: the gift and the donor Contact are read in user mode (object, field and sharing checks of the running user), so a user who cannot see either gets nothing to send. The recipient is always the gift's own donor Contact, not a caller-supplied address, and setSaveAsActivity(false) means the send writes no record. The other two sources reported are the SOQL builder's parameters, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:196 oppSel.selectById (USER_MODE), :211 conSel.selectById (USER_MODE)
 base/main/default/classes/donation/service/ReceiptService.cls:223-227 setTargetObjectId + setSaveAsActivity(false)
@@ -1025,6 +1224,13 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1059,16 +1265,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send performs no DML (setSaveAsActivity(false), explicit addresses); the gift Id it refers to was validated against the authenticated donor's own giving history when the request was recorded, and the message goes only to that gift's owner and the configured reply-to address.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>This notifies staff that a donor asked for a refund through the donor portal; the gift Id was checked against the authenticated donor's own giving history when the request was recorded, and the message goes to that gift's owner and the configured reply-to address, never to a caller-supplied address. It is plain text with explicit addresses and setSaveAsActivity(false), so it writes no record. The reported sources are the SOQL builder's parameter methods, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/guestrequest/handler/RefundRequestHandler.cls:194-199 setToAddresses + setSaveAsActivity(false)
 DonorPortalService.submitRefundRequest -&gt; requireOwnedDonation
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1103,10 +1324,20 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for DML operations involving "ContentDistribution" object</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>The claim that this delete should run in user mode is false because the user was already authorized for the action that triggers it (deleting or replacing a campaign post passes the controller's deletable/editable check on the post in user mode), and ContentDistribution is a standard object a 2GP permission set cannot grant: a user-mode delete of a public link created by a different staff member fails with INSUFFICIENT_ACCESS_OR_READONLY (measured), which would leave a revoked file publicly downloadable.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>This delete revokes the public ContentDistribution link a campaign post served, after staff have deleted the post or replaced its file. It runs only after an action the user was already authorised for: deleting a post first passes requireDeletable on Campaign_Post__c and commits the delete through a user-mode Unit of Work, so the platform refuses it without delete access; replacing a file first filters the posts through RecordAccess.editableIds. The revocation set is narrow: planRevocations keeps any link that another post still serves, so only the link the released post exposed is removed. ContentDistribution is a standard object a second-generation package permission set cannot grant, so a user-mode delete would depend on a manual admin step. The path is never reachable by a guest, and revoking a public link reduces exposure; it never widens it. Converting this delete to user mode was tested and rejected because it breaks the feature for the users it is built for. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: deleting a ContentDistribution created by another staff member with `Database.delete(rows, AccessLevel.USER_MODE)` fails with `INSUFFICIENT_ACCESS_OR_READONLY`. In user mode the public link of a post one colleague published could not be revoked when another colleague deletes that post, and the file would stay publicly reachable. System mode is what guarantees the link is withdrawn.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/campaign/controller/CampaignPostController.cls:156 - `requireDeletable(Campaign_Post__c.SObjectType, 'campaign posts')` before :166 `deletePost(postId)`
 base/main/default/classes/campaign/service/CampaignPostService.cls:163-187 - deletePost: the UserModeDML delete commits at :179-183 before `retirement.execute(false)` at :186
@@ -1116,6 +1347,12 @@
 base/main/default/classes/campaign/service/CampaignPostService.cls:453 - `private with sharing class FileRetirement`; outer class `with sharing` at :28</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (user-mode DML enforces the running user's object permissions and sharing)
+AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1150,15 +1387,30 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for DML operations involving "ContentDistribution" object</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because TestDataFactory is an @IsTest class that production code cannot invoke; the statement seeds a sample ContentDistribution fixture for unit tests and must succeed under whatever user the subscriber's org-wide test run executes as, so user mode would make the package's tests fail in an org whose test runner lacks the grant.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/TestDataFactory.cls:1-4 - @IsTest, `without sharing` with rationale
 base/main/default/classes/shared/TestDataFactory.cls:669-694 - seedOrgLogoOnSettings fixture</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm (@IsTest classes are excluded from code coverage and cannot be called from non-test code)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1193,15 +1445,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for DML operations involving "ContentDistribution" object</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because TestDataFactory is an @IsTest class that production code cannot invoke; the statement seeds a Settings__c fixture row for unit tests and must succeed under whatever user the subscriber's org-wide test run executes as (custom-setting DML in user mode would require Customize Application).</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/TestDataFactory.cls:1-4 - @IsTest, `without sharing` with rationale
 base/main/default/classes/shared/TestDataFactory.cls:669-694 - seedOrgLogoOnSettings fixture</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm (@IsTest classes are excluded from code coverage and cannot be called from non-test code)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_customsettings.htm (custom-setting DML requires Customize Application; unverified exact URL)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1236,16 +1504,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for DML operations involving "ContentDistribution" object
+This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert is the package's diagnostic log, which must succeed from catch blocks in every context including guest controllers; no permission set grants Create on Log__c by design, so a user-mode insert fails for every user (measured: `insert as user new Log__c` throws TypeException "DML operation INSERT not allowed on Log__c"), and the row holds only a class name, level and message with no caller-controlled routing.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>AppLogger persists diagnostic entries from catch blocks in every context, including guest controllers whose users cannot hold Create on any internal object; no permission set grants Create on Log__c by design, so logs are writable only through this class. Values are truncated to field length, Log__c is Private with read granted only to internal staff sets, and no client-callable method takes a log payload - the message text comes from server-side exceptions and developer-written strings. The class-level comment documents why it is `without sharing` and bypasses the Unit of Work. Converting this insert to user mode was tested and rejected. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `insert as user new Log__c(...)` throws `System.TypeException: DML operation INSERT not allowed on Log__c`, because no permission set grants Create on the log object - by design, so that no user can author or forge diagnostic rows. A user-mode insert would therefore lose every log entry, including the ones that record security-relevant failures.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/AppLogger.cls:1-9 - `without sharing` with rationale
 base/main/default/classes/shared/AppLogger.cls:117-135 - DML-limit guard; left() truncation; failures swallowed
 Log__c OWD Private; Fundraising_Admin/User/ReadOnly: Read only, no Create; GuestDonor: no grant</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (user-mode DML throws when the running user lacks object Create)
+Measured in a scratch org (2026-09-30): `insert as user new Log__c(...)` throws System.TypeException "DML operation INSERT not allowed on Log__c"</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1280,10 +1565,23 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for DML operations involving "ContentDistribution" object
+This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.
+USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false on both counts: the upsert is shared by the InstallHandler (package system user, no permission set) and the admin console (gated by the Manage_Fundraising_Settings custom permission), and in both contexts a user-mode write on the package's hierarchy custom setting requires Customize Application, which neither the install user nor the package's admin permission set can hold (measured: `upsert as user` throws SecurityException). The ContentDistribution query reads only a Content Delivery the same code created from a packaged static resource.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>This upsert is shared by the package install handler, which runs as the package's system user with no permission set, and by the settings console controller, which is granted only in the Fundraising_Admin permission set. System mode is kept because the install path has no FLS to enforce and because DML on a Hierarchy Custom Setting in user mode requires Customize Application, a system permission no packaged permission set can carry. The console path does not rely on Apex class access alone: every controller action that reaches this write (SaveGeneralSettings, DetectOrgFeatures, ResetToDefaults, SaveExperienceSite) first checks the packaged custom permission Manage_Fundraising_Settings, granted only in Fundraising_Admin, and refuses the save with a generic error when the running user does not hold it. The site carries a SYSTEM_MODE comment naming that gate. The user-mode alternative was tested and does not work for the people who use this screen. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Schema.sObjectType.Settings__c` reports isCreateable, isUpdateable and isAccessible all false, and `upsert as user` on the settings row throws `System.SecurityException: Access to entity 'Settings__c' denied`. The platform ties custom-setting DML to Customize Application, which is a system permission the fundraising administrator is not expected to hold, so a user-mode write would lock every non-system-administrator out of the settings console. The custom-permission check before the write is the access control; it is enforced in Apex on every action that reaches this line.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/SettingsService.cls:338-345 - `// SYSTEM_MODE:` reason naming the Manage_Fundraising_Settings gate, then `upsert as system settings`
 base/main/default/classes/setup/controller/SetupController.cls:1737-1742 - SettingsWriteAction.requireSettingsPermission(): FeatureManagement.checkPermission('Manage_Fundraising_Settings') else addError(SETTINGS_NOT_AUTHORIZED)
@@ -1294,6 +1592,15 @@
 docs/security/appexchange-security-review-readiness.md F-13</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.cs_schema_settings.htm
+https://applicationperfection.com/2024/02/29/control-who-gets-read-access-to-custom-settings/
+https://github.com/patronmanager/apex-dml-manager/issues/2
+https://help.salesforce.com/s/articleView?language=en_US&amp;id=release-notes.rn_apex_default_user_mode.htm&amp;release=262&amp;type=5
+https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1328,10 +1635,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>This query detects external data flowing into a javascript execution context when that data comes from the database or other stored parameters influced by external users. This may be a false positive if the datatype is safe to render unescaped (such as an integer or rich text field).</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>The claim that stored, externally influenced data reaches a JavaScript execution context is false because the reported source (the donor's portal session token) is only passed as an Apex parameter and never written to the DOM; the value rendered at the flagged line is the response envelope's error text or a packaged constant, bound through an LWC `{expression}`, which the framework renders as escaped text and never as HTML or script.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>The flagged source is the donor's own portal session token read from sessionStorage; it is passed as an Apex parameter to DonorPortalController.getGivingStatement and is never written into the DOM. The value rendered at base/main/default/lwc/pfGivingStatement/pfGivingStatement.html:34 is either the `error` string of the controller's response envelope or a package-authored literal. The controller's action classes extend GuestAction, whose callerSafeMessage returns an AppException message (every one on this path is a constant: the invalid-session message, 'Choose a tax year.', 'That tax year is not available.', 'A donor is required to build a giving statement.') or one fixed generic sentence for any other exception - no record field, request parameter or token is echoed. Finally, the sink is an LWC `{expression}` text binding, which the framework renders as a text node, not HTML; neither pfGivingStatement nor publicDonorDashboard uses innerHTML, lwc:inner-html or lwc:dom="manual". The flagged source is also shape-checked: the value read from sessionStorage is accepted only when it matches the exact shape of a session token the server issues (64 lowercase hexadecimal characters); anything else is discarded and removed from storage before it reaches component state or an Apex call. The finding is a false positive - the value is never rendered - and storage content that the component did not write cannot enter it at all.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.js:314-331 - stored = window.sessionStorage.getItem(SESSION_KEY) (SESSION_KEY = 'pf-donor-portal-session', :41); assigned to this.token then loadDashboard(); not bound into markup
 base/main/default/lwc/publicDonorDashboard/publicDonorDashboard.js:45 and :320-330 - `SESSION_TOKEN_SHAPE = /^[0-9a-f]{64}$/`; a stored value that fails the test is removed and the sign-in form is shown
@@ -1347,6 +1664,13 @@
 grep lwc:dom|lwc:inner-html|innerHTML in lwc/pfGivingStatement and lwc/publicDonorDashboard - zero hits</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://lwc.dev/guide/html_templates
+https://trailhead.salesforce.com/content/learn/modules/secure-clientside-development/mitigate-crosssite-scripting
+https://developer.salesforce.com/docs/platform/lwc/guide/security-lwsec-sanitize.html</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1381,16 +1705,31 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isDeletable() permisison before performing the delete operation.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>The claim that an isDeletable() check is missing is false because the delete runs in batch Apex, which the scan's own rule exempts, over a scope produced only by the retention selectors (diagnostic, staging and request rows past the administrator-configured window); no caller chooses the rows, and a job owner without Delete on an internal object would otherwise silently leave expired data in place.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>This is the data-retention purge: the scope is produced only by the per-target selector locators (Log__c and Transaction_Log__c older than the admin-configured retention window, terminal Donation_Staging__c and Guest_Request__c older than it, and terminal or stale portal tokens after 7 days). It runs as a scheduled batch or when an administrator runs it from the setup console; no caller supplies record Ids. No packaged permission set grants Delete on these append-only tables by design, so the purge must delete in system mode.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/async/RetentionPurgeBatch.cls:1-16 - rationale; `without sharing`
 base/main/default/classes/shared/async/RetentionPurgeBatch.cls:41-78 - fixed selector locators per Target; else throws
 base/main/default/classes/setup/service/SettingsService.cls:927-932 - dataRetentionDays default 90 (no lower floor; admin-controlled)</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1425,16 +1764,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert is an operations alarm written by a scheduled job with no user input, every field a constant or a count of stuck rows; the job runs as whoever scheduled it, including the install context that holds no permission set, and Salesforce's own guidance accepts system-mode DML in scheduled context.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>This is an operations alarm written by a scheduled job with no user input: every field is a constant or a message built from a count of stuck staging rows. The job is scheduled at package install (post-install context, which holds no permission sets) or by an administrator from the setup console, so the insert must not depend on the scheduling user's Transaction_Log__c grants; Transaction_Log__c is an internal audit object not granted to guests. No record Id or value from a caller reaches the insert.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/ReconciliationHeartbeat.cls:8-11 - `without sharing` with rationale (scheduled job; runs as whoever scheduled it)
 base/main/default/classes/donation/async/ReconciliationHeartbeat.cls:26-62 - execute(): selector count -&gt; constant-valued log insert -&gt; admin email
 base/main/default/classes/setup/controller/PostInstallHandler.cls:495 - scheduleIfAbsent schedules it at install</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1469,15 +1823,30 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert records the outcome of a scheduled repair sweep with constant values, the staging Id being repaired and a caught exception message; it runs in batch context, including when scheduled at install by a user with no permission set, and no caller-supplied value reaches it.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>logSweep records the outcome of the scheduled Stripe-to-Salesforce repair sweep; its arguments are constants chosen by the sweep, the staging Id it is repairing, and a caught exception message. The sweep is scheduled at install or started by an administrator from the setup console, and the install-context owner holds no permission sets, so the audit insert runs in system mode. No caller-supplied value reaches it.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/StripePaymentSweep.cls:23-26 - `without sharing` with rationale
 base/main/default/classes/donation/async/StripePaymentSweep.cls:200-210 - private logSweep, all values from sweep internals</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1512,15 +1881,30 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert writes the job's own audit row with every field system-derived (Ids created in the same transaction, a constant event type, an exception message, a timestamp), in a scheduled batch context the scan's own rule exempts and that may run as a user with no permission set.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>This inserts the reconciliation audit row (Transaction_Log__c) for each staging the job processes; every field is system-derived (staging Id, Opportunity Id created by the same transaction, a constant event type/status, an exception message, a timestamp). It runs in the scheduled reconciler and the internal retry action; the scheduled run can be owned by the install context user, which holds no permission sets, so the audit write must not depend on the running user's grants. Transaction_Log__c is internal and not granted to the guest profile.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/StagingReconciliationBatch.cls:186-250 - log fields populated from staging Id, oppId, constants, e.getMessage()
 base/main/default/classes/donation/async/StagingReconciliationBatch.cls:281 - single insert per staging</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1555,10 +1939,21 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write seeds the org-default row of the package's own hierarchy custom setting from compiled constants, runs only in the InstallHandler as the package's system user (no permission set), and fills only blank fields; custom-setting DML in user mode requires Customize Application, which the install user does not hold, so a user-mode write would fail the install.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
           <t>This seeds the org-default row of the package's hierarchy custom setting with constant defaults during package install or upgrade, filling only blank fields. It runs only from the InstallHandler, which executes as the package's special system user; that user holds no permission set, so there is no user FLS to enforce. The method is not reachable from any controller, guest page or subscriber Apex.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1570,6 +1965,11 @@
 All values are package constants or derived from existing org data; no user input</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1604,10 +2004,21 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>The claim that this write bypasses a required createable/updateable check is false: the row is the package's own job cursor (two timestamps computed from the payment gateway's responses), the statement runs only inside a scheduled batch with no interactive user, and Salesforce's own guidance accepts system-mode DML in batch context as a false positive. A user-mode write would make the job's correctness depend on which administrator happened to schedule it.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>This write stores two Datetime high-water marks (refund and dispute cursors) computed by the batch from the payment gateway's list responses; no user-supplied value reaches it. It runs only in the scheduled reconciliation job or when an administrator starts that job from the settings console, and the cursor must advance regardless of the scheduling user's field permissions or the next run re-reads the whole window. Enforcing FLS here would not protect any user data; it would only let a missing grant silently stall reconciliation.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/RefundReconciliationBatch.cls:334-344 finish(): only when !hadError; sets Refund_Reconcile_Cursor__c / Dispute_Reconcile_Cursor__c from cursorTarget/disputeCursorTarget (system-computed), then `upsert as system s`
 base/main/default/classes/donation/async/RefundReconciliationBatch.cls:170-171 reads the same cursors with a 2h overlap
@@ -1616,6 +2027,11 @@
 base/main/default/classes/donation/async/RefundReconciliationBatch.cls:155 and :336 use Settings__c.getOrgDefaults() (the org-default row only)</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=platform.code_schedule_batch_apex.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1650,10 +2066,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.
+USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write is to the org-default row of the package's own custom setting, reached only through an administrator console gated by the Manage_Fundraising_Settings custom permission, with both the field name and the value validated against fixed allow-lists; and a user-mode upsert on a hierarchy custom setting requires Customize Application, which the package's own admin permission set cannot grant (measured: `upsert as user` throws SecurityException for a Fundraising_Admin user).</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
           <t>This writes one of two scheduling-interval fields on the org-default Settings__c row; the family is checked against two fixed names and the interval against a fixed allow-list before the write. It is reached only from the settings console controller's ScheduleJobFamily action, which is granted only in the Fundraising_Admin permission set. System mode is retained because DML on a Hierarchy Custom Setting in user mode requires Customize Application, which a packaged permission set cannot grant. ScheduleJobFamily.doValidate() first checks the packaged custom permission Manage_Fundraising_Settings (granted only in Fundraising_Admin) and refuses the save when the running user does not hold it; the site carries a SYSTEM_MODE comment naming that gate. The user-mode alternative was tested and does not work for the people who use this screen. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Schema.sObjectType.Settings__c` reports isCreateable, isUpdateable and isAccessible all false, and `upsert as user` on the settings row throws `System.SecurityException: Access to entity 'Settings__c' denied`. The platform ties custom-setting DML to Customize Application, which is a system permission the fundraising administrator is not expected to hold, so a user-mode write would lock every non-system-administrator out of the settings console. The custom-permission check before the write is the access control; it is enforced in Apex on every action that reaches this line.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/SettingsService.cls:1022-1026 - `// SYSTEM_MODE:` reason naming the ScheduleJobFamily gate, then `upsert as system s`
 base/main/default/classes/setup/controller/SetupController.cls:2192-2201 - ScheduleJobFamily extends SettingsWriteAction; doValidate() calls requireSettingsPermission() before the family / interval checks
@@ -1662,6 +2090,13 @@
 docs/security/appexchange-security-review-readiness.md F-13</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.cs_schema_settings.htm
+https://github.com/patronmanager/apex-dml-manager/issues/2
+https://help.salesforce.com/s/articleView?language=en_US&amp;id=release-notes.rn_apex_default_user_mode.htm&amp;release=262&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1696,10 +2131,21 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write targets the org-default row of the package's own hierarchy custom setting, runs only inside the InstallHandler as the package's system user (no permission set), and writes an Id the same install step just produced; custom-setting DML in user mode would additionally require Customize Application, which no install user holds.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>This stores the Id of the event pricebook that the same install step just found or created on the org-default custom setting row, only when that field is blank. It runs only from the InstallHandler as the package's system user, which has no permission set to enforce, and never overwrites an administrator's value. No user input reaches the write.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1711,6 +2157,11 @@
 Value is the Id of a record this same method just found or inserted; no user input</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1745,10 +2196,21 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write is to the org-default row of the package's own custom setting, from the InstallHandler's system user with no permission set, storing an Id the install step itself created; there is no running user whose field permissions could meaningfully be checked.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
           <t>This records the Id of the event donation product, found or created by the same install step, on the org-default custom setting row when that field is blank. It runs only from the InstallHandler as the package's system user and does not overwrite an administrator's value. No user input reaches the write.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1760,6 +2222,11 @@
 Value is the Id of a record this same method just found or inserted; no user input</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1794,10 +2261,21 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write is to the org-default row of the package's own custom setting, from the InstallHandler's system user with no permission set, storing an Id the install step itself created; the administrator's existing value is never overwritten.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>This records the Id of the event processing-fee product, found or created by the same install step, on the org-default custom setting row when that field is blank. It runs only from the InstallHandler as the package's system user and never overwrites an administrator's value. No user-supplied data reaches it.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1809,6 +2287,11 @@
 Value is the Id of a record this same method just found or inserted; no user input</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1843,15 +2326,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs during install as the package's system user, which holds no permission set, and copies the package's own static-resource image into ContentVersion with constant Title and PathOnClient; ContentVersion is a standard object a 2GP permission set cannot grant, and no subscriber data is involved.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
           <t>PackagedAssetSeeder copies the package's own static-resource images (default logo, hero image, social-share image) into ContentVersion so the public pages have a default; Title/PathOnClient are constants and VersionData is the packaged resource body. It runs in the post-install context, whose user holds no permission sets, and ContentVersion is a standard object a second-generation package permission set cannot grant. The interactive admin upload of a custom logo uses user mode instead.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/SettingsService.cls:543-594 - PackagedAssetSeeder, inner `without sharing` with rationale; content from DefaultOrgLogo/DefaultHeroImage/DefaultSocialShareImage
 base/main/default/classes/setup/service/SettingsService.cls createLogoDistribution - USER_MODE for the admin upload path</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm (post-install script runs as a package-specific system user)
+AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1886,12 +2385,28 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs during install as the package's system user, which holds no permission set, and publishes a public link for the file the previous statement created from a packaged static resource; ContentDistribution is a standard object a 2GP permission set cannot grant, and the public link is the feature (default images on unauthenticated donation pages and receipts), not a leak.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
           <t>This publishes a public link for the package's own default image, which must be publicly reachable because it is rendered on unauthenticated donation pages and in receipt emails. The file is created one line earlier from a packaged static resource, so no subscriber or user file can be published through this path. It runs in the post-install context (no permission sets) or from an administrator's reset-to-default action.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/SettingsService.cls:570-581 - ContentDistribution on the ContentVersion just inserted from a static resource</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm (post-install script runs as a package-specific system user)
+AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -1928,10 +2443,20 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs only inside the package InstallHandler as the package's system user, which holds no permission set, and Pricebook2 is a standard object a 2GP permission set cannot grant; every value is a constant, so no user input reaches the write.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
           <t>This creates the package's event pricebook once, at install, with a constant name, only if it does not already exist. Pricebook2 is a standard object that a packaged permission set cannot grant, and the method runs only from the InstallHandler as the package's system user. No controller, guest page or subscriber code can call it.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1944,6 +2469,11 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1501 `new Pricebook2(Name = EVENT_PRICEBOOK_NAME, IsActive = true)` - constant values; inserted only when neither the current nor the legacy pricebook exists</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1978,10 +2508,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs only inside the package InstallHandler as the package's system user, which holds no permission set, and Product2 is a standard object a 2GP permission set cannot grant; every field value is a compiled constant.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
           <t>This creates the package's generic event donation product once, at install, with constant field values and only if it does not already exist. Product2 is a standard object that a packaged permission set cannot grant, and the code runs only from the InstallHandler as the package's system user. It is not reachable from any user-facing entry point.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -1994,6 +2534,11 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1534 `new Product2(Name = EVENT_DONATION_PRODUCT_NAME, IsActive = true)` - constants; only when no Product2 with that name exists (query WITH SYSTEM_MODE)</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2028,10 +2573,20 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs only inside the package InstallHandler as the package's system user, which holds no permission set, and Product2 is a standard object a 2GP permission set cannot grant; the values are constants.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
           <t>This creates the package's event processing-fee product once, at install, with constant values and only if it does not already exist. Product2 is a standard object a packaged permission set cannot grant, and the method runs only from the InstallHandler as the package's system user. It has no interactive or guest caller.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -2044,6 +2599,11 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1578 `new Product2(Name = EVENT_FEE_PRODUCT_NAME, IsActive = true)` - constants; only when absent</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2078,15 +2638,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs in the reconciliation job that finalizes a paid ticket order, a context the scan's own rule exempts, and CampaignMember is a standard object a 2GP permission set cannot grant; the Contact and Campaign Ids come from the finalized order, not from a caller.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>After a paid ticket order is finalized by the reconciliation job, attendees with a Contact are added to the event Campaign as CampaignMembers. CampaignMember is a standard object that a second-generation package permission set cannot grant, and the finalizer runs in scheduled context, so the insert runs in system mode. The Campaign comes from the server-side staging record and the Contacts from the attendees created in the same finalization; existing members are skipped, and no browser input chooses either.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService.cls:570-590 - campaign from staging, contacts from attendees, existing members excluded
 Comment cites 'CampaignMemberSyncService.syncForOpportunities', which does not exist (method is syncForDonations); 'after a guest order is committed' - it actually runs in the batch/retry finalizer</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_batch_interface.htm (batch Apex runs asynchronously; Salesforce false-positive guidance exempts batch and async context)
+AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2121,15 +2697,31 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs inside the platform-event subscriber trigger as the Automated Process entity, which can hold no permission set, and CampaignMember is a standard object a 2GP permission set cannot grant; the Contact and Campaign Ids come from the finalized donation itself, not from a caller.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
           <t>This adds the donor to the donation's campaign as a CampaignMember after a gift is finalized; it runs in the platform-event subscriber trigger, which executes as the Automated Process entity. CampaignMember is a standard object that a second-generation package permission set cannot grant, and the Automated Process context has no user permissions to enforce. CampaignId and ContactId are read from the finalized Opportunity itself, and existing memberships are skipped, so the insert cannot target arbitrary campaigns or contacts.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/CampaignMemberSyncService.cls:68 - CampaignMember built from Opportunity CampaignId + resolved contact
 base/main/default/classes/donation/service/CampaignMemberSyncService.cls:80 - comment present and accurate</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.platform_events.meta/platform_events/platform_events_subscribe_apex.htm
+AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2164,10 +2756,20 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the insert runs only inside the package InstallHandler as the package's system user, which holds no permission set, and the rows are starter templates whose text is literal in the package source; no user supplies any value and no user's permissions exist to check.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
           <t>This inserts a starter set of question and FAQ templates, whose text is literal in the package source, the first time the package is installed and only when the template table is empty. It runs only from the InstallHandler as the package's system user, which holds no permission set. Administrators edit or delete these templates afterwards through the normal, permission-checked console.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -2178,6 +2780,11 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1615-1672 seedContentTemplates inserts starter question/FAQ Content_Template__c rows (RecordTypeId, Name, Prompt__c, Question_Type__c, Is_Active__c, Picklist_Options__c, Answer__c) only when the table is empty; all text is literal in source</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2212,10 +2819,21 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.
+This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the upsert creates or refreshes the six packaged theme records from constants compiled into the package, runs only in the InstallHandler as the package's system user with no permission set, and cannot be invoked by any user at runtime.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
           <t>This creates or refreshes the six packaged page-design theme records from constants compiled into the package, during install or upgrade. It runs only from the InstallHandler as the package's system user, which holds no permission set, and every assigned value is a literal from the package source. Packaged themes are read-only to administrators, who clone them to customise, so no administrator data is overwritten.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -2227,6 +2845,11 @@
 Packaged themes are read-only in the console (clone to edit), so overwriting their style fields on upgrade is the intended contract</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2261,16 +2884,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because PricebookEntry is a standard object a 2GP permission set cannot grant, and the insert runs from install (package system user, no permission set), admin ticket-tier saves and guest purchases, where the Guest licence cannot hold Create; every value is fixed by Apex from a Product2 the package itself created.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
           <t>This creates the standard pricebook PricebookEntry a ticket Product2 needs before an OpportunityLineItem can reference it. Values are fixed by Apex (the Product2 the package created for the ticket tier, the pricebook Id, a placeholder unit price, IsActive=true, the org currency) - the real price lives on the line item. PricebookEntry/Pricebook2 are standard objects the package permission sets cannot grant, and the same method runs in the post-install context and the scheduled finalizer; the staff entry point first verifies the user can edit the event Campaign and that the tier belongs to it.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/PricebookService.cls - class `without sharing` with doc rationale (Pricebook2 unresolvable under with sharing in post-install context)
 base/main/default/classes/event/service/PricebookService.cls:142-143 - PricebookEntry(Product2Id, Pricebook2Id, UnitPrice=PLACEHOLDER_PRICE, IsActive=true)
 base/main/default/classes/event/controller/EventTicketAdminController.cls:156-176, 197-263 - requireCampaignWritable + requireTiersBelongToCampaign before ensureEntriesFor; wrapped non-fatal</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2305,16 +2943,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Delete operations that are performed without checking for isCreatable() permisison before performing the Create operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because PricebookEntry is a standard object a 2GP permission set cannot grant, and the insert runs from install (package system user, no permission set), admin ticket-tier saves and guest purchases, where the Guest licence cannot hold Create; every value is fixed by Apex from a Product2 the package itself created.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
           <t>This creates the package event pricebook PricebookEntry a ticket Product2 needs before an OpportunityLineItem can reference it. Values are fixed by Apex (the Product2 the package created for the ticket tier, the pricebook Id, a placeholder unit price, IsActive=true, the org currency) - the real price lives on the line item. PricebookEntry/Pricebook2 are standard objects the package permission sets cannot grant, and the same method runs in the post-install context and the scheduled finalizer; the staff entry point first verifies the user can edit the event Campaign and that the tier belongs to it.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/PricebookService.cls - class `without sharing` with doc rationale (Pricebook2 unresolvable under with sharing in post-install context)
 base/main/default/classes/event/service/PricebookService.cls:142-143 - PricebookEntry(Product2Id, Pricebook2Id, UnitPrice=PLACEHOLDER_PRICE, IsActive=true)
 base/main/default/classes/event/controller/EventTicketAdminController.cls:156-176, 197-263 - requireCampaignWritable + requireTiersBelongToCampaign before ensureEntriesFor; wrapped non-fatal</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2349,16 +3002,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the update runs in a scheduled batch (and the equivalent staff 'Retry now' path that re-reads the gateway), writing only the caught exception message and the gateway's own payment status onto a guest-created staging row that no running user is granted Edit on; the values never come from the caller.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
           <t>The reconciler writes the finalization error and, for an unpaid staging past its TTL, sets Status__c='Expired'; the values come from the caught exception and Stripe's PaymentIntent status, never from the caller. It runs in a scheduled batch and in an internal 'retry now' action; Fundraising_User can view and retry stagings but deliberately has no Edit on Donation_Staging__c (the row is system-owned state), so the status transition must run in system mode. The only caller input is the staging Id on the retry path, and the action it triggers is the same idempotent reconciliation the scheduler would perform anyway.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/StagingReconciliationBatch.cls:260-276 - upd built from e.getMessage() and pi.status; Expired only when past TTL and payment not succeeded
 base/main/default/permissionsets/Fundraising_User - Donation_Staging__c Create/Read, no Edit
 base/main/default/classes/donation/staging/DonationStagingSelector.cls selectById - SYSTEM_MODE read, so retry has no record-visibility gate (minor; controller granted only to staff sets)</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2393,10 +3061,20 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write increments the failed-attempt counter on a portal access code and locks it, a brute-force defence that must run as the Experience Cloud guest user; the Guest User licence cannot hold Edit on any object, and the credential table carries no guest grant at all, so a user-mode update would disable the lockout.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
           <t>This increments the failed-attempt counter on a donor-portal access code and locks it after the maximum attempts - a brute-force defence. The guest user cannot hold Edit on any object, and the credential table carries no guest grant at all, so the write must be system mode. The row is resolved server-side from the submitted email under FOR UPDATE, never from a client-supplied Id, and the only fields written are Attempt_Count__c and Status__c='Locked', both computed by Apex. The worst a caller can do is lock a code, which the legitimate donor replaces by requesting a new one.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:367-383 - bump built from selector row; attempts computed server-side
 base/main/default/classes/donor/service/DonorPortalService.cls class header - `without sharing` with rationale
@@ -2404,6 +3082,11 @@
 ControllerAction.run has no savepoint rollback on caught error, so the increment persists after a failed verify (intended)</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>project memory/platform limit: Guest User licence cannot be granted object Edit/Delete (AGENTS.md guest-user notes) - unverified against a primary URL in this pass</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2438,10 +3121,20 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement runs only inside the package InstallHandler, which executes as a package-specific system user that holds no permission set, so there is no user whose isUpdateable() could be consulted; and Pricebook2 is a standard object that a second-generation package permission set cannot grant, so no permission check could ever be satisfied by package metadata.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
           <t>This renames the package's own event pricebook from its earlier name to the current one during upgrade, so existing price book entries are kept. Pricebook2 is a standard object that a packaged permission set cannot grant, and the code runs only from the InstallHandler as the package's system user. The new name is a constant; nothing user-supplied is written.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -2454,6 +3147,11 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1477-1499 seedEventPricebook: if only the pre-rename pricebook exists, renames it in place to EVENT_PRICEBOOK_NAME ('Fundraising Events') so its PricebookEntry rows survive; the new name is a constant</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2488,10 +3186,20 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write runs asynchronously from the request queue, after ownership of the ticket order was verified synchronously against the donor's portal session, and only the attendee-name fields of that order's own seats are written; the running user is the guest user or the sweep's scheduler, neither of whom can hold Edit on the object.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
           <t>A donor who is signed in to the donor portal with a verified access code may name the blank guest seats on their own ticket order. Ownership is checked synchronously before anything is queued (requireOwnedOrder against the portal session), the verified order Id is stored server-side in Subject_Id__c, and this handler re-reads the seats of that order only - seat Ids in the payload that are not on the order, cancelled seats, and seats already named are ignored. The only fields written are First_Name__c, Last_Name__c and (when blank) Email__c, length-clipped and email-validated, which are exactly the data the donor is entitled to supply; the Guest licence cannot hold Edit, hence system mode.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:1231-1283 - requireOwnedOrder(ctx, orderId); payload rebuilt from owned seats, never echoed from the browser
 base/main/default/classes/guestrequest/handler/AttendeeNamingHandler.cls:83-117 - seats re-read from Subject_Id__c order; unmatched/cancelled/already-named seats skipped; NAME_MAX/EMAIL_MAX
@@ -2499,6 +3207,11 @@
 base/main/default/classes/guestrequest/handler/AttendeeNamingHandler.cls:19 - MAX_SEATS payload cap</t>
         </is>
       </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>unverified in this pass: Guest User licence cannot hold object Edit (project-documented platform limit)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2533,16 +3246,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write claims queued requests (status and attempt counter only) so the queueable and the sweep never process a row twice; it runs in the guest user's own queueable, where the Guest User licence cannot hold Edit on any object, or in the scheduled sweep, so a user-mode update could never succeed.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
           <t>This claims queued public requests (Status__c Pending -&gt; Processing, Attempt_Count__c + 1) so the queueable and the sweep never process the same row twice. It runs in the guest user's own queueable - the Guest licence cannot hold Edit on any object - or in the scheduled sweep; the request Ids come from the row the server just inserted or from the sweep's query, and only rows still Pending are claimed. Both written values are computed by Apex.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/guestrequest/service/GuestRequestService.cls:120-138 - only Pending rows; status/attempts computed
 base/main/default/classes/guestrequest/async/GuestRequestQueueable.cls:31, base/main/default/classes/guestrequest/async/GuestRequestSweepBatch.cls:48 - sole callers of process()
 Fundraising_GuestDonor has no Edit on Guest_Request__c</t>
         </is>
       </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>unverified against primary docs (developer.salesforce.com apex_scheduler.htm returned 403 / cookie wall); secondary: https://help.salesforce.com/s/articleView?id=sf.code_schedule_batch_apex.htm (search snippet: scheduled Apex executes under the user who scheduled the job)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2577,16 +3305,32 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the write closes the donor's own refund request only after the refund itself succeeded under the refund controller's Process_Refunds authorization; it selects rows by the refunded gift's Id and writes only a status, and the staff user is not granted Edit on the guest-request object by design, so a user-mode update would leave the portal showing a completed refund as pending.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
           <t>After staff refund a gift, this closes the donor's matching refund request that was parked for review so the donor portal stops showing it as pending. It runs only after the refund itself succeeded under the refund controller's own authorization, it selects requests by the refunded Opportunity Id and only those in Awaiting_Review of the refund type, and it writes a fixed status, a fixed donor-facing sentence and a timestamp. The request rows are created by the guest user and owned by the site's default owner, so an internal user generally has no sharing on them; system mode is what lets the refund close its own request.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/RefundService.cls:352-357 - sole caller, constant status/message
 base/main/default/classes/guestrequest/service/GuestRequestService.cls:214-238 - filters to Awaiting_Review + type
 Fundraising_User has Edit but not View All on Guest_Request__c; Admin has Modify All - so the real blocker for a user-mode update is record sharing, not the object grant</t>
         </is>
       </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (user-mode DML requires the running user's Edit permission on the object)
+https://help.salesforce.com/s/articleView?id=sf.perm_sets_custom.htm (custom permission Process_Refunds is the authorization the refund controller enforces; unverified exact URL)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2621,10 +3365,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>This query looks for CRUD Update operations that are performed without checking for isUpdateable() permisison before performing the Update operation on the Object and its fields.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the update runs only inside the InstallHandler as the package's system user, which holds no permission set, touches only the package's own theme records (selected by their packaged names) and writes a URL computed from the org's own site settings; no user input and no user permissions are involved.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
           <t>This backfills the default hero image URL on the package's own theme records during install or upgrade, limited to the packaged theme names. It runs only from the InstallHandler as the package's system user, which has no permission set, and the value is a URL the install step itself generated from a packaged static resource. No interactive or guest caller reaches it.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:18 `public without sharing class PostInstallHandler implements InstallHandler`; lines 1-4 header: 'runs in package install/upgrade context'
 base/main/default/classes/setup/controller/PostInstallHandler.cls:169-173 doc: 'the script runs as a per-package system user that does not exist before runtime'
@@ -2636,6 +3390,11 @@
 Value originates from the packaged static-resource distribution URL seeded by SettingsService.ensureDefaultImagesSeeded, not user input</t>
         </is>
       </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2670,16 +3429,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the query reads only Id and CurrencyIsoCode for parent records whose Ids a trigger-driven rollup already holds, in order to convert amounts before writing the rollup total; the object name comes from the Id's schema token, not from input, and the read runs in trigger context as the DML writer, where a user without the parent's currency field would otherwise see the rollup silently fail.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
           <t>The query reads only Id and CurrencyIsoCode for parent records whose Ids the trigger-driven rollup already holds, so it can convert gift amounts into the parent's currency before writing the total. The object name comes from the Id's own schema token, not from input, so the dynamic FROM cannot be injected. The result is a map of Id to ISO code that is used in the arithmetic and never returned to a user. Running in user mode would make a rollup fail or mis-convert for a staff user who can save a gift but lacks read FLS on a standard CurrencyIsoCode field. The code catches any exception and falls back to the corporate currency.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/CurrencyResolver.cls:258-269 - dynamic FROM built from Id.getSObjectType().getDescribe().getName(); bind is Set&lt;Id&gt;; SYSTEM_MODE; catch returns empty map
 base/main/default/classes/shared/CurrencyResolver.cls - isoCodesByRecordId doc states the reason (currency code is not customer data)
 base/main/default/classes/donation/selector/OpportunitiesSelector.cls:189 - upstream SYSTEM_MODE rollup read, itself commented</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2714,10 +3488,20 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>The claim that USER_MODE is missing is false: the query is executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), which enforces the running user's object permissions, field-level security and sharing. The scanner recognises only the literal WITH USER_MODE clause, and adding that clause to this query is impossible: the platform rejects a dynamic query that carries both (measured: "Cannot use the WITH AccessLevel clause in dynamic queries that also specify an access level").</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
           <t>This query already runs in user mode: it is executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), which enforces object permissions, field-level security and sharing for the running user. The scanner only recognises the literal WITH USER_MODE clause and does not read the AccessLevel argument. The caller, DonorDetailController.requireDonor, uses this user-mode, sharing-enforced read as its IDOR gate: if the record Id supplied by the component is not visible to the user, zero rows come back and the controller throws "Donor not found" before any related data is read. A literal `WITH USER_MODE` clause cannot be added to satisfy the pattern: the query is built by the FFLib query factory as a dynamic string, and the platform rejects a dynamic query that carries both the clause and an AccessLevel argument. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Database.queryWithBinds('SELECT Id FROM Account WITH USER_MODE', binds, AccessLevel.USER_MODE)` throws `System.SecurityException: Cannot use the WITH AccessLevel clause in dynamic queries that also specify an access level.` The AccessLevel argument is the documented way to run a dynamic query in user mode.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/selector/AccountsSelector.cls:311-~322 - Database.queryWithBinds(..., AccessLevel.USER_MODE); class is inherited sharing
 base/main/default/classes/donor/controller/DonorDetailController.cls:352 - requireDonor calls the Account/Contact detail selector and throws QueryException("Donor not found") on an empty result
@@ -2726,6 +3510,12 @@
 base/main/default/classes/campaign/controller/FundraiserDetailController.cls:39 - getRecurring never calls AccountsSelector; Checkmarx path 4/6 source is spurious</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2760,10 +3550,20 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>The claim that USER_MODE is missing is false: the query factory is built with CRUD and FLS enforcement on and the SOQL is executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), which enforces object permissions, FLS and sharing for the running user. The scanner recognises only the literal WITH USER_MODE clause, which the platform forbids in a dynamic query that already specifies an access level (measured).</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
           <t>The SOQL string is built by the query factory and executed with Database.queryWithBinds(..., AccessLevel.USER_MODE), so object permissions, FLS and sharing are enforced for the running user. The factory is also constructed with CRUD enforcement on. The scanner does not recognise the AccessLevel argument. The only caller that passes a client-supplied Id is DonorDetailController.requireDonor, which throws "Donor not found" when this user-mode read returns nothing, so a user cannot reach another donor's gifts, recurring plans or requests by guessing an Id. A literal `WITH USER_MODE` clause cannot be added to satisfy the pattern: the query is built by the FFLib query factory as a dynamic string, and the platform rejects a dynamic query that carries both the clause and an AccessLevel argument. Measured 2026-10-01 in a scratch org, running as a Standard User who holds the Fundraising_Admin permission set: `Database.queryWithBinds('SELECT Id FROM Account WITH USER_MODE', binds, AccessLevel.USER_MODE)` throws `System.SecurityException: Cannot use the WITH AccessLevel clause in dynamic queries that also specify an access level.` The AccessLevel argument is the documented way to run a dynamic query in user mode.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/selector/ContactsSelector.cls:228-~242 - newQueryFactory() (fflib defaults enforceCRUD=true) then queryWithBinds with AccessLevel.USER_MODE
 base/main/default/classes/donor/controller/DonorDetailController.cls:352 - requireDonor gate; empty result -&gt; QueryException
@@ -2771,6 +3571,12 @@
 base/main/default/classes/campaign/controller/FundraiserDetailController.cls:39 - getRecurring uses RecurringDonationsSelector.selectByCampaignPaged, not ContactsSelector</t>
         </is>
       </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2805,10 +3611,20 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the read returns only the Experience site's Id, name, URL prefix and status, org configuration rather than record data, and is reachable only from the administrator-only setup console; Network is a setup object, and a user-mode read of setup objects requires View Setup and Configuration, which the package's admin permission set cannot assume every administrator holds.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
           <t>This read resolves the Experience Cloud site that the administrator is configuring. It returns only the Network's Id, name, URL prefix and status, which are org configuration and not record data. It is reachable only from the package's setup console, whose controller is granted solely by the admin permission set. Network visibility in user mode is limited to sites the user is a member of, unless the user holds Create and Set Up Experiences, View All Data or Modify All Data. The admin must be able to resolve a site they are about to repoint the package at, including one still in Preview. The Id binds as a variable, and the query sits in a try/catch that reports "site not found" instead of exposing an error.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:269-277 - Database.query with AccessLevel.SYSTEM_MODE; bind variable, not concatenation
 base/main/default/classes/setup/service/CommunityService.cls:251-266 - resolveByNetworkId wraps it in try/catch and logs via AppLogger.info
@@ -2818,6 +3634,12 @@
 https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_network.htm - special access rules: users with Create and Set Up Experiences / View All Data / Modify All Data see all Network rows; others see only sites they are members of</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_network.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2852,10 +3674,20 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the read is a diagnostic over PermissionSetAssignment, a setup object with no sharing model, returning only a boolean and a remediation message to the administrator-only setup console; the guest user Id is resolved on the server, and a user-mode read would require View Setup and Configuration, which the package cannot grant.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
           <t>This is a read-only diagnostic in the admin setup console. It checks whether the site's guest user has been assigned the package's guest permission set and returns only a boolean and a remediation message. The guest user Id is resolved on the server from the selected site, not taken from the client. No record data is returned, and the read is wrapped in a try/catch that degrades to 'could not verify'. PermissionSetAssignment is a setup object whose visibility is governed by View Setup and Configuration rather than record sharing, which the package's admin permission set does not grant; the read stays in system mode so an administrator without it gets a true answer. The site carries its own SYSTEM_MODE comment stating this.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:325-331 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
 python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
@@ -2863,6 +3695,13 @@
 docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm
+https://developer.salesforce.com/blogs/2021/05/boost-security-by-auditing-your-privileged-users-with-soql</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2897,10 +3736,20 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the read checks the guest user's permission-set assignments for a standard-object grant the administrator must add by hand and returns only a boolean to the administrator-only setup console; the objects are setup objects with no sharing model, and a user-mode read would require View Setup and Configuration, which the package cannot grant.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
           <t>This read-only check verifies that the site guest user has read/create on User External Credential, a standard-object grant the admin must add by hand because a 2GP permission set cannot carry it. The method returns only a boolean for the setup console checklist. The guest user Id is derived on the server, the read never runs as or for a guest request, and failures degrade to a 'check manually' message. The reads are setup data governed by View Setup and Configuration, so they stay in system mode; each carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:566-583 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
 python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
@@ -2908,6 +3757,12 @@
 docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2942,10 +3797,20 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the read is over SetupEntityAccess, a setup object with no sharing model, returning only permission-set Ids used for an in-memory comparison in the administrator-only setup console; a user-mode read would require View Setup and Configuration, which the package's admin permission set cannot grant.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
           <t>This read-only check finds which permission sets grant access to the Stripe external credential's principal, so the setup console can tell the admin whether the guest user can make the payment callout. It returns only permission-set Ids used for an in-memory set intersection, never record data. SetupEntityAccess is a setup object whose visibility is governed by View Setup and Configuration, which the admin permission set does not grant, so the read stays in system mode. The inputs are resolved on the server, the call is reachable only from the admin-only setup controller, and the site carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:605-611 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
 python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
@@ -2953,6 +3818,12 @@
 docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_setupentityaccess.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2987,10 +3858,20 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the read counts ObjectPermissions rows on the guest user's permission sets and returns only a boolean to the administrator-only setup console; both are setup objects with no sharing model, and a user-mode read would require View Setup and Configuration, which the package's admin permission set cannot grant.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
           <t>This read-only check powers the setup console's 'guest user can read Campaign' step. It reads the guest user's permission-set assignments and counts ObjectPermissions rows granting Campaign read, returning only a boolean so the admin knows whether the documented manual grant is done (a managed package cannot ship that grant on a standard object). No record data leaves the method and the user Id is derived on the server. Both reads are setup data governed by View Setup and Configuration, which the admin permission set does not grant, so they stay in system mode; each carries its own SYSTEM_MODE comment.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:404-418 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
 python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
@@ -2998,6 +3879,12 @@
 docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.object_reference.meta/object_reference/sforce_api_objects_permissionsetassignment.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3032,16 +3919,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>The claim that this statement needs USER_MODE is false because it is a fixture write inside an @IsTest class: test code cannot be invoked by a user at runtime, and it must create its setup data regardless of which user the subscriber's org-wide test run executes as. It is also a DML statement, not a query, so the SOQL/SOSL rule does not apply to it.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
           <t>This line is in an @IsTest class (FundraiserAdminController_Test). It seeds the hierarchy custom setting org defaults as test setup before the code under test runs. Test classes cannot be invoked by users at runtime. The flagged statement is a DML fixture write, not a query, and the dataflow source is a picklist describe, not user input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (Customize Application, which user-mode DML on a custom setting requires). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/campaign/controller/FundraiserAdminController_Test.cls:1 - class annotated @isTest(SeeAllData=false)
 base/main/default/classes/campaign/controller/FundraiserAdminController_Test.cls:428-438 - setDefaultCampaignType fixture: reads the Campaign.Type picklist describe, then upserts org-default Settings__c as system to seed a test precondition
 The flagged line is a DML statement, not SOQL. The "source" is a schema describe. No user input is involved.</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3076,16 +3978,31 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture delete inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:906 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3120,16 +4037,31 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture write inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:261 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3164,16 +4096,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture write inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:578 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3208,16 +4155,31 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture write inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:610 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3252,16 +4214,31 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture write inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:641 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3296,16 +4273,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture write inside an @IsTest class, which no user can invoke at runtime, and must succeed under whatever user the subscriber's org-wide test run executes as; it is also DML, not a query, so the SOQL/SOSL rule does not apply.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
           <t>This is a fixture write inside an @IsTest class. It adjusts a test ticket-tier product (for example, sets it sold out or outside its sale window) to arrange the scenario for the service method under test. The class runs only in Apex test execution and is not reachable by any runtime user. The dataflow source is a schema record-type describe, not external input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/EventPurchaseService_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/event/service/EventPurchaseService_Test.cls:672 - fixture mutation of a test ticket tier (capacity, sold count, or window) before the method under test runs; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3340,16 +4332,31 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the statement is a fixture update inside an @IsTest class, which cannot run outside Apex test execution and must succeed under whatever user the subscriber's org-wide test run executes as; it is DML, not a query, so the SOQL/SOSL rule does not apply, and the reported dataflow source is a schema describe, not user input.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
           <t>This line is a test-fixture update inside an @IsTest class. It prepares a ticket product so the controller method under test sees a particular state. It cannot run outside Apex test execution. The dataflow source is a schema describe. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (edit access to Campaign, the master of the ticket-type object, which the platform ties to the Marketing User flag). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/fundraising/controller/EventRegistrationController_Test.cls:1 - class annotated @IsTest(SeeAllData=false)
 base/main/default/classes/shared/TestDataFactory.cls:743 - the dataflow source is the Product2 record-type describe in TestDataFactory.createTicketProduct (:741), a test fixture helper
 base/main/default/classes/fundraising/controller/EventRegistrationController_Test.cls:171 - fixture update of a test ticket product; DML, not SOQL</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_annotation_isTest.htm</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3384,10 +4391,20 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the row is an internal per-tax-year receipt counter holding only a year and the last number issued, not donor data; the FOR UPDATE lock keeps receipt numbers gapless, and the read must succeed from the guest finalize path and the renewal job, neither of whose running users can be granted the object.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
           <t>Receipt_Sequence__c is an internal per-tax-year counter row, not donor data. It holds only a year and the last receipt number issued. The query locks the counter (FOR UPDATE) so receipt numbers stay gapless and unique. Access must not depend on the running user, because a user without read access on the counter would otherwise break receipt numbering for their own gift. The only bind is a set of tax years derived from the Opportunity close date; no caller-supplied Id or filter reaches the query, and nothing from the counter row is returned to a UI.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/selector/ReceiptSequenceSelector.cls:60-65 - SYSTEM_MODE queryWithBinds, FOR UPDATE, bind is Set&lt;Decimal&gt; of tax years
 base/main/default/classes/donation/service/ReceiptNumberService.cls - lockCounters/assignWithoutUnitOfWork are the only callers; class is inherited sharing
@@ -3396,6 +4413,11 @@
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm - USER_MODE with no object access throws a QueryException rather than returning zero rows</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3430,16 +4452,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>USER_MODE is recommended for SOQL or SOSL operations</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the query reads only Id and CurrencyIsoCode for parent records whose Ids a trigger-driven rollup already holds, in order to convert amounts before writing the rollup total; the object name comes from the Id's schema token, not from input, and the read runs in trigger context as the DML writer, where a user without the parent's currency field would otherwise see the rollup silently fail.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
           <t>The query reads only Id and CurrencyIsoCode for parent records whose Ids the trigger-driven rollup already holds, so it can convert gift amounts into the parent's currency before writing the total. The object name comes from the Id's own schema token, not from input, so the dynamic FROM cannot be injected. The result is a map of Id to ISO code that is used in the arithmetic and never returned to a user. Running in user mode would make a rollup fail or mis-convert for a staff user who can save a gift but lacks read FLS on a standard CurrencyIsoCode field. The code catches any exception and falls back to the corporate currency.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/CurrencyResolver.cls:258-269 - dynamic FROM built from Id.getSObjectType().getDescribe().getName(); bind is Set&lt;Id&gt;; SYSTEM_MODE; catch returns empty map
 base/main/default/classes/shared/CurrencyResolver.cls - isoCodesByRecordId doc states the reason (currency code is not customer data)
 base/main/default/classes/donation/selector/OpportunitiesSelector.cls:189 - upstream SYSTEM_MODE rollup read, itself commented</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3474,16 +4511,31 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because `inherited sharing` is the documented mode for a class that is never an entry point: the selector takes the sharing of its caller, so a staff request is sharing-enforced and only the guest and job callers, which declare `without sharing` with a stated reason, bypass it.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
           <t>`inherited sharing` is intentional on this selector. It is never the entry point of a transaction, so its record visibility is that of the caller: staff controllers are `with sharing`, and the guest controllers and reconciliation jobs are `without sharing` for their own documented reasons. The Apex Developer Guide recommends `inherited sharing` for 'service classes that must be flexible and support use cases with different sharing modes'. Each query also sets an explicit AccessLevel, and each SYSTEM_MODE query carries its own reason at the call site.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/recurring/selector/RecurringDonationsSelector.cls:11 - declaration
 base/main/default/classes/shared/Application.cls - resolved via the Selector factory only
 grep: no entry-point annotation or async interface in the class</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3518,16 +4570,31 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because `inherited sharing` is the documented mode for a class that is never an entry point: the selector takes the sharing of its caller, so a staff request is sharing-enforced and only the guest and job callers, which declare `without sharing` with a stated reason, bypass it.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
           <t>`inherited sharing` is intentional on this selector. It is never the entry point of a transaction, so its record visibility is that of the caller: staff controllers are `with sharing`, and the guest controllers and reconciliation jobs are `without sharing` for their own documented reasons. The Apex Developer Guide recommends `inherited sharing` for 'service classes that must be flexible and support use cases with different sharing modes'. Each query also sets an explicit AccessLevel, and each SYSTEM_MODE query carries its own reason at the call site.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/recurring/selector/RecurringDesignationsSelector.cls:4 - declaration
 base/main/default/classes/shared/Application.cls - resolved via the Selector factory only
 grep: no entry-point annotation or async interface in the class</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3562,15 +4629,30 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class is never an entry point (`inherited sharing`, taking the mode of the admin settings controller that calls it) and it reads only setup entities, Named Credential, External Credential and permission-set assignments, which have no sharing model to enforce.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
           <t>This service grades the payment-credential setup for an administrator: Named Credential, External Credential grants and permission-set assignments. It reads setup entities that have no sharing model. It is only reached from the admin settings controller and is never a transaction entry point, so `inherited sharing` gives it the admin controller's `with sharing` mode.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/payment/service/PaymentSetupGuideService.cls:80-82 - rationale + declaration
 base/main/default/permissionsets/Fundraising_Admin.permissionset-meta.xml - SetupController (only set granting it)</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3605,16 +4687,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because `inherited sharing` is the documented mode for a class that is never an entry point: the selector takes the sharing of its caller, so a staff controller's request is sharing-enforced and only the guest and job paths, which declare `without sharing` with a stated reason, bypass it.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
           <t>`inherited sharing` is intentional on this selector. It is never the entry point of a transaction, so its record visibility is that of the caller: staff controllers are `with sharing`, and the guest controllers and reconciliation jobs are `without sharing` for their own documented reasons. The Apex Developer Guide recommends `inherited sharing` for 'service classes that must be flexible and support use cases with different sharing modes'. Each query also sets an explicit AccessLevel, and each SYSTEM_MODE query carries its own reason at the call site.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/selector/OpportunitiesSelector.cls:19 - declaration
 base/main/default/classes/shared/Application.cls - resolved via the Selector factory only
 grep: no entry-point annotation or async interface in the class</t>
         </is>
       </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3649,10 +4746,20 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because SimpleDML is declared `inherited sharing`, the documented mode for a non-entry-point class: a commit runs in the sharing mode of the class that called commitWork(), so a staff controller's commit is sharing-enforced by the platform and only callers that explicitly opt into the `SystemDML` subclass, each with a stated reason, bypass it.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
           <t>SimpleDML is the FFLib Unit of Work's default DML strategy. It is declared `inherited sharing`, so a commit follows the sharing mode of the class that called commitWork(). Every staff controller and service in the package is `with sharing`, so a staff commit runs with sharing and the platform enforces the running user's record access on the write. The writes that must bypass sharing (guest entry points, batch jobs, the platform-event subscriber and trigger-fired rollups) do not rely on this class: they construct their Unit of Work with SystemDML, a package-authored `without sharing` subclass, and each of the 24 construction sites states which of those families it belongs to. Object and field permissions are enforced one layer up, in the FFLib Selectors and by Security.stripInaccessible. SystemDML_Test proves, with a Minimum Access user, that a SimpleDML commit on a record the user is not shared is refused and a SystemDML commit succeeds.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:64 - `public virtual inherited sharing class fflib_SObjectUnitOfWork`, rationale at :54-61
 base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:165-191 - rationale and `public inherited sharing virtual class SimpleDML implements IDML, IDMLUpsertable`
@@ -3664,6 +4771,12 @@
 https://github.com/apex-enterprise-patterns/fflib-apex-common/issues/530 - upstream proposal for the same `inherited sharing` declarations</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://github.com/apex-enterprise-patterns/fflib-apex-common/issues/530</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3698,16 +4811,31 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because `inherited sharing` is the documented mode for a class that is never an entry point: the selector takes the sharing of its caller. Its reads are additionally gated on the master Campaign's visibility by the calling controller, because the object is a master-detail detail whose field permissions are inert.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
           <t>`inherited sharing` is intentional on this selector. It is never the entry point of a transaction, so its record visibility is that of the caller: staff controllers are `with sharing`, and the guest controllers and reconciliation jobs are `without sharing` for their own documented reasons. The Apex Developer Guide recommends `inherited sharing` for 'service classes that must be flexible and support use cases with different sharing modes'. Each query also sets an explicit AccessLevel, and each SYSTEM_MODE query carries its own reason at the call site.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/selector/EventTicketTypesSelector.cls:6 - declaration
 base/main/default/classes/shared/Application.cls - resolved via the Selector factory only
 grep: no entry-point annotation or async interface in the class</t>
         </is>
       </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3742,10 +4870,20 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the inner action class is `inherited sharing` (matching the GuestAction base it extends) and is invoked only from the public event-registration controller, where the Experience Cloud guest user holds no record sharing; the controller's `without sharing` carries its reason, and the action's reads are gated on an active, published campaign.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
           <t>The inner class extends GuestAction, which is `inherited sharing`, and declares the same keyword so its mode is readable at the declaration. Invoked from the `without sharing` guest controller, it runs without sharing. That is required: an Experience Cloud guest creates a ticket order against a Campaign it is not shared under sharing rules, and the Guest User licence holds no record sharing. Record visibility is decided by explicit predicates instead: requireOpenCampaign refuses the request unless the campaign is active, published and open for sales, and checkout is not blocked. GuestAction also collapses any unexpected error to one generic message, so nothing internal reaches the guest.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/fundraising/controller/EventRegistrationController.cls:194-196 - rationale and `private inherited sharing class CreateTicketIntent extends GuestAction`
 base/main/default/classes/fundraising/controller/EventRegistrationController.cls:9 - `public without sharing class EventRegistrationController`
@@ -3754,6 +4892,11 @@
 base/main/default/classes/shared/GuestAction.cls:30 - `public abstract inherited sharing class GuestAction extends ControllerAction`</t>
         </is>
       </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3788,15 +4931,30 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class is a stateless helper that is never a transaction entry point and reads only org email configuration; `inherited sharing` makes it run in the mode of the service that builds the message, which is the documented purpose of that keyword.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
           <t>This is a stateless helper that stamps the org's configured sender identity onto outbound donor email. It is never a transaction entry point, and it takes the sharing mode of the service that builds the message. It reads only org email configuration. The keyword was reviewed for a change to `with sharing` on 2026-10-01 and kept: the class is called from the guest donation path and from the platform-event subscriber as well as from staff actions, and `inherited sharing` is the declaration that lets each of those run in its caller's mode instead of forcing one mode on all of them.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/EmailSenderService.cls:1-10 - header + declaration
 grep: no entry-point annotation or async interface</t>
         </is>
       </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3831,16 +4989,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because DonationService is never a transaction entry point; `inherited sharing` makes it take the mode of its callers, the guest controllers (where visibility is decided by token or campaign predicates) and the reconciliation jobs, each of which declares its own keyword with its reason.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
           <t>DonationService is never an entry point. Its public methods are reached from the guest donation controllers, where visibility is decided by token or campaign predicates, and from the reconciliation jobs. Both of those callers establish `without sharing` and document why. When a `with sharing` staff controller calls it, it runs with sharing. That is the documented behavior of `inherited sharing` and the reason it is used here.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/DonationService.cls:7 - declaration
 base/main/default/classes/donation/async/StagingReconciliationBatch.cls:216 - finalizeSucceededStaging caller
 base/main/default/classes/donation/async/StripePaymentSweep.cls:166 - caller</t>
         </is>
       </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3875,16 +5048,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because `inherited sharing` is the mode Salesforce documents for non-entry-point classes and is accepted by its own false-positive guidance: the selector is never a transaction entry point, so it runs with the sharing of whichever controller or job called it, which is exactly the behaviour the rule asks for.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
           <t>`inherited sharing` is intentional on this selector. It is never the entry point of a transaction, so its record visibility is that of the caller: staff controllers are `with sharing`, and the guest controllers and reconciliation jobs are `without sharing` for their own documented reasons. The Apex Developer Guide recommends `inherited sharing` for 'service classes that must be flexible and support use cases with different sharing modes'. Each query also sets an explicit AccessLevel, and each SYSTEM_MODE query carries its own reason at the call site.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/selector/DonationDesignationsSelector.cls:8 - declaration
 base/main/default/classes/shared/Application.cls - resolved via the Selector factory only
 grep: no entry-point annotation or async interface in the class</t>
         </is>
       </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3919,15 +5107,30 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the helper is never a transaction entry point; `inherited sharing` makes it run in the mode of the controller or trigger that called it, which is the documented purpose of that keyword.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
           <t>This helper resolves the currency for a campaign or payment account. It is never a transaction entry point and runs in whatever sharing mode its calling controller established, which is the purpose of `inherited sharing`.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/CurrencyResolver.cls:8 - declaration
 grep: no entry-point annotation or async interface</t>
         </is>
       </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3962,15 +5165,30 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class has no @AuraEnabled, REST or asynchronous surface of its own, so it is not an entry point; `inherited sharing` makes it run in its caller's mode, which is the documented purpose of that keyword.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
           <t>This is a service, never a transaction entry point. It takes the sharing mode of the controller or job that calls it, which is what `inherited sharing` is documented for. It has no @AuraEnabled, REST, or async surface of its own.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/CampaignMemberSyncService.cls:9 - declaration
 grep: no entry-point annotation or async interface</t>
         </is>
       </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4005,10 +5223,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because SystemDML is a deliberately narrow wrapper, not an entry point: it is the package's explicit, per-site opt-in for commits where the running user is by design not the authority over the records (guest entry points, batch and queueable jobs, trigger-fired rollups), each opt-in carrying its reason in code; staff commits use the user-mode strategy instead. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
           <t>SystemDML is the package's explicit opt-in for writes where the running user is, by design, not the authority over the records: Experience Cloud guest entry points (the Guest User licence holds no record sharing), batch and queueable jobs that must write every donor's records whoever scheduled them, the platform-event subscriber that runs as Automated Process, and trigger-fired rollups written for whoever saved the gift. The default Unit of Work strategy follows its caller's sharing; this class is used only where a site asks for it, and each of the 24 construction sites carries a `// SystemDML: guest|job|rollup` comment naming its family. The class contains nothing but four DML statements. Object and field permissions are enforced one layer up, in the FFLib Selectors and by Security.stripInaccessible. SystemDML_Test proves the difference with a Minimum Access user.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/SystemDML.cls:1-30 - class description, family list and `public without sharing class SystemDML extends fflib_SObjectUnitOfWork.SimpleDML`
 grep: `new SystemDML()` at 24 production sites, each preceded by a `// SystemDML: guest|job|rollup` comment; none in a staff controller
@@ -4016,6 +5244,11 @@
 base/main/default/classes/shared/SystemDML_Test.cls:60 - SystemDML commit on the same record succeeds</t>
         </is>
       </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4050,15 +5283,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is batch Apex, which the scan's own rule exempts; the sweep compares the gateway ledger to every staging row and Opportunity in the org and takes no user input (the admin 'run now' button starts the same batch with no parameters).</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
           <t>The sweep compares Stripe's payment ledger to the org's staging rows and Opportunities, and repairs gaps. That only works if it sees every row. It takes no input from users: the admin 'run now' button starts the same batch with no parameters.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/StripePaymentSweep.cls:26 - declaration
 base/main/default/classes/setup/controller/SetupController.cls:2142 - admin-only executeBatch, no parameters</t>
         </is>
       </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4093,10 +5342,20 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is batch Apex, which the scan's own rule exempts; it must finalize staging rows created by the site guest user that no job owner is shared on. The single staff 'Retry now' entry point takes only a row Id and re-reads the charge from the gateway, so no caller-controlled data is written.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
           <t>The batch has to finalize donation staging rows created by the site guest user, and those rows are not owned by whoever runs the job. The one non-batch entry point is a single-row 'Retry now' action for staff. It re-reads the charge from Stripe and applies the same idempotent outcome logic as the batch. Donation_Staging__c ships with a Public Read/Write internal sharing model, so `without sharing` gives internal staff no visibility they do not already have.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/StagingReconciliationBatch.cls:134-148 - reconcileOne: selectById (SYSTEM_MODE) then Stripe retrieve then applyOutcome
 base/main/default/classes/donation/controller/DonationMonitorController.cls:196-212 - RetryDonationStagingNow calls reconcileOne(stagingId); only requireNotNull
@@ -4104,6 +5363,12 @@
 base/main/default/permissionsets/Fundraising_User.permissionset-meta.xml - Donation_Staging__c allowRead=true, allowEdit=false</t>
         </is>
       </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4138,16 +5403,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is a private inner helper, not an entry point, that runs only during install as the package's system user to copy the package's own static-resource images into public content distributions; that user cannot read StaticResource under sharing, and the helper never touches subscriber or donor data. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
           <t>This private helper copies the package's own static-resource images into public content distributions during install, so the default logo and hero images exist. The install user cannot read StaticResource under sharing. The helper never touches admin- or donor-supplied files, which go through the user-mode upload path. The elevation covers two short methods and nothing else.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/SettingsService.cls:529-543 - rationale
 base/main/default/classes/setup/service/SettingsService.cls:547-552 - StaticResource read by packaged name only
 base/main/default/classes/setup/service/SettingsService.cls:378,141 - only instantiation sites</t>
         </is>
       </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4182,15 +5462,31 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is batch Apex, which the scan's own rule exempts; it enforces the configured retention policy by deleting expired diagnostic and staging rows, and a row hidden from the job owner by sharing would otherwise never be purged. It has no entry point besides its scheduler. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
           <t>This batch enforces the configured data-retention policy by deleting expired diagnostic and staging rows. A row hidden from the job's running user by sharing would never be purged, which would defeat the policy. The batch has no entry point other than its scheduler and takes no user input.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/async/RetentionPurgeBatch.cls:16 - declaration
 base/main/default/classes/shared/async/RetentionPurgeScheduler.cls:29-33 - sole enqueuer</t>
         </is>
       </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4225,15 +5521,31 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the scan's own rule exempts batch and asynchronous Apex: this is a Batchable with no other entry point, and reconciling gateway refunds against every donation would silently skip records hidden from the job owner if it ran with sharing. Its reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
           <t>This is a batch with no public surface beyond the Batchable interface. It reconciles refunds recorded in Stripe against every donation in the org. If it ran with the sharing of the job owner, refunds on records that user cannot see would be silently skipped. No caller can pass it record Ids.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/RefundReconciliationBatch.cls:44 - declaration
 base/main/default/classes/donation/async/RefundReconciliationScheduler.cls:39 - sole enqueuer</t>
         </is>
       </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4268,16 +5580,32 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>The claim that this entry point should run with sharing is false because the scan's own rule says batch and asynchronous Apex should not; this is a Schedulable whose only job is to count every stuck staging row in the org, a count that would silently under-report under the sharing of whichever user scheduled it. Its reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
           <t>This is a Schedulable with no other entry point. It counts every non-terminal donation staging row in the org and alerts when any is stuck. A sharing-restricted count would depend on who owns the scheduled job, and would under-report. Its only writes are a Transaction_Log__c row and the alert, and nothing is returned to a user.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/async/ReconciliationHeartbeat.cls:11 - declaration + rationale
 base/main/default/classes/setup/controller/PostInstallHandler.cls:495 - scheduled at install
 base/main/default/classes/setup/controller/SetupController.cls:2231 - admin re-schedule (SetupController granted to Fundraising_Admin only)</t>
         </is>
       </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4312,16 +5640,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class is not an entry point and its only work is creating and reading the package's own event price book and its entries, standard objects a 2GP permission set cannot grant, during install (system user), admin ticket-tier saves and guest ticket purchases; none of those running users can hold sharing on Pricebook2. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
           <t>PricebookService only creates and looks up the package's event price book and its PricebookEntry rows for ticket products. It runs during install, when an admin saves ticket tiers, and during a guest ticket purchase. None of those contexts can rely on the running user's price-book sharing. It handles no donor data, and it only receives Product2 Ids that its callers have read from records they already gated. `with sharing` is not an option here: in the package install context a `with sharing` class cannot resolve the standard price book, which made the install-time seed fail when it was tried (2026-08-09).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/event/service/PricebookService.cls:25 - declaration
 base/main/default/classes/event/controller/EventTicketAdminController.cls:156-176,197-263 - requireCampaignWritable gates; product Id derived from the saved tier
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1544,1588 - install callers</t>
         </is>
       </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4356,10 +5699,20 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because an InstallHandler is not a user entry point: it runs once, as a package-specific system user with no permission set, to seed org-wide configuration that must exist regardless of who installed the package. Salesforce's own false-positive guidance accepts install context, and the reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
           <t>This is the package InstallHandler. It seeds settings, themes, record-type mappings, the event price book and content templates, and schedules the package's background jobs. That data is org-wide configuration, which must be created regardless of the install user's sharing. Its public helpers are also re-run from the admin-only Settings console to repair a missing seed or a job owned by a deactivated user. They take no record Ids and are idempotent.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:1-4 - rationale
 base/main/default/classes/setup/controller/SetupController.cls:834-847 - admin Fix button calls scheduleJobs(true)/seedRecordTypeMappings
@@ -4367,6 +5720,11 @@
 base/main/default/permissionsets/Fundraising_Admin.permissionset-meta.xml - SetupController granted only here</t>
         </is>
       </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4401,10 +5759,20 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class is not an entry point: it runs only from the platform-event subscriber (the Automated Process user) and the reconciliation jobs, both asynchronous contexts the scan's own rule exempts, and it writes NPSP objects the package cannot grant any user permissions on. Its reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
           <t>This service mirrors finalized donations into the optional NPSP objects (allocations and recurring donations). It runs from system contexts: the finalization platform-event subscriber and the reconciliation jobs that finalize donations. The records it writes belong to another package, and this package's permission sets cannot grant access to them. It never takes a record Id from a user: every Id comes from a donation or schedule the same transaction just finalized. NPSP rejections are logged and swallowed, so they cannot roll back a captured payment.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/NpspSyncService.cls:1-14 - header + declaration
 base/main/default/classes/donation/service/DonationFinalizedSubscriberHandler.cls:23-24 - syncAllocations caller
@@ -4413,6 +5781,12 @@
 No PlatformEventSubscriberConfig in base/ - the subscriber runs as the default Automated Process user</t>
         </is>
       </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.platform_events.meta/platform_events/platform_events_trigger_config.htm</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4447,10 +5821,20 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the service is reached only after the donor portal has authorized the donor by a verified access code, or from the background sweep, and the guest user holds no sharing on the request object; the staff methods it serves filter their rows through user-mode reads. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
           <t>This service queues and processes public requests (attendee naming, refund requests) submitted from the donor portal. It is only reached after the portal has authorized the donor, and by the background sweep. The staff methods it also serves read and close requests for a gift. They are gated by the Process_Refunds custom permission, and Guest_Request__c ships with a Public Read/Write internal sharing model, so running `without sharing` gives staff no visibility they would not already have.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/guestrequest/service/GuestRequestService.cls:8-13 - rationale
 base/main/default/classes/donation/controller/RefundController.cls:95-105 - staff caller gated by Process_Refunds
@@ -4458,6 +5842,11 @@
 base/main/default/classes/donor/service/DonorPortalService.cls:1286,1269 - submit callers</t>
         </is>
       </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4492,10 +5881,20 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is a guest-facing Experience Cloud controller: the guest user has no sharing that could expose an event campaign, so `with sharing` would make the public page empty. Reads are gated on an active, published campaign resolved by slug or Id, the single write is a staging row, and the reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
           <t>This is the public event-registration controller for an Experience Cloud site, and the guest user has no sharing that would expose an event campaign. Every method is narrow. Reads are gated on an active, published campaign resolved by slug or Id. The write is gated on the event being open for sales. The two status methods require the unguessable access token issued at checkout. Errors are sanitized through GuestAction. Staff hold the same class grant, but reach nothing beyond what an anonymous visitor can.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/fundraising/controller/EventRegistrationController.cls:25-112 - the five @AuraEnabled methods
 base/main/default/classes/fundraising/controller/EventRegistrationController.cls:856-879 - requireActiveCampaign/requireOpenCampaign
@@ -4503,6 +5902,11 @@
 base/main/default/permissionsets/Fundraising_GuestDonor.permissionset-meta.xml:36 - guest grant</t>
         </is>
       </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4537,16 +5941,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class serves an Experience Cloud guest user, who holds no record sharing on Contact, Account or the access-code object, so `with sharing` would return nothing; every guest method is instead authorized by possession of a verified access code, and the staff twins re-read their records in user mode. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
           <t>The class is `without sharing` so the Experience Cloud guest user, which has no sharing on Contact, Account or Portal_Access_Token__c, can resolve a donor from an access code and mint a portal session; every guest method is authorized by possession of the code or session it produces and trusts no client-supplied record Id. The class also holds two staff methods, issueAccessCodeForDonor and createAccessCodeForDonor, which take a record Id from a Lightning component. Both staff methods re-read the donor in the staff user's mode (USER_MODE selectors, resolveStaffDonorEmail) and refuse a donor the user cannot see before anything is minted or returned, and the class header states that its `without sharing` must not become a way to reach records outside the caller's access.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:38-47 - header rationale for `without sharing` and the staff-twin exception; :48 declaration
 base/main/default/classes/donor/controller/DonorPortalAdminController.cls:156 / :175 - USER_MODE reads of the Contact / Person Account before the service is called
 docs/security/appexchange-security-review-readiness.md F-10; FP-3 sharing census</t>
         </is>
       </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4581,16 +6000,31 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the service is reachable only from the administrator-only settings console, and the one record-shared object it reads is User, where a Private user-sharing model can hide the site's guest user from the administrator and turn every guest-setup check into a false failure; all other reads are setup objects with no sharing model. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
           <t>CommunityService backs the admin Settings console's Experience Cloud panel. The one record-shared object it reads is User: it looks up the site's guest user, which a Private User sharing model can hide from the admin, turning every guest check into a false "no guest user". Its other reads (Network, BackgroundOperation, PermissionSetAssignment, ObjectPermissions and SetupEntityAccess) are setup objects with no record sharing, and each carries its own SYSTEM_MODE reason. The only caller is the admin-only settings controller. It returns status flags and names only.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:6-13 - rationale
 base/main/default/classes/setup/controller/SetupController.cls:44-45 - communityServiceInstance, the only reference (e.g. :2811)
 grep: CommunityService referenced only by SetupController, Application and TestDataFactory among non-test classes (others are comments)</t>
         </is>
       </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4625,16 +6059,32 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the handler runs asynchronously from the request queue, a context the scan's own rule exempts, where no sharing relationship to the donor's order exists; the authorization (verified portal access code plus ownership of the order) was performed synchronously before the request was queued. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
           <t>This handler fills in guest names on the seats of one ticket order, for a request the donor submitted through the portal. It runs asynchronously from the request queue, where no sharing relationship to the donor's order exists. The authorization was performed when the request was accepted (portal session or code, then the order Id recorded server-side). The payload is size-capped and parsed defensively.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/guestrequest/handler/AttendeeNamingHandler.cls:10-14 - rationale
 base/main/default/classes/guestrequest/handler/GuestRequestRouter.cls:28 - sole constructor site
 base/main/default/classes/guestrequest/handler/AttendeeNamingHandler.cls:19 - MAX_SEATS cap on untrusted payload</t>
         </is>
       </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_scheduler.htm</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4669,15 +6119,30 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
+          <t>All entry points to an app (Global or Controller classes) must use the 'with sharing' keyword. Classes without this keyword run without sharing if they are entry points to your code, or with the sharing policy of the caller. Do not omit the sharing declaration as this hides critical security information in side-effects that can change when code is refactored. Only declare classes as 'without sharing' if they are not entry points to your app and if they only modify objects whose security is managed by your code (such as wizard state, or fields in a site). It is a common misconception to believe that batch apex or async apex must run with the global keyword. This is not true, the only classes that must be global are those that expose webservices or are intended to be used by extension packages. All async apex should run as public in order to avoid creating privileged entry points to your app.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the class only inserts diagnostic rows, performs no queries and returns no records, so sharing could not expose any data through it; it must succeed from every context, including a guest user and a failure caused by sharing itself, or the error being logged would be lost. The reason is stated at the declaration.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
           <t>AppLogger only inserts diagnostic Log__c rows. It performs no queries and returns no records, so there is no data a caller could read through it. It must succeed from any context, including the guest user and failures caused by sharing, or the error being logged is lost. Log__c is read-only to staff and not granted to the guest user.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/shared/AppLogger.cls:1-9 - rationale
 base/main/default/classes/shared/AppLogger.cls:125 - the only DML: insert as system Log__c</t>
         </is>
       </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4712,10 +6177,20 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
+          <t>Static resources must be used load third-party javascript code</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>The claim that the script resource is dynamic is false because the src is a literal https://js.stripe.com/v3/ string with no merge field, parameter or stored value contributing to it; and the rule's remedy (a static resource) is prohibited for this library, because Stripe requires Stripe.js to be loaded from js.stripe.com for PCI compliance and does not permit self-hosting.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
           <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL; no merge field, parameter or stored value contributes to the src, so it is not a dynamically constructed resource. Stripe's documentation requires Stripe.js to be loaded directly from https://js.stripe.com and not bundled or self-hosted, so it cannot be moved into a static resource; js.stripe.com is shipped as a packaged CSP Trusted Site. The page exists precisely to keep Stripe.js out of the LWC runtime: the LWC frames this Visualforce page by relative URL and talks to it by postMessage, Stripe Elements tokenizes card data in Stripe's own nested iframe, and only a payment-method id is returned to Apex. The page has no Apex controller and renders no server value into its script: the postMessage peer is the page's own origin (window.location.origin), and inbound messages are accepted only from that origin and from window.parent. Moving the script into a static resource was reviewed again on 2026-10-01 and is not permitted: Stripe's integration guidance states that Stripe.js must always be loaded directly from js.stripe.com and must not be included in a bundle or self-hosted, as a condition of PCI compliance.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>base/main/default/pages/stripePayment.page:48-53 - justification comment + static script tag
 base/main/default/pages/stripePayment.page:1-7 - &lt;apex:page&gt; declares no controller; the page contains no {!...} merge field
@@ -4729,6 +6204,14 @@
 base/main/default/cspTrustedSites/ - also Stripe_api (api.stripe.com), Stripe_hooks (hooks.stripe.com), Stripe_m, Stripe_m_network; no *.js.stripe.com entry (Stripe lists it as optional, for performance)</t>
         </is>
       </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/js/including
+https://docs.stripe.com/security/guide
+https://docs.stripe.com/sdks/stripejs-versioning
+https://stripe.com/guides/pci-compliance</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4763,10 +6246,20 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
+          <t>Static resources must be used load third-party javascript code</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>The claim that the script resource is dynamic is false because the src is a literal https://js.stripe.com/v3/ string with nothing dynamic contributing to it; and Stripe requires Stripe.js to be loaded from js.stripe.com rather than bundled as a static resource, so the rule's remedy is not available for this library.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
           <t>This is a static &lt;script&gt; tag with a literal https://js.stripe.com URL, the second of the two Stripe.js loads in the package; nothing dynamic contributes to the src. Stripe redirects the donor here after an off-site authentication step (3D Secure, bank redirect), and the page needs Stripe.js to call retrievePaymentIntent/retrieveSetupIntent; Stripe's documentation requires Stripe.js to be loaded from js.stripe.com rather than self-hosted, which is why it is not a static resource. URL parameters read by the page (pk and the Stripe intent client secret) are passed only to Stripe.js calls, and status text is written with textContent. The page has no Apex controller. Its only server-rendered value is the 'Return to the site' link, whose href is the org's saved Experience site URL read through a $Setup merge field, rendered only when it begins with https://, and never taken from the query string. Moving the script into a static resource was reviewed again on 2026-10-01 and is not permitted: Stripe's integration guidance states that Stripe.js must always be loaded directly from js.stripe.com and must not be included in a bundle or self-hosted, as a condition of PCI compliance.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>base/main/default/pages/stripePaymentReturn.page:35-40 - justification comment + static script tag
 base/main/default/pages/stripePaymentReturn.page:1-7 - &lt;apex:page&gt; declares no controller
@@ -4780,9 +6273,17 @@
 base/main/default/cspTrustedSites/ - also Stripe_api (api.stripe.com), Stripe_hooks (hooks.stripe.com), Stripe_m, Stripe_m_network; no *.js.stripe.com entry (Stripe lists it as optional, for performance)</t>
         </is>
       </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/js/including
+https://docs.stripe.com/security/guide
+https://docs.stripe.com/sdks/stripejs-versioning
+https://stripe.com/guides/pci-compliance</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H96"/>
+  <autoFilter ref="A1:K96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14714,7 +16215,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>222397f2</t>
+          <t>ae49fada</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -17332,17 +17332,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17372,17 +17372,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17412,17 +17412,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17452,17 +17452,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17532,17 +17532,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17572,17 +17572,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17612,17 +17612,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17652,17 +17652,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17692,17 +17692,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17732,17 +17732,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17772,17 +17772,17 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17812,17 +17812,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17852,17 +17852,17 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17892,17 +17892,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17932,17 +17932,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -17972,17 +17972,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18012,17 +18012,17 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18052,17 +18052,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18092,17 +18092,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18132,17 +18132,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18172,17 +18172,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18212,17 +18212,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18252,17 +18252,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18292,17 +18292,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18332,17 +18332,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18372,17 +18372,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18412,17 +18412,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18452,17 +18452,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18492,17 +18492,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18532,17 +18532,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18572,17 +18572,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18612,17 +18612,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18652,17 +18652,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18692,17 +18692,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18732,17 +18732,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18772,17 +18772,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18812,17 +18812,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18852,17 +18852,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18892,17 +18892,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18932,17 +18932,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -18972,17 +18972,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19012,17 +19012,17 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19052,17 +19052,17 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19092,17 +19092,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19132,17 +19132,17 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19172,17 +19172,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19212,17 +19212,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19252,17 +19252,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19292,17 +19292,17 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19332,17 +19332,17 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19372,17 +19372,17 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19412,17 +19412,17 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19452,17 +19452,17 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19492,17 +19492,17 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19532,17 +19532,17 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19572,17 +19572,17 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19612,17 +19612,17 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19652,17 +19652,17 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19692,17 +19692,17 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19732,17 +19732,17 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19772,17 +19772,17 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19812,17 +19812,17 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19852,17 +19852,17 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19892,17 +19892,17 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19932,17 +19932,17 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -19972,17 +19972,17 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20012,17 +20012,17 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20052,17 +20052,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20092,17 +20092,17 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20132,17 +20132,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20172,17 +20172,17 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20212,17 +20212,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20252,17 +20252,17 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20292,17 +20292,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20332,17 +20332,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20372,17 +20372,17 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20412,17 +20412,17 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20452,17 +20452,17 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20492,17 +20492,17 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20532,17 +20532,17 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -20572,17 +20572,17 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Vendored FFLib test — upstream library code</t>
+          <t>Vendored FFLib test — real assertion added since the scan</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Third-party code — not changed</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one; the package's local patches to FFLib are recorded in its dependency log. 72 of them test the mocking library's verification: fflib_ApexMocks.verify() throws fflib_ApexMocks.ApexMocksException when the expected interaction did not happen, so the test fails if the behaviour is wrong. 3 register a mock answer class whose body holds the System.Assert calls on the argument handling under test. The other 7 check that a call completes without an exception: the Unit of Work's object-type guards, system-mode selector queries run as a minimum-access user, the default domain validation hook, describe caching and an access check run as an administrator; an unexpected exception fails them. Rewriting upstream tests would fork the library without adding assurance about package behaviour, which the package's own tests cover.</t>
+          <t>These methods are the open-source FFLib libraries' own tests (fflib-apex-mocks, fflib-apex-common, BSD-3-Clause), vendored into the package because a managed package cannot depend on an unlocked one. Each now carries System.Assert calls in its own body. The 72 mock-verification tests keep their passing verification and then run the next-stricter one (one more call than was made, a lower bound one above the real count, or a call the in-order verifier has already passed) and assert that it throws fflib_ApexMocks.ApexMocksException with the library's exact expected/actual count message, which proves the passing check counted the real calls. The 3 answer tests assert on the invocation the answer received (method signature, argument count and values) and on the stubbed return value. The other 7 assert the outcome directly: the field-set map equals the platform describe, the system-mode selector queries carry WITH SYSTEM_MODE and return no rows for an unused Id as a minimum-access user, the default domain hook records no errors and raises no validation exception on update, and the Unit of Work type guards and an administrator's access checks raise no exception. The changes are test-only and recorded in the package's dependency log.</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>d495ca14</t>
+          <t>9d0e746b</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>classes/shared/TestDataFactory.cls:687</t>
+          <t>classes/shared/TestDataFactory.cls:722 (corrected since scan)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>insert as system cd;</t>
+          <t>insert as user cd;</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1394,18 +1394,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because TestDataFactory is an @IsTest class that production code cannot invoke; the statement seeds a sample ContentDistribution fixture for unit tests and must succeed under whatever user the subscriber's org-wide test run executes as, so user mode would make the package's tests fail in an org whose test runner lacks the grant.</t>
+          <t>The finding no longer applies: the ContentDistribution insert and read now run in user mode.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
+          <t>Changed after the scan from `insert as system` to `insert as user`, and the read-back of the new row from `WITH SYSTEM_MODE` to `WITH USER_MODE`. The test fixture now creates and reads the ContentDistribution in user mode.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/shared/TestDataFactory.cls:1-4 - @IsTest, `without sharing` with rationale
-base/main/default/classes/shared/TestDataFactory.cls:669-694 - seedOrgLogoOnSettings fixture</t>
+          <t>classes/shared/TestDataFactory.cls:710-729 - seedOrgLogoOnSettings</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1422,7 +1421,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1437,12 +1436,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>classes/shared/TestDataFactory.cls:693</t>
+          <t>classes/shared/TestDataFactory.cls:728 (corrected since scan)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>upsert as system settings;</t>
+          <t>upsert as user settings;</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1452,18 +1451,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because TestDataFactory is an @IsTest class that production code cannot invoke; the statement seeds a Settings__c fixture row for unit tests and must succeed under whatever user the subscriber's org-wide test run executes as (custom-setting DML in user mode would require Customize Application).</t>
+          <t>The finding no longer applies: the DML now runs in user mode.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>TestDataFactory is an @IsTest class; seedOrgLogoOnSettings builds fixture data (a sample ContentDistribution and a Settings__c row) for unit tests and cannot be invoked from production code. System mode is used so fixtures can be created regardless of the runAs user under test. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (content-delivery rights for ContentDistribution, or Customize Application for the custom setting row). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
+          <t>Changed after the scan from `upsert as system` to `upsert as user`. The settings row that records the ContentDistribution URL is now written in user mode.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/shared/TestDataFactory.cls:1-4 - @IsTest, `without sharing` with rationale
-base/main/default/classes/shared/TestDataFactory.cls:669-694 - seedOrgLogoOnSettings fixture</t>
+          <t>classes/shared/TestDataFactory.cls:710-729 - seedOrgLogoOnSettings</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3895,7 +3893,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3910,12 +3908,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>classes/campaign/controller/FundraiserAdminController_Test.cls:438</t>
+          <t>classes/campaign/controller/FundraiserAdminController_Test.cls:438 (corrected since scan)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>upsert as system s;</t>
+          <t>upsert as user s;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3925,19 +3923,17 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>The claim that this statement needs USER_MODE is false because it is a fixture write inside an @IsTest class: test code cannot be invoked by a user at runtime, and it must create its setup data regardless of which user the subscriber's org-wide test run executes as. It is also a DML statement, not a query, so the SOQL/SOSL rule does not apply to it.</t>
+          <t>The finding no longer applies: the DML now runs in user mode.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>This line is in an @IsTest class (FundraiserAdminController_Test). It seeds the hierarchy custom setting org defaults as test setup before the code under test runs. Test classes cannot be invoked by users at runtime. The flagged statement is a DML fixture write, not a query, and the dataflow source is a picklist describe, not user input. The statement stays in system mode on purpose: the package's tests are also run in subscriber orgs (an org-wide test run there includes managed-package tests), where the running user may lack a permission the fixture would need in user mode (Customize Application, which user-mode DML on a custom setting requires). A user-mode fixture would fail the subscriber's test run for a reason unrelated to the behaviour under test, while protecting nothing, because a test class has no runtime caller.</t>
+          <t>Changed after the scan from `upsert as system` to `upsert as user`. The test fixture now writes the settings row in user mode.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/campaign/controller/FundraiserAdminController_Test.cls:1 - class annotated @isTest(SeeAllData=false)
-base/main/default/classes/campaign/controller/FundraiserAdminController_Test.cls:428-438 - setDefaultCampaignType fixture: reads the Campaign.Type picklist describe, then upserts org-default Settings__c as system to seed a test precondition
-The flagged line is a DML statement, not SOQL. The "source" is a schema describe. No user input is involved.</t>
+          <t>classes/campaign/controller/FundraiserAdminController_Test.cls:435-439 - setDefaultCampaignType</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4605,7 +4601,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4620,12 +4616,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>classes/payment/service/PaymentSetupGuideService.cls:82</t>
+          <t>classes/payment/service/PaymentSetupGuideService.cls:83 (corrected since scan)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>public virtual inherited sharing class PaymentSetupGuideService implements IPaymentSetupGuideService {</t>
+          <t>public virtual with sharing class PaymentSetupGuideService implements IPaymentSetupGuideService {</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4635,18 +4631,18 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because the class is never an entry point (`inherited sharing`, taking the mode of the admin settings controller that calls it) and it reads only setup entities, Named Credential, External Credential and permission-set assignments, which have no sharing model to enforce.</t>
+          <t>The finding no longer applies: the class now declares `with sharing`.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>This service grades the payment-credential setup for an administrator: Named Credential, External Credential grants and permission-set assignments. It reads setup entities that have no sharing model. It is only reached from the admin settings controller and is never a transaction entry point, so `inherited sharing` gives it the admin controller's `with sharing` mode.</t>
+          <t>Changed after the scan from `inherited sharing` to `with sharing`. The class has one caller, `SetupController`, which is `with sharing`, so the mode it runs in is unchanged and the declaration now states it explicitly.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/payment/service/PaymentSetupGuideService.cls:80-82 - rationale + declaration
-base/main/default/permissionsets/Fundraising_Admin.permissionset-meta.xml - SetupController (only set granting it)</t>
+          <t>classes/payment/service/PaymentSetupGuideService.cls:80-83 - rationale + declaration
+classes/setup/controller/SetupController.cls - the only caller (with sharing)</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -7390,7 +7386,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7421,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14526,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15086,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26659,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9d0e746b</t>
+          <t>9279d2db</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -15768,7 +15768,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
         </is>
       </c>
     </row>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16808,7 +16808,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17848,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18208,7 +18208,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18368,7 +18368,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18798,17 +18798,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Loop removed since scan</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>By design</t>
+          <t>Fixed since scan</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>DonationService.publishErrorText no longer loops over the event bus's errors. A one-event publish returns one error in practice, so it now quotes the first error's status code and message and counts any others; no value built in a loop reaches the AppLogger insert.</t>
         </is>
       </c>
     </row>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19248,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19408,7 +19408,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices; in one path (DonationService.publishErrorText) the loop only joins the event bus's error messages into one string, which a single AppLogger.error call then records. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>073ee3bd</t>
+          <t>db425b78</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$K$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All paths'!$A$1:$G$274</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Quality'!$A$1:$H$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Quality'!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,100 +518,40 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 1; Apex SOQL SOSL USER MODE MISSING: 9</t>
+          <t>Apex CRUD Violation: 1, 9, 14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>classes/CommunityService.cls:513</t>
+          <t>classes/PaymentSetupGuideService.cls:1918</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>classes/setup/service/CommunityService.cls:513</t>
+          <t>classes/payment/service/PaymentSetupGuideService.cls:1918</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Integer assignedCount = [</t>
+          <t>if (m.find()) {</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.
-USER_MODE is recommended for SOQL or SOSL operations</t>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because the statement is a read-only COUNT() of PermissionSetAssignment, a setup object with no sharing model, returning a yes/no verdict and no record data; it is reachable only from the administrator-only setup console, and a user-mode read of setup objects requires View Setup and Configuration, which the package's admin permission set cannot assume every administrator holds.</t>
+          <t>The claim is false because the flagged line is a regular-expression match on a string already in memory, not a query or DML statement, so no CRUD operation exists to check; the string was read with WITH USER_MODE, so the running administrator's permissions were already enforced.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>This is a read-only count of the site guest user's permission-set assignments, run from the administrator-only setup console to report whether the payment credential is granted to that guest user; it returns a yes/no verdict and no record data. It runs in system mode because PermissionSetAssignment is setup data that the running administrator can read only with 'View Setup and Configuration', which the package's admin permission set does not grant, and without it the console would falsely report the grant as missing. Only users holding the administrator permission set can reach it. The site carries its own SYSTEM_MODE comment saying so, as does every other setup-object read in the class.</t>
+          <t>The flagged line is a regular-expression match on a string already in memory; it is not a query or DML statement. The data it examines was read with WITH USER_MODE, so the running administrator's object and field permissions were already enforced, and only credential and parameter names are retained for a setup checklist. The path is reachable only by the administrator permission set; the fake-Id generator source is test-only and the other is the SOQL builder.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/classes/setup/service/CommunityService.cls:511-516 - `// SYSTEM_MODE: the guest user's assignments ... a count only, for the Fundraising_Admin-only Settings console.` above the query
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites (header-only count now excludes this file's reads)
-SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no ViewSetup userPermission</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>R-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 2, 7, 15</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>classes/PaymentSetupGuideService.cls:1918</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>classes/payment/service/PaymentSetupGuideService.cls:1918</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>if (m.find()) {</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>The claim is false because the flagged line is a regular-expression match on a string already in memory, not a query or DML statement, so no CRUD operation exists to check; the string was read with WITH USER_MODE, so the running administrator's permissions were already enforced.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>The flagged line is a regular-expression match on a string already in memory; it is not a query or DML statement. The data it examines was read with WITH USER_MODE, so the running administrator's object and field permissions were already enforced, and only credential and parameter names are retained for a setup checklist. The path is reachable only by the administrator permission set; the fake-Id generator source is test-only and the other is the SOQL builder.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/payment/service/PaymentSetupGuideService.cls:1917 Matcher m = MERGE_FORMULA.matcher(...); if (m.find())
 queryNamedCredentials (:1583) and queryCustomHeaders (:1607) WITH USER_MODE
@@ -620,9 +560,70 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>R-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 2, 18</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>classes/ReceiptService.cls:518</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>classes/donation/service/ReceiptService.cls:518</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because this is an internal alert from a scheduled job using explicit addresses, no target record and setSaveAsActivity(false); it performs no DML and no user- or guest-reachable path leads to it.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>This is an internal alert sent by a scheduled reconciliation job to the owner of a disputed gift and the configured reply-to address; it uses explicit addresses, no target record, and setSaveAsActivity(false), so it performs no DML. No user- or guest-reachable code path reaches it; the reported sources are a test-only fake-Id generator and the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>base/main/default/classes/donation/service/ReceiptService.cls:575-579 setToAddresses + setSaveAsActivity(false)
+base/main/default/classes/donation/async/RefundReconciliationBatch.cls:726 sole caller
+base/main/default/classes/donation/selector/OpportunitiesSelector.cls:940 selectOwnerEmailById SYSTEM_MODE
+fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.
+fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
         </is>
       </c>
     </row>
@@ -639,7 +640,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 3, 10, 20</t>
+          <t>Apex CRUD Violation: 3, 10, 22</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -701,158 +702,279 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 4, 13</t>
+          <t>Apex CRUD Violation: 4, 20, 24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>classes/DonorPortalService.cls:548</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>classes/donor/service/DonorPortalService.cls:548</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send itself performs no DML (setSaveAsActivity(false)); the staff actions that reach it re-read the donor Contact in user mode, so the running user's CRUD, FLS and sharing have already been enforced on the only record involved.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. The staff 'send portal link' and 'show portal code' actions accept a Contact Id, so both staff twins re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base/main/default/classes/donor/service/DonorPortalService.cls:30-47 - class header: the staff twins re-read the donor in the STAFF user's mode (resolveStaffDonorEmail) and refuse a donor that user cannot see
+base/main/default/classes/donor/controller/DonorPortalAdminController.cls:72 SendPortalLinkAction, :93 CreatePortalLinkAction, :156 ContactsSelector.selectById (USER_MODE), :175 AccountsSelector.selectPersonDonorById (USER_MODE)
+DonorPortalService_Test / DonorPortalAdminController_Test: a Fundraising_User who cannot see the Contact gets 'not found' and no Portal_Access_Token__c row is created
+docs/security/appexchange-security-review-readiness.md F-10 (donor-portal IDOR closed 2026-09-25)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 5, 21, 25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>classes/DonorPortalService.cls:483</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>classes/donor/service/DonorPortalService.cls:483</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because Messaging.sendEmail with explicit addresses and setSaveAsActivity(false) writes no record, so there is no DML to guard; the address must already belong to an existing donor, the request is rate-limited, and the response is identical whether or not it matched.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>This sends a one-time sign-in code to a donor's own address after a guest asks for it; the address must match an existing donor, the request is rate-limited, and the response is the same whether or not it matched. The message uses explicit addresses with no target record and setSaveAsActivity(false), so no record is created. The staff controller methods listed as sources reach a different send site (the staff twin) and share only the message-building helper; the fake-Id generator source is test-only. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>base/main/default/classes/donor/service/DonorPortalService.cls:481-490 sendCodeEmail
+buildCodeEmail: setToAddresses, setSaveAsActivity(false)
+fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>R-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 6, 11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>classes/ReceiptService.cls:149</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>classes/donation/service/ReceiptService.cls:149</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>The claim is false because Messaging.sendEmail with setSaveAsActivity(false) performs no create, read, update or delete on any sObject, so no CRUD check applies; the recipient Contact Id is read from the finalized ticket order, not from a caller.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>The event-ticket receipt is sent to the purchaser's own Contact after the purchase is finalized; setSaveAsActivity(false) means the send creates no activity record, so there is no create/read/update/delete for a CRUD check to guard. The recipient Id comes from the purchase record, not from any request parameter. The only reported source is the SOQL builder class, which is a helper rather than an entry point. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:143-149 — setTargetObjectId, setWhatId, setSaveAsActivity(false), sendEmail
 base/main/default/classes/event/service/EventPurchaseService.cls:533 caller (sendTicketReceiptQuietly, :1281)
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>R-005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 5</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>classes/ReceiptService.cls:734</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>classes/donation/service/ReceiptService.cls:734</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>R-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 7, 16, 26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>classes/ReceiptService.cls:329</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>classes/donation/service/ReceiptService.cls:329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because every reported dataflow source is test-support framework code reachable only from test classes, and the sink is an email send with setSaveAsActivity(false) that creates no record; in production the method runs from the platform-event subscriber after a gift is finalized, to that gift's own donor.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Every source reported for this sink is test-support framework code (the mocking library's mock/verify methods and its fake-Id generator), which is only called from test classes. In production the method runs from a platform-event subscriber after a gift is finalized and emails matching-gift instructions to that gift's own donor Contact. setSaveAsActivity(false) is set, so no activity record is written and there is no DML to check. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>base/main/default/classes/donation/service/ReceiptService.cls:313-327 — loop builds messages, setSaveAsActivity(false)
+base/main/default/classes/donation/service/CompanyMatchService.cls:65 sole production caller
+fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>R-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 8, 13</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>classes/ReceiptService.cls:603</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>classes/donation/service/ReceiptService.cls:603</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>The claim is false because the send writes no record (setSaveAsActivity(false)), is reached only from the finalize path and a scheduled renewal job, and addresses the recurring schedule's own donor Contact; no user- or guest-callable entry point selects the recipient.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Recurring-gift notices (confirmation, failed payment, dunning, re-authorization) are sent by the finalize path and a scheduled renewal job to the schedule's own donor Contact, with setSaveAsActivity(false), so the send writes no record. No user- or guest-callable entry point reaches this method. The reported sources are the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/classes/donation/service/ReceiptService.cls:709-734
-base/main/default/classes/recurring/async/RecurringRenewalBatch.cls:197-202; base/main/default/classes/recurring/service/RecurringDonationService.cls:956
-fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>R-006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 6, 8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>classes/ReceiptService.cls:603</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>classes/donation/service/ReceiptService.cls:603</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>The claim is false because the send has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing; it fires once during server-side finalization, to the honoree address the donor supplied with their own gift, and only when the donor opted in.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>The tribute notice is a one-time email to the honoree address the donor entered with their gift, sent during server-side finalization on first creation and only when the donor opted in. It has no target record (setTargetObjectId(null)) and setSaveAsActivity(false), so it writes nothing. The reported sources are a test-only fake-Id generator and the SOQL builder. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:702-704 setTargetObjectId(null), setToAddresses(honoree), setSaveAsActivity(false)
 base/main/default/classes/donation/service/DonationService.cls:404 caller
@@ -860,126 +982,6 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>R-007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 9, 22</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>classes/ReceiptService.cls:518</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>classes/donation/service/ReceiptService.cls:518</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>The claim is false because this is an internal alert from a scheduled job using explicit addresses, no target record and setSaveAsActivity(false); it performs no DML and no user- or guest-reachable path leads to it.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>This is an internal alert sent by a scheduled reconciliation job to the owner of a disputed gift and the configured reply-to address; it uses explicit addresses, no target record, and setSaveAsActivity(false), so it performs no DML. No user- or guest-reachable code path reaches it; the reported sources are a test-only fake-Id generator and the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/classes/donation/service/ReceiptService.cls:575-579 setToAddresses + setSaveAsActivity(false)
-base/main/default/classes/donation/async/RefundReconciliationBatch.cls:726 sole caller
-base/main/default/classes/donation/selector/OpportunitiesSelector.cls:940 selectOwnerEmailById SYSTEM_MODE
-fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.
-fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>R-008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 11, 23, 27</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>classes/DonorPortalService.cls:483</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>classes/donor/service/DonorPortalService.cls:483</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>The claim is false because Messaging.sendEmail with explicit addresses and setSaveAsActivity(false) writes no record, so there is no DML to guard; the address must already belong to an existing donor, the request is rate-limited, and the response is identical whether or not it matched.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>This sends a one-time sign-in code to a donor's own address after a guest asks for it; the address must match an existing donor, the request is rate-limited, and the response is the same whether or not it matched. The message uses explicit addresses with no target record and setSaveAsActivity(false), so no record is created. The staff controller methods listed as sources reach a different send site (the staff twin) and share only the message-building helper; the fake-Id generator source is test-only. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/classes/donor/service/DonorPortalService.cls:481-490 sendCodeEmail
-buildCodeEmail: setToAddresses, setSaveAsActivity(false)
-fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
@@ -999,22 +1001,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 12, 24, 28</t>
+          <t>Apex CRUD Violation: 12</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:548</t>
+          <t>classes/ReceiptService.cls:734</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>classes/donor/service/DonorPortalService.cls:548</t>
+          <t>classes/donation/service/ReceiptService.cls:734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1024,27 +1026,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because the send itself performs no DML (setSaveAsActivity(false)); the staff actions that reach it re-read the donor Contact in user mode, so the running user's CRUD, FLS and sharing have already been enforced on the only record involved.</t>
+          <t>The claim is false because the send writes no record (setSaveAsActivity(false)), is reached only from the finalize path and a scheduled renewal job, and addresses the recurring schedule's own donor Contact; no user- or guest-callable entry point selects the recipient.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>The CRUD finding on the send itself is a false positive: setSaveAsActivity(false) is set and no record is written by Messaging.sendEmail. The staff 'send portal link' and 'show portal code' actions accept a Contact Id, so both staff twins re-read the donor in the staff user's own mode (resolveStaffDonorEmail, USER_MODE selectors for Contact and Person Account) and refuse a donor that user cannot see, before any code is minted, any email is sent or any address is returned. The guest path, which is authorized by possession of the code it produces, is unchanged. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+          <t>Recurring-gift notices (confirmation, failed payment, dunning, re-authorization) are sent by the finalize path and a scheduled renewal job to the schedule's own donor Contact, with setSaveAsActivity(false), so the send writes no record. No user- or guest-callable entry point reaches this method. The reported sources are the SOQL builder's parameter methods. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donor/service/DonorPortalService.cls:30-47 - class header: the staff twins re-read the donor in the STAFF user's mode (resolveStaffDonorEmail) and refuse a donor that user cannot see
-base/main/default/classes/donor/controller/DonorPortalAdminController.cls:72 SendPortalLinkAction, :93 CreatePortalLinkAction, :156 ContactsSelector.selectById (USER_MODE), :175 AccountsSelector.selectPersonDonorById (USER_MODE)
-DonorPortalService_Test / DonorPortalAdminController_Test: a Fundraising_User who cannot see the Contact gets 'not found' and no Portal_Access_Token__c row is created
-docs/security/appexchange-security-review-readiness.md F-10 (donor-portal IDOR closed 2026-09-25)</t>
+          <t>base/main/default/classes/donation/service/ReceiptService.cls:709-734
+base/main/default/classes/recurring/async/RecurringRenewalBatch.cls:197-202; base/main/default/classes/recurring/service/RecurringDonationService.cls:956
+fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
-https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
-https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
         </is>
       </c>
     </row>
@@ -1061,49 +1060,50 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 14, 17, 25</t>
+          <t>Apex CRUD Violation: 15; Apex SOQL SOSL USER MODE MISSING: 9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:329</t>
+          <t>classes/CommunityService.cls:513</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>classes/donation/service/ReceiptService.cls:329</t>
+          <t>classes/setup/service/CommunityService.cls:513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+          <t>Integer assignedCount = [</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.
+USER_MODE is recommended for SOQL or SOSL operations</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>The claim is false because every reported dataflow source is test-support framework code reachable only from test classes, and the sink is an email send with setSaveAsActivity(false) that creates no record; in production the method runs from the platform-event subscriber after a gift is finalized, to that gift's own donor.</t>
+          <t>The claim is false because the statement is a read-only COUNT() of PermissionSetAssignment, a setup object with no sharing model, returning a yes/no verdict and no record data; it is reachable only from the administrator-only setup console, and a user-mode read of setup objects requires View Setup and Configuration, which the package's admin permission set cannot assume every administrator holds.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Every source reported for this sink is test-support framework code (the mocking library's mock/verify methods and its fake-Id generator), which is only called from test classes. In production the method runs from a platform-event subscriber after a gift is finalized and emails matching-gift instructions to that gift's own donor Contact. setSaveAsActivity(false) is set, so no activity record is written and there is no DML to check. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+          <t>This is a read-only count of the site guest user's permission-set assignments, run from the administrator-only setup console to report whether the payment credential is granted to that guest user; it returns a yes/no verdict and no record data. It runs in system mode because PermissionSetAssignment is setup data that the running administrator can read only with 'View Setup and Configuration', which the package's admin permission set does not grant, and without it the console would falsely report the grant as missing. Only users holding the administrator permission set can reach it. The site carries its own SYSTEM_MODE comment saying so, as does every other setup-object read in the class.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donation/service/ReceiptService.cls:313-327 — loop builds messages, setSaveAsActivity(false)
-base/main/default/classes/donation/service/CompanyMatchService.cls:65 sole production caller
-fflib_ApexMocks.mock/verify and fflib_IDGenerator.generate are vendored test-support framework code: they are only ever invoked from *_Test classes to build stubs and fake Ids, and no production entry point reaches this sink through them.</t>
+          <t>base/main/default/classes/setup/service/CommunityService.cls:511-516 - `// SYSTEM_MODE: the guest user's assignments ... a count only, for the Fundraising_Admin-only Settings console.` above the query
+python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites (header-only count now excludes this file's reads)
+SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no ViewSetup userPermission</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Apex CRUD Violation: 16, 18, 26</t>
+          <t>Apex CRUD Violation: 17, 23, 27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1189,35 +1189,94 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>classes/RefundRequestHandler.cls:138</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>classes/guestrequest/handler/RefundRequestHandler.cls:138</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The claim is false because the send performs no DML (setSaveAsActivity(false), explicit addresses); the gift Id it refers to was validated against the authenticated donor's own giving history when the request was recorded, and the message goes only to that gift's owner and the configured reply-to address.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>This notifies staff that a donor asked for a refund through the donor portal; the gift Id was checked against the authenticated donor's own giving history when the request was recorded, and the message goes to that gift's owner and the configured reply-to address, never to a caller-supplied address. It is plain text with explicit addresses and setSaveAsActivity(false), so it writes no record. The reported sources are the SOQL builder's parameter methods, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>base/main/default/classes/guestrequest/handler/RefundRequestHandler.cls:194-199 setToAddresses + setSaveAsActivity(false)
+DonorPortalService.submitRefundRequest -&gt; requireOwnedDonation
+fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>R-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>False positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Apex CRUD Violation: 28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>classes/ReceiptService.cls:173</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>classes/donation/service/ReceiptService.cls:173</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>The claim is false because the send writes no record (setSaveAsActivity(false)), and the only records involved, the gift and its donor Contact, are read in user mode before the message is built, so a staff user who cannot see them gets nothing to send.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Resending a receipt is a staff action whose record access is enforced before the message is built: the gift and the donor Contact are read in user mode (object, field and sharing checks of the running user), so a user who cannot see either gets nothing to send. The recipient is always the gift's own donor Contact, not a caller-supplied address, and setSaveAsActivity(false) means the send writes no record. The other two sources reported are the SOQL builder's parameters, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/donation/service/ReceiptService.cls:196 oppSel.selectById (USER_MODE), :211 conSel.selectById (USER_MODE)
 base/main/default/classes/donation/service/ReceiptService.cls:223-227 setTargetObjectId + setSaveAsActivity(false)
@@ -1226,70 +1285,11 @@
 fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (system mode ignores the running user's FLS and object permissions; record sharing is governed by the class sharing keyword. Verified via search excerpt only; page body not fetchable)
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_keywords_sharing.htm (sharing mode of the class where a method is DEFINED applies, not the caller's; inherited sharing takes the caller's. Page body not fetchable; the 'defined, not called' rule confirmed only via secondary sources, e.g. https://salesforcegeek.in/with-sharing-and-without-sharing-in-apex/ — treat as partially verified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Apex CRUD Violation: 21</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>classes/RefundRequestHandler.cls:138</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>classes/guestrequest/handler/RefundRequestHandler.cls:138</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>This query looks for CRUD operations that are performed without checking for isAccessible(), isUpdateable() orisDeletable(). When an object uses WhoId, WhatId, ParentId, LinkedEntityId fields an additional CRUD check should also be performed on the parent object along with the CRUD and FLS checks on the child object and fields.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>The claim is false because the send performs no DML (setSaveAsActivity(false), explicit addresses); the gift Id it refers to was validated against the authenticated donor's own giving history when the request was recorded, and the message goes only to that gift's owner and the configured reply-to address.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>This notifies staff that a donor asked for a refund through the donor portal; the gift Id was checked against the authenticated donor's own giving history when the request was recorded, and the message goes to that gift's owner and the configured reply-to address, never to a caller-supplied address. It is plain text with explicit addresses and setSaveAsActivity(false), so it writes no record. The reported sources are the SOQL builder's parameter methods, not entry points. The send was reviewed for a code change on 2026-10-01 and none applies: `Messaging.sendEmail` takes no access-level argument, and with setSaveAsActivity(false) there is no record operation for a CRUD check to guard.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/classes/guestrequest/handler/RefundRequestHandler.cls:194-199 setToAddresses + setSaveAsActivity(false)
-DonorPortalService.submitRefundRequest -&gt; requireOwnedDonation
-fflib_QueryFactory.setCondition/selectField(s)/addOrdering is the SOQL builder the selectors use; it is a query-construction helper, not an entry point, and appears as a source only because the engine starts the trace at the builder's string parameters.</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://developer.salesforce.com/docs/atlas.en-us.apexref.meta/apexref/apex_classes_email_outbound_base.htm (Email base class: setSaveAsActivity is true by default; saving as activity applies to the targetObjectId record. Verified via search excerpt; the page body returned 403 to direct fetch and via r.jina.ai only a cookie shell, so the exact wording is not quoted. Whether saveAsActivity=false also suppresses an Enhanced Email EmailMessage row: unverified)</t>
         </is>
       </c>
     </row>
@@ -6121,17 +6121,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>classes/SetupController.cls:642</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>classes/CommunityService.cls:513</t>
+          <t>classes/PaymentSetupGuideService.cls:1918</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Integer assignedCount = [</t>
+          <t>if (m.find()) {</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:360</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>classes/PaymentSetupGuideService.cls:1918</t>
+          <t>classes/ReceiptService.cls:518</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>if (m.find()) {</t>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:360</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:360</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:149</t>
+          <t>classes/DonorPortalService.cls:548</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:360</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:734</t>
+          <t>classes/DonorPortalService.cls:483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:360</t>
+          <t>classes/fflib_IDGenerator.cls:37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:603</t>
+          <t>classes/ReceiptService.cls:149</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>classes/PaymentSetupGuideService.cls:1918</t>
+          <t>classes/ReceiptService.cls:329</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>if (m.find()) {</t>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>R-002</t>
+          <t>R-007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>R-006</t>
+          <t>R-008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6401,22 +6401,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/fflib_QueryFactory.cls:360</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:518</t>
+          <t>classes/PaymentSetupGuideService.cls:1918</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+          <t>if (m.find()) {</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>R-007</t>
+          <t>R-001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/fflib_QueryFactory.cls:360</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6471,22 +6471,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/fflib_QueryFactory.cls:360</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:483</t>
+          <t>classes/ReceiptService.cls:149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>R-008</t>
+          <t>R-006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/fflib_QueryFactory.cls:360</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:548</t>
+          <t>classes/ReceiptService.cls:734</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/fflib_QueryFactory.cls:360</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:149</t>
+          <t>classes/ReceiptService.cls:603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>R-004</t>
+          <t>R-008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6576,22 +6576,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_IDGenerator.cls:37</t>
+          <t>classes/SetupController.cls:479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:329</t>
+          <t>classes/PaymentSetupGuideService.cls:1918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+          <t>if (m.find()) {</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>R-010</t>
+          <t>R-001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6611,22 +6611,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>classes/SetupController.cls:479</t>
+          <t>classes/SetupController.cls:642</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>classes/PaymentSetupGuideService.cls:1918</t>
+          <t>classes/CommunityService.cls:513</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>if (m.find()) {</t>
+          <t>Integer assignedCount = [</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>R-002</t>
+          <t>R-010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundController.cls:22</t>
+          <t>classes/fflib_ApexMocks.cls:69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:408</t>
+          <t>classes/ReceiptService.cls:329</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>R-011</t>
+          <t>R-007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_ApexMocks.cls:115</t>
+          <t>classes/fflib_ApexMocks.cls:69</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:329</t>
+          <t>classes/ReceiptService.cls:408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>R-010</t>
+          <t>R-011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_ApexMocks.cls:115</t>
+          <t>classes/fflib_QueryFactory.cls:218</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:408</t>
+          <t>classes/ReceiptService.cls:518</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>R-011</t>
+          <t>R-002</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptAdminController.cls:38</t>
+          <t>classes/fflib_QueryFactory.cls:218</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:173</t>
+          <t>classes/RefundRequestHandler.cls:138</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6786,22 +6786,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>classes/DonationMonitorController.cls:57</t>
+          <t>classes/DonorPortalAdminController.cls:40</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:103</t>
+          <t>classes/DonorPortalService.cls:548</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>R-003</t>
+          <t>R-004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6821,22 +6821,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:218</t>
+          <t>classes/DonorPortalAdminController.cls:40</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundRequestHandler.cls:138</t>
+          <t>classes/DonorPortalService.cls:483</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>R-013</t>
+          <t>R-005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_QueryFactory.cls:218</t>
+          <t>classes/DonationMonitorController.cls:57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:518</t>
+          <t>classes/ReceiptService.cls:103</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>R-007</t>
+          <t>R-003</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6891,22 +6891,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalAdminController.cls:40</t>
+          <t>classes/RefundController.cls:22</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:483</t>
+          <t>classes/ReceiptService.cls:408</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>R-008</t>
+          <t>R-011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalAdminController.cls:40</t>
+          <t>classes/DonorPortalAdminController.cls:50</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>R-009</t>
+          <t>R-004</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6961,22 +6961,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_ApexMocks.cls:69</t>
+          <t>classes/DonorPortalAdminController.cls:50</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:329</t>
+          <t>classes/DonorPortalService.cls:483</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>R-010</t>
+          <t>R-005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_ApexMocks.cls:69</t>
+          <t>classes/fflib_ApexMocks.cls:115</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:408</t>
+          <t>classes/ReceiptService.cls:329</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>R-011</t>
+          <t>R-007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7031,22 +7031,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalAdminController.cls:50</t>
+          <t>classes/fflib_ApexMocks.cls:115</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:483</t>
+          <t>classes/ReceiptService.cls:408</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{</t>
+          <t>if (!msgs.isEmpty()) { Messaging.sendEmail(msgs); }</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>R-008</t>
+          <t>R-011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7066,22 +7066,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalAdminController.cls:50</t>
+          <t>classes/ReceiptAdminController.cls:38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:548</t>
+          <t>classes/ReceiptService.cls:173</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ code.message });</t>
+          <t>Messaging.sendEmail(new List&lt;Messaging.SingleEmailMessage&gt;{ msg });</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>R-009</t>
+          <t>R-013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-010</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -15677,7 +15677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>before insert, before update, before delete,</t>
+          <t>after insert, after update, after delete, after undelete</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on four different objects (Contact, the donation-designation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the four share is an event list, in pairs: the Contact and donation-designation triggers each declare the four after events, where FFLib asserts the running user's object permission, and the ticket-type and payment-account triggers each declare before delete only. The rule matches triggers by event list, not by object. The previous scan reported the Contact, Opportunity and recurring-donation triggers together, when all three declared the same seven events; once the Contact and recurring-donation triggers were reduced to the events their domain classes use, the Opportunity and recurring-donation triggers each had an event list of their own and dropped out of the report, and the Contact trigger is now reported with the donation-designation trigger instead. No trigger whose event list is its own has been reported in any run.</t>
         </is>
       </c>
     </row>
@@ -15783,17 +15783,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>triggers/OpportunityTrigger.trigger:2</t>
+          <t>triggers/DonationDesignationTrigger.trigger:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>triggers/OpportunityTrigger.trigger:2</t>
+          <t>triggers/DonationDesignationTrigger.trigger:2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>before insert, before update, before delete,</t>
+          <t>after insert, after update, after delete, after undelete</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on four different objects (Contact, the donation-designation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the four share is an event list, in pairs: the Contact and donation-designation triggers each declare the four after events, where FFLib asserts the running user's object permission, and the ticket-type and payment-account triggers each declare before delete only. The rule matches triggers by event list, not by object. The previous scan reported the Contact, Opportunity and recurring-donation triggers together, when all three declared the same seven events; once the Contact and recurring-donation triggers were reduced to the events their domain classes use, the Opportunity and recurring-donation triggers each had an event list of their own and dropped out of the report, and the Contact trigger is now reported with the donation-designation trigger instead. No trigger whose event list is its own has been reported in any run.</t>
         </is>
       </c>
     </row>
@@ -15823,17 +15823,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>triggers/RecurringDonationTrigger.trigger:2</t>
+          <t>triggers/EventTicketTypeTrigger.trigger:1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>triggers/RecurringDonationTrigger.trigger:2</t>
+          <t>triggers/EventTicketTypeTrigger.trigger:1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>before insert, before update, before delete,</t>
+          <t>trigger EventTicketTypeTrigger on Event_Ticket_Type__c (before delete) {</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on four different objects (Contact, the donation-designation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the four share is an event list, in pairs: the Contact and donation-designation triggers each declare the four after events, where FFLib asserts the running user's object permission, and the ticket-type and payment-account triggers each declare before delete only. The rule matches triggers by event list, not by object. The previous scan reported the Contact, Opportunity and recurring-donation triggers together, when all three declared the same seven events; once the Contact and recurring-donation triggers were reduced to the events their domain classes use, the Opportunity and recurring-donation triggers each had an event list of their own and dropped out of the report, and the Contact trigger is now reported with the donation-designation trigger instead. No trigger whose event list is its own has been reported in any run.</t>
         </is>
       </c>
     </row>
@@ -15863,17 +15863,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>triggers/EventTicketTypeTrigger.trigger:1</t>
+          <t>triggers/PaymentAccountTrigger.trigger:1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>triggers/EventTicketTypeTrigger.trigger:1</t>
+          <t>triggers/PaymentAccountTrigger.trigger:1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>trigger EventTicketTypeTrigger on Event_Ticket_Type__c (before delete) {</t>
+          <t>trigger PaymentAccountTrigger on Payment_Account__c (before delete) {</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -15888,47 +15888,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
+          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on four different objects (Contact, the donation-designation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the four share is an event list, in pairs: the Contact and donation-designation triggers each declare the four after events, where FFLib asserts the running user's object permission, and the ticket-type and payment-account triggers each declare before delete only. The rule matches triggers by event list, not by object. The previous scan reported the Contact, Opportunity and recurring-donation triggers together, when all three declared the same seven events; once the Contact and recurring-donation triggers were reduced to the events their domain classes use, the Opportunity and recurring-donation triggers each had an event list of their own and dropped out of the report, and the Contact trigger is now reported with the donation-designation trigger instead. No trigger whose event list is its own has been reported in any run.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Multiple Trigger On same sObject</t>
+          <t>DML Statements Inside Loops</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>triggers/PaymentAccountTrigger.trigger:1</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:1037</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>triggers/PaymentAccountTrigger.trigger:1</t>
+          <t>classes/SystemDML.cls:35</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>trigger PaymentAccountTrigger on Payment_Account__c (before delete) {</t>
+          <t>System.Database.insert(objList, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>One trigger per object — scanner misfire</t>
+          <t>Unit of Work commit — one statement per object type</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>By design</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>The package has exactly one trigger per object; each is a single line that hands off to its FFLib domain class (fflib_SObjectDomain.triggerHandler). The reported triggers are on five different objects (Contact, Opportunity, the recurring-donation object, the ticket-type object and the payment-account object). Reproduce with grep -h "^trigger" base/main/default/triggers/*.trigger | awk '{print $4}' | sort | uniq -d, which prints nothing. What the five share is an event list: at scan time the Contact, Opportunity and recurring-donation triggers each declared all seven events, and the ticket-type and payment-account triggers each declare before delete only. No trigger whose event list is its own was reported. Since the scan, the Contact and recurring-donation triggers declare only the events their domain classes use: the four after events, where FFLib asserts the running user's object permission, plus before insert on the recurring-donation object.</t>
+          <t>fflib_SObjectUnitOfWork.commitWork() and its SystemDML strategy iterate over the registered object types and issue one DML statement per type, passing the full list of records of that type. The number of statements is bounded by the number of object types registered, not by the number of records, which is the bulkification pattern the Unit of Work exists to provide.</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -15948,12 +15948,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>classes/SystemDML.cls:35</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:208</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>System.Database.insert(objList, AccessLevel.SYSTEM_MODE);</t>
+          <t>System.Database.insert(objList,AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -15979,7 +15979,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -15988,12 +15988,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:208</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:286</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>System.Database.insert(objList,AccessLevel.SYSTEM_MODE);</t>
+          <t>System.Database.insert(objList, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -16019,21 +16019,21 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:1037</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:1046</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:286</t>
+          <t>classes/SystemDML.cls:40</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>System.Database.insert(objList, AccessLevel.USER_MODE);</t>
+          <t>System.Database.update(objList, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>classes/SystemDML.cls:40</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:218</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -16108,12 +16108,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:218</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:290</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>System.Database.update(objList, AccessLevel.SYSTEM_MODE);</t>
+          <t>System.Database.update(objList, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -16139,21 +16139,21 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:1046</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:1056</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:290</t>
+          <t>classes/SystemDML.cls:45</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>System.Database.update(objList, AccessLevel.USER_MODE);</t>
+          <t>System.Database.upsert(objList, externalId, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -16179,7 +16179,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>classes/SystemDML.cls:45</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:229</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -16219,7 +16219,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -16228,12 +16228,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:229</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>System.Database.upsert(objList, externalId, AccessLevel.SYSTEM_MODE);</t>
+          <t>System.Database.upsert(objList, externalId, true, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -16259,21 +16259,21 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:1056</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:1070</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:299</t>
+          <t>classes/SystemDML.cls:50</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>System.Database.upsert(objList, externalId, true, AccessLevel.USER_MODE);</t>
+          <t>System.Database.delete(objList, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -16299,7 +16299,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -16308,12 +16308,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>classes/SystemDML.cls:50</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:240</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>System.Database.delete(objList, AccessLevel.SYSTEM_MODE);</t>
+          <t>System.Database.delete(objList, AccessLevel.SYSTEM_MODE) ;</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -16348,12 +16348,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:240</t>
+          <t>classes/fflib_SObjectUnitOfWork.cls:294</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>System.Database.delete(objList, AccessLevel.SYSTEM_MODE) ;</t>
+          <t>System.Database.delete(objList, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -16379,26 +16379,26 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:1070</t>
+          <t>classes/StripePaymentSweep.cls:149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>classes/fflib_SObjectUnitOfWork.cls:294</t>
+          <t>classes/StripePaymentSweep.cls:203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>System.Database.delete(objList, AccessLevel.USER_MODE);</t>
+          <t>insert as system new Transaction_Log__c(</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Unit of Work commit — one statement per object type</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>fflib_SObjectUnitOfWork.commitWork() and its SystemDML strategy iterate over the registered object types and issue one DML statement per type, passing the full list of records of that type. The number of statements is bounded by the number of object types registered, not by the number of records, which is the bulkification pattern the Unit of Work exists to provide.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -16428,17 +16428,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:203</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Transaction_Log__c(</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -16468,17 +16468,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/EventPurchaseService.cls:590</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -16499,26 +16499,26 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:149</t>
+          <t>classes/StagingReconciliationBatch.cls:92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:590</t>
+          <t>classes/StagingReconciliationBatch.cls:234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
+          <t>update as system new Donation_Staging__c(Id = st.Id, Status__c = 'Failed');</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -16548,12 +16548,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>classes/StagingReconciliationBatch.cls:234</t>
+          <t>classes/StagingReconciliationBatch.cls:240</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>update as system new Donation_Staging__c(Id = st.Id, Status__c = 'Failed');</t>
+          <t>update as system new Donation_Staging__c(Id = st.Id, Status__c = 'Expired');</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -16588,12 +16588,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>classes/StagingReconciliationBatch.cls:240</t>
+          <t>classes/StagingReconciliationBatch.cls:275</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>update as system new Donation_Staging__c(Id = st.Id, Status__c = 'Expired');</t>
+          <t>update as system upd;</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -16628,12 +16628,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>classes/StagingReconciliationBatch.cls:275</t>
+          <t>classes/StagingReconciliationBatch.cls:281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>update as system upd;</t>
+          <t>insert as system log;</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -16668,17 +16668,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>classes/StagingReconciliationBatch.cls:281</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>insert as system log;</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16699,7 +16699,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -16708,17 +16708,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/EventPurchaseService.cls:590</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -16739,26 +16739,26 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>classes/StagingReconciliationBatch.cls:92</t>
+          <t>classes/GuestRequestService.cls:140</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:590</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16779,11 +16779,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>classes/GuestRequestService.cls:140</t>
+          <t>classes/RecurringRenewalBatch.cls:153</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -16819,26 +16819,26 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringRenewalBatch.cls:153</t>
+          <t>classes/StripePaymentSweep.cls:86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/StripePaymentSweep.cls:191</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>update as system new Payment_Account__c(Id = acct.Id, Payment_Sweep_Cursor__c = runStartedAt);</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -16868,17 +16868,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:191</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>update as system new Payment_Account__c(Id = acct.Id, Payment_Sweep_Cursor__c = runStartedAt);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -16899,11 +16899,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:86</t>
+          <t>classes/NpspSyncService.cls:82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -16939,11 +16939,11 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>classes/NpspSyncService.cls:82</t>
+          <t>classes/NpspSyncService.cls:148</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -16979,11 +16979,11 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>classes/NpspSyncService.cls:148</t>
+          <t>classes/CampaignMemberSyncService.cls:150</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -17019,11 +17019,11 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignMemberSyncService.cls:150</t>
+          <t>classes/CampaignMemberSyncService.cls:152</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -17059,11 +17059,11 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignMemberSyncService.cls:152</t>
+          <t>classes/CampaignDesignationService.cls:171</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -17099,11 +17099,11 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignDesignationService.cls:171</t>
+          <t>classes/AttendeeNamingHandler.cls:193</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -17139,11 +17139,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler.cls:193</t>
+          <t>classes/RefundReconciliationBatch.cls:217</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -17179,11 +17179,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundReconciliationBatch.cls:217</t>
+          <t>classes/ReceiptService.cls:313</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -17219,11 +17219,11 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:313</t>
+          <t>classes/ReceiptService.cls:392</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -17259,11 +17259,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:392</t>
+          <t>classes/FundraiserAdminController.cls:519</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -17299,11 +17299,11 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>classes/FundraiserAdminController.cls:519</t>
+          <t>classes/CommunityService.cls:698</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -17339,11 +17339,11 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>classes/CommunityService.cls:698</t>
+          <t>classes/EventPurchaseService.cls:911</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -17379,11 +17379,11 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:911</t>
+          <t>classes/EventPurchaseService.cls:917</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -17419,11 +17419,11 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:917</t>
+          <t>classes/RecurringRenewalBatch.cls:80</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -17459,26 +17459,26 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringRenewalBatch.cls:80</t>
+          <t>classes/StripePaymentSweep_Test.cls:207</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/StripePaymentSweep.cls:191</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>update as system new Payment_Account__c(Id = acct.Id, Payment_Sweep_Cursor__c = runStartedAt);</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -17508,17 +17508,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:191</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>update as system new Payment_Account__c(Id = acct.Id, Payment_Sweep_Cursor__c = runStartedAt);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17539,11 +17539,11 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep_Test.cls:207</t>
+          <t>classes/RecurringRenewalBatch.cls:66</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -17579,11 +17579,11 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringRenewalBatch.cls:66</t>
+          <t>classes/EventTicketAdminController.cls:258</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -17619,7 +17619,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -17628,17 +17628,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/PricebookService.cls:125</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -17668,12 +17668,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:125</t>
+          <t>classes/PricebookService.cls:135</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
+          <t>insert as system newEvt;</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -17699,26 +17699,26 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>classes/EventTicketAdminController.cls:258</t>
+          <t>classes/RefundReconciliationBatch.cls:283</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:135</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>insert as system newEvt;</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -17739,11 +17739,11 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundReconciliationBatch.cls:283</t>
+          <t>classes/EventRegistrationController.cls:591</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -17779,11 +17779,11 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>classes/EventRegistrationController.cls:591</t>
+          <t>classes/EventPurchaseService.cls:1195</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -17819,11 +17819,11 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:1195</t>
+          <t>classes/NpspSyncService.cls:114</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -17859,11 +17859,11 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>classes/NpspSyncService.cls:114</t>
+          <t>classes/GuestRequestService.cls:124</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -17899,26 +17899,26 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>classes/GuestRequestService.cls:124</t>
+          <t>classes/AttendeeNamingHandler_Test.cls:237</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/AttendeeNamingHandler_Test.cls:40</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system r;</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Test fixture</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The loop and the DML are in test code (TestDataFactory and _Test classes) that builds a small, fixed set of records for a test. Test classes do not run in subscriber transactions.</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -17948,17 +17948,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler_Test.cls:40</t>
+          <t>classes/AttendeeNamingHandler.cls:129</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>insert as system r;</t>
+          <t>Database.SaveResult[] results = Database.update(toUpdate, false, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Test fixture</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>The loop and the DML are in test code (TestDataFactory and _Test classes) that builds a small, fixed set of records for a test. Test classes do not run in subscriber transactions.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -17979,21 +17979,21 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler_Test.cls:237</t>
+          <t>classes/SecureTokens.cls:30</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler.cls:129</t>
+          <t>classes/DonationService.cls:890</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Database.SaveResult[] results = Database.update(toUpdate, false, AccessLevel.SYSTEM_MODE);</t>
+          <t>insert as system new Transaction_Log__c(</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -18019,26 +18019,26 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>classes/SecureTokens.cls:30</t>
+          <t>classes/CancelGoalReachedRecurringQueueable.cls:89</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>classes/DonationService.cls:887</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Transaction_Log__c(</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18059,11 +18059,11 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>classes/CancelGoalReachedRecurringQueueable.cls:89</t>
+          <t>classes/RefundReconciliationBatch.cls:177</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -18099,11 +18099,11 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundReconciliationBatch.cls:177</t>
+          <t>classes/ReceiptService.cls:514</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -18139,11 +18139,11 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>classes/ReceiptService.cls:514</t>
+          <t>classes/CampaignPostService.cls:679</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -18179,11 +18179,11 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:679</t>
+          <t>classes/PostInstallHandler.cls:804</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -18219,11 +18219,11 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>classes/PostInstallHandler.cls:804</t>
+          <t>classes/AttendeeNamingHandler.cls:133</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -18259,26 +18259,26 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler.cls:133</t>
+          <t>classes/CampaignPostService.cls:332</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18299,26 +18299,26 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:332</t>
+          <t>classes/CommunityService.cls:728</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18339,11 +18339,11 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>classes/CommunityService.cls:728</t>
+          <t>classes/CampaignMemberSyncService.cls:65</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -18379,26 +18379,26 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignMemberSyncService.cls:65</t>
+          <t>classes/StripePaymentSweep.cls:113</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/StripePaymentSweep.cls:203</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system new Transaction_Log__c(</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -18419,7 +18419,7 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
@@ -18428,17 +18428,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:203</t>
+          <t>classes/EventPurchaseService.cls:590</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Transaction_Log__c(</t>
+          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18459,26 +18459,26 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:113</t>
+          <t>classes/AttendeeNamingHandler.cls:185</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:590</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler.cls:185</t>
+          <t>classes/CompanyMatchService.cls:47</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18539,11 +18539,11 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>classes/CompanyMatchService.cls:47</t>
+          <t>classes/EventPurchaseService.cls:419</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18579,26 +18579,26 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:419</t>
+          <t>classes/DonorPortalService.cls:452</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/DonorPortalService.cls:443</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>Database.insert(row, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18619,26 +18619,26 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:452</t>
+          <t>classes/CommunityService.cls:793</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:443</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Database.insert(row, AccessLevel.SYSTEM_MODE);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18659,11 +18659,11 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>classes/CommunityService.cls:793</t>
+          <t>classes/PostInstallHandler.cls:1754</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -18699,26 +18699,26 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>classes/PostInstallHandler.cls:1754</t>
+          <t>classes/CampaignPostService.cls:613</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18739,26 +18739,26 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:613</t>
+          <t>classes/EventPurchaseService.cls:1049</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18779,36 +18779,36 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>classes/DonationService.cls:652</t>
+          <t>classes/CampaignPostService.cls:286</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Loop removed since scan</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Fixed since scan</t>
+          <t>By design</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>DonationService.publishErrorText no longer loops over the event bus's errors. A one-event publish returns one error in practice, so it now quotes the first error's status code and message and counts any others; no value built in a loop reaches the AppLogger insert.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18819,26 +18819,26 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:1049</t>
+          <t>classes/CampaignPostService.cls:302</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -18859,21 +18859,21 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:286</t>
+          <t>classes/EventPurchaseService.cls:832</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/PricebookService.cls:125</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -18899,21 +18899,21 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:302</t>
+          <t>classes/EventPurchaseService.cls:832</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/PricebookService.cls:135</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>insert as system newEvt;</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -18939,26 +18939,26 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:832</t>
+          <t>classes/RecurringRenewalBatch.cls:426</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:125</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -18979,26 +18979,26 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:832</t>
+          <t>classes/NpspSyncService.cls:56</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:135</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>insert as system newEvt;</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19019,26 +19019,26 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringRenewalBatch.cls:426</t>
+          <t>classes/RecordTypeMappingService.cls:112</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/SettingsService.cls:345</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>upsert as system settings;</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -19059,26 +19059,26 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>classes/NpspSyncService.cls:56</t>
+          <t>classes/StripeGateway.cls:533</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/StripePaymentSweep.cls:203</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system new Transaction_Log__c(</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Batch job — per-row isolation by design</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
         </is>
       </c>
     </row>
@@ -19099,21 +19099,21 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>classes/RecordTypeMappingService.cls:112</t>
+          <t>classes/StripeGateway.cls:533</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>classes/SettingsService.cls:345</t>
+          <t>classes/EventPurchaseService.cls:590</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>upsert as system settings;</t>
+          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -19139,26 +19139,26 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>classes/StripeGateway.cls:533</t>
+          <t>classes/RecurringRenewalBatch_Test.cls:722</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>classes/StripePaymentSweep.cls:203</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Transaction_Log__c(</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Batch job — per-row isolation by design</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>The two jobs write per record on purpose. StripePaymentSweep runs with a batch scope of 1 and caps repairs at 5 per run, so each execution writes for one payment account. StagingReconciliationBatch runs with a scope of 5, makes all its Stripe callouts first, then writes each staging row's outcome separately so that one row's failure does not roll back the outcome already recorded for another. Both stay far inside the per-transaction DML limit.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19179,21 +19179,21 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>classes/StripeGateway.cls:533</t>
+          <t>classes/PricebookService_Test.cls:182</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>classes/EventPurchaseService.cls:590</t>
+          <t>classes/PricebookService.cls:125</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>insert as system toAdd; // bulk — never per-attendee DML</t>
+          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -19219,26 +19219,26 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringRenewalBatch_Test.cls:722</t>
+          <t>classes/PricebookService_Test.cls:182</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/PricebookService.cls:135</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>insert as system newEvt;</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -19259,21 +19259,21 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService_Test.cls:182</t>
+          <t>classes/CampaignPostService.cls:589</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -19299,26 +19299,26 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService_Test.cls:182</t>
+          <t>classes/RecurringDonationService_Test.cls:1399</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:135</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>insert as system newEvt;</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19339,26 +19339,26 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:589</t>
+          <t>classes/RefundReconciliationBatch.cls:628</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/AppLogger.cls:125</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>insert as system new Log__c(</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Single statement after the loop</t>
+          <t>Error logging — guarded insert</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
+          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
         </is>
       </c>
     </row>
@@ -19379,26 +19379,26 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>classes/RecurringDonationService_Test.cls:1399</t>
+          <t>classes/CampaignPostService.cls:605</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/CampaignPostService.cls:678</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -19419,11 +19419,11 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>classes/RefundReconciliationBatch.cls:628</t>
+          <t>classes/AttendeeNamingHandler.cls:92</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -19459,11 +19459,11 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:605</t>
+          <t>classes/CampaignPostService.cls:256</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -19499,26 +19499,26 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>classes/AttendeeNamingHandler.cls:92</t>
+          <t>classes/EventTicketAdminController.cls:210</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>classes/AppLogger.cls:125</t>
+          <t>classes/PricebookService.cls:125</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>insert as system new Log__c(</t>
+          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Error logging — guarded insert</t>
+          <t>Single statement after the loop</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>AppLogger.write() inserts one Log__c row per call. The callers inside loops log from catch blocks, anomaly branches and per-row outcome notices. Before inserting, write() returns when the entry's level is below the org's configured log-level threshold (or logging is off), and when the transaction has no DML statements left (Limits.getLimitDmlStatements() &lt;= Limits.getDmlStatements()), so logging cannot raise a limit exception that would mask the error being recorded. The insert itself is wrapped in try/catch.</t>
+          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
         </is>
       </c>
     </row>
@@ -19539,21 +19539,21 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:256</t>
+          <t>classes/EventTicketAdminController.cls:210</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>classes/CampaignPostService.cls:678</t>
+          <t>classes/PricebookService.cls:135</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>List&lt;Database.SaveResult&gt; results = Database.insert(toCreate, false, AccessLevel.USER_MODE);</t>
+          <t>insert as system newEvt;</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -19579,21 +19579,21 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>classes/EventTicketAdminController.cls:210</t>
+          <t>classes/DonorPortalService_Test.cls:456</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:125</t>
+          <t>classes/DonorPortalService.cls:392</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
+          <t>Database.update(new Portal_Access_Token__c(Id = matched.Id,</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -19619,21 +19619,21 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>classes/EventTicketAdminController.cls:210</t>
+          <t>classes/DonorPortalService_Test.cls:456</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>classes/PricebookService.cls:135</t>
+          <t>classes/DonorPortalService.cls:383</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>insert as system newEvt;</t>
+          <t>Database.update(bump, AccessLevel.SYSTEM_MODE);</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -19659,21 +19659,21 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService_Test.cls:456</t>
+          <t>classes/EventPurchaseService.cls:772</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:392</t>
+          <t>classes/PricebookService.cls:125</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Database.update(new Portal_Access_Token__c(Id = matched.Id,</t>
+          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -19699,21 +19699,21 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService_Test.cls:456</t>
+          <t>classes/EventPurchaseService.cls:772</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>classes/DonorPortalService.cls:383</t>
+          <t>classes/PricebookService.cls:135</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Database.update(bump, AccessLevel.SYSTEM_MODE);</t>
+          <t>insert as system newEvt;</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -19732,88 +19732,8 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>DML Statements Inside Loops</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>classes/EventPurchaseService.cls:772</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>classes/PricebookService.cls:125</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>if (!newStd.isEmpty()) { insert as system newStd; } // MUST precede the custom-pricebook insert below</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Single statement after the loop</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>By design</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>DML Statements Inside Loops</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>classes/EventPurchaseService.cls:772</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>classes/PricebookService.cls:135</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>insert as system newEvt;</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Single statement after the loop</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>By design</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>The DML statement is not inside the loop the scanner names. In each path the loop builds the list that one bulk statement then writes (insert as system newStd, Database.insert(toCreate, false, AccessLevel.USER_MODE), Database.update(toUpdate, false, ...)), generates a token character by character before a single insert, or joins the record-type mappings into one encoded string that a single upsert of the settings record then saves; in the remaining paths the loop is in a test method that calls the service more than once. The rule follows data from the loop into any method that contains a DML statement, including a call made once after the loop has ended, so a bulk call that receives the list the loop built is reported as DML inside the loop. The statement runs once per call whatever the number of records.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H103"/>
+  <autoFilter ref="A1:H101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19839,7 +19759,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>a0OKX000001JT8J2AW</t>
+          <t>a0OKX000001JTAA2A4</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19795,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 04:53:53</t>
+          <t>2026-10-06 21:57:40</t>
         </is>
       </c>
     </row>
@@ -19887,7 +19807,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 10:38:14</t>
+          <t>2026-10-07 03:41:59</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19838,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -19929,7 +19849,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>db425b78</t>
+          <t>32ec92a2</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19861,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -19849,7 +19849,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>32ec92a2</t>
+          <t>36949d12</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/checkmarx-false-positives.xlsx
+++ b/assets/security-review/checkmarx-false-positives.xlsx
@@ -740,7 +740,7 @@
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:30-47 - class header: the staff twins re-read the donor in the STAFF user's mode (resolveStaffDonorEmail) and refuse a donor that user cannot see
 base/main/default/classes/donor/controller/DonorPortalAdminController.cls:72 SendPortalLinkAction, :93 CreatePortalLinkAction, :156 ContactsSelector.selectById (USER_MODE), :175 AccountsSelector.selectPersonDonorById (USER_MODE)
 DonorPortalService_Test / DonorPortalAdminController_Test: a Fundraising_User who cannot see the Contact gets 'not found' and no Portal_Access_Token__c row is created
-docs/security/appexchange-security-review-readiness.md F-10 (donor-portal IDOR closed 2026-09-25)</t>
+The staff path re-reads the donor under the staff user's own sharing and field permissions (DonorPortalAdminController.cls:156 and :175, USER_MODE) before this service acts, so a staff user who cannot see the donor record cannot obtain a portal code for it (hardened 2026-09-25).</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:511-516 - `// SYSTEM_MODE: the guest user's assignments ... a count only, for the Fundraising_Admin-only Settings console.` above the query
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites (header-only count now excludes this file's reads)
+Every SYSTEM_MODE query and DML statement in the package carries a `// SYSTEM_MODE:` reason comment directly at the call site (`grep -rn 'SYSTEM_MODE' base/main/default/classes` shows the comment above each use); for this statement it is at :511-512.
 SetupController granted only in Fundraising_Admin; Fundraising_Admin carries no ViewSetup userPermission</t>
         </is>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_classes_enforce_usermode.htm (user-mode DML enforces the running user's object permissions and sharing)
-AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
 base/main/default/customPermissions/Manage_Fundraising_Settings.customPermission-meta.xml; Fundraising_Admin.permissionset-meta.xml grants it; Fundraising_User / Fundraising_ReadOnly / Fundraising_GuestDonor do not
 SetupController_Test: five deny tests (bare Standard User), one deny test (Fundraising_User), one allow test (Fundraising_Admin); 312 tests pass, SetupController 96%, SettingsService 98%
 PostInstallHandler.onInstall -&gt; seedRecordTypeMappings / ensureDefaultLogoSeeded still reach this write with no permission check: install context, no running user to check
-docs/security/appexchange-security-review-readiness.md F-13</t>
+Every settings write in the package is reached only through a SetupController action whose doValidate() calls requireSettingsPermission(), i.e. FeatureManagement.checkPermission('Manage_Fundraising_Settings'); only the Fundraising_Admin permission set grants that custom permission. The install-time seeds are the one other caller and run with no interactive user (hardened 2026-09-25).</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
 base/main/default/classes/setup/controller/SetupController.cls:2192-2201 - ScheduleJobFamily extends SettingsWriteAction; doValidate() calls requireSettingsPermission() before the family / interval checks
 SetupController_Test.test_scheduleJobFamily_userWithoutSettingsPermission_isRefused
 Fundraising_Admin is the only permission set with SetupController classAccess and the only one carrying Manage_Fundraising_Settings
-docs/security/appexchange-security-review-readiness.md F-13</t>
+Every settings write in the package is reached only through a SetupController action whose doValidate() calls requireSettingsPermission(), i.e. FeatureManagement.checkPermission('Manage_Fundraising_Settings'); only the Fundraising_Admin permission set grants that custom permission. The install-time seeds are the one other caller and run with no interactive user (hardened 2026-09-25).</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm (post-install script runs as a package-specific system user)
-AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm (post-install script runs as a package-specific system user)
-AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2348,14 +2348,15 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:183-186 onInstall calls each seed* step in its own try/catch; only logStepFailure on error
 grep of non-test classes: seedDefaultSettings, seedDefaultImages, seedDefaultPageDesign, seedEventPricebook, seedEventDonationProduct, seedEventFeeProduct, seedContentTemplates have NO callers outside PostInstallHandler (mentions in PricebookService/SettingsService are comments/strings only)
 Class is `public`, not `global` (changed 2026-09-05), so subscriber anonymous Apex / other namespaces cannot invoke these methods
-Pricebook2 and Product2 are standard objects; AGENTS.md / readiness FP-1 item 2 record that a 2GP permission set cannot ship a standard-object grant (build strips it silently), and the install user holds no permission set anyway
+Pricebook2 and Product2 are standard objects. A managed package cannot ship object permissions on a standard object — Salesforce ignores them at install (packaging guide, cited below) — and the per-package install user holds no permission set in any case, so a user-mode write here could never satisfy the check the scanner asks for.
 base/main/default/classes/event/service/PricebookService.cls:11-24 doc: install-testing (2026-08-09) showed a `with sharing` path could not even resolve Pricebook2 as the per-package system user
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1501 `new Pricebook2(Name = EVENT_PRICEBOOK_NAME, IsActive = true)` - constant values; inserted only when neither the current nor the legacy pricebook exists</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2413,14 +2414,15 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:183-186 onInstall calls each seed* step in its own try/catch; only logStepFailure on error
 grep of non-test classes: seedDefaultSettings, seedDefaultImages, seedDefaultPageDesign, seedEventPricebook, seedEventDonationProduct, seedEventFeeProduct, seedContentTemplates have NO callers outside PostInstallHandler (mentions in PricebookService/SettingsService are comments/strings only)
 Class is `public`, not `global` (changed 2026-09-05), so subscriber anonymous Apex / other namespaces cannot invoke these methods
-Pricebook2 and Product2 are standard objects; AGENTS.md / readiness FP-1 item 2 record that a 2GP permission set cannot ship a standard-object grant (build strips it silently), and the install user holds no permission set anyway
+Pricebook2 and Product2 are standard objects. A managed package cannot ship object permissions on a standard object — Salesforce ignores them at install (packaging guide, cited below) — and the per-package install user holds no permission set in any case, so a user-mode write here could never satisfy the check the scanner asks for.
 base/main/default/classes/event/service/PricebookService.cls:11-24 doc: install-testing (2026-08-09) showed a `with sharing` path could not even resolve Pricebook2 as the per-package system user
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1534 `new Product2(Name = EVENT_DONATION_PRODUCT_NAME, IsActive = true)` - constants; only when no Product2 with that name exists (query WITH SYSTEM_MODE)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2478,14 +2480,15 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:183-186 onInstall calls each seed* step in its own try/catch; only logStepFailure on error
 grep of non-test classes: seedDefaultSettings, seedDefaultImages, seedDefaultPageDesign, seedEventPricebook, seedEventDonationProduct, seedEventFeeProduct, seedContentTemplates have NO callers outside PostInstallHandler (mentions in PricebookService/SettingsService are comments/strings only)
 Class is `public`, not `global` (changed 2026-09-05), so subscriber anonymous Apex / other namespaces cannot invoke these methods
-Pricebook2 and Product2 are standard objects; AGENTS.md / readiness FP-1 item 2 record that a 2GP permission set cannot ship a standard-object grant (build strips it silently), and the install user holds no permission set anyway
+Pricebook2 and Product2 are standard objects. A managed package cannot ship object permissions on a standard object — Salesforce ignores them at install (packaging guide, cited below) — and the per-package install user holds no permission set in any case, so a user-mode write here could never satisfy the check the scanner asks for.
 base/main/default/classes/event/service/PricebookService.cls:11-24 doc: install-testing (2026-08-09) showed a `with sharing` path could not even resolve Pricebook2 as the per-package system user
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1578 `new Product2(Name = EVENT_FEE_PRODUCT_NAME, IsActive = true)` - constants; only when absent</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2547,7 @@
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_batch_interface.htm (batch Apex runs asynchronously; Salesforce false-positive guidance exempts batch and async context)
-AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2606,7 @@
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://developer.salesforce.com/docs/atlas.en-us.platform_events.meta/platform_events/platform_events_subscribe_apex.htm
-AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2793,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2852,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AGENTS.md Change Management: 2GP strips standard-object grants (project finding 2026-08-16)</t>
+          <t>https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2971,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>project memory/platform limit: Guest User licence cannot be granted object Edit/Delete (AGENTS.md guest-user notes) - unverified against a primary URL in this pass</t>
+          <t>https://help.salesforce.com/s/articleView?id=sf.networks_guest_policies_timelines.htm — Guest User Security Policies and Timelines: since Spring '21 the Edit, Delete, View All and Modify All object permissions are removed from guest users, and a permission set that grants any of them cannot be assigned to a guest user; guest users can hold only Read and Create.</t>
         </is>
       </c>
     </row>
@@ -3026,14 +3029,15 @@
 base/main/default/classes/setup/controller/PostInstallHandler.cls:183-186 onInstall calls each seed* step in its own try/catch; only logStepFailure on error
 grep of non-test classes: seedDefaultSettings, seedDefaultImages, seedDefaultPageDesign, seedEventPricebook, seedEventDonationProduct, seedEventFeeProduct, seedContentTemplates have NO callers outside PostInstallHandler (mentions in PricebookService/SettingsService are comments/strings only)
 Class is `public`, not `global` (changed 2026-09-05), so subscriber anonymous Apex / other namespaces cannot invoke these methods
-Pricebook2 and Product2 are standard objects; AGENTS.md / readiness FP-1 item 2 record that a 2GP permission set cannot ship a standard-object grant (build strips it silently), and the install user holds no permission set anyway
+Pricebook2 and Product2 are standard objects. A managed package cannot ship object permissions on a standard object — Salesforce ignores them at install (packaging guide, cited below) — and the per-package install user holds no permission set in any case, so a user-mode write here could never satisfy the check the scanner asks for.
 base/main/default/classes/event/service/PricebookService.cls:11-24 doc: install-testing (2026-08-09) showed a `with sharing` path could not even resolve Pricebook2 as the per-package system user
 base/main/default/classes/setup/controller/PostInstallHandler.cls:1477-1499 seedEventPricebook: if only the pre-rename pricebook exists, renames it in place to EVENT_PRICEBOOK_NAME ('Fundraising Events') so its PricebookEntry rows survive; the new name is a constant</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5</t>
+          <t>https://help.salesforce.com/s/articleView?id=sf.apex_post_install_script.htm&amp;language=en_US&amp;type=5
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -3574,9 +3578,8 @@
       <c r="J51" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:325-331 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
-SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
-docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
+Every SYSTEM_MODE query and DML statement in the package carries a `// SYSTEM_MODE:` reason comment directly at the call site (`grep -rn 'SYSTEM_MODE' base/main/default/classes` shows the comment above each use); for this statement it is at :325-331.
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3636,9 +3639,8 @@
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:566-583 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
-SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
-docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
+Every SYSTEM_MODE query and DML statement in the package carries a `// SYSTEM_MODE:` reason comment directly at the call site (`grep -rn 'SYSTEM_MODE' base/main/default/classes` shows the comment above each use); for this statement it is at :566-568.
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3697,9 +3699,8 @@
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:605-611 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
-SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
-docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
+Every SYSTEM_MODE query and DML statement in the package carries a `// SYSTEM_MODE:` reason comment directly at the call site (`grep -rn 'SYSTEM_MODE' base/main/default/classes` shows the comment above each use); for this statement it is at :605-607.
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3758,9 +3759,8 @@
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>base/main/default/classes/setup/service/CommunityService.cls:404-418 - per-site `// SYSTEM_MODE:` comment directly above the query (setup data about the site GUEST user; only a Boolean / Set&lt;Id&gt; leaves the method)
-python3 scripts/lint/system-mode-inventory.py -&gt; 0 unjustified sites
-SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin
-docs/security/appexchange-security-review-readiness.md F-1 (third pass, 2026-09-25)</t>
+Every SYSTEM_MODE query and DML statement in the package carries a `// SYSTEM_MODE:` reason comment directly at the call site (`grep -rn 'SYSTEM_MODE' base/main/default/classes` shows the comment above each use); for this statement it is at :404-406.
+SetupController.cls saveExperienceSite / checkGuestPermissionSet are @AuraEnabled on a with-sharing controller granted only in Fundraising_Admin</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
 grep: `new SystemDML()` at 24 production sites, each preceded by a `// SystemDML: guest|job|rollup` comment; none in a staff controller
 base/main/default/classes/shared/SystemDML_Test.cls:33 - test_simpleDml_withSharingCaller_cannotUpdateUnsharedRecord
 base/main/default/classes/shared/SystemDML_Test.cls:60 - test_systemDml_withSharingCaller_updatesUnsharedRecord
-DEPENDENCIES.md fork log row for fflib_SObjectUnitOfWork.cls
+This declaration is a deliberate local patch to the vendored FFLib library: upstream declares no sharing keyword on fflib_SObjectUnitOfWork or SimpleDML, and the package declares both `inherited sharing` (reason at :54-61 and :165-190) so a commit runs in its caller's sharing mode. The upstream proposal for the same declarations is fflib-apex-common issue #530 (cited below).
 https://github.com/apex-enterprise-patterns/fflib-apex-common/issues/530 - upstream proposal for the same `inherited sharing` declarations</t>
         </is>
       </c>
@@ -5725,7 +5725,7 @@
         <is>
           <t>base/main/default/classes/donor/service/DonorPortalService.cls:38-47 - header rationale for `without sharing` and the staff-twin exception; :48 declaration
 base/main/default/classes/donor/controller/DonorPortalAdminController.cls:156 / :175 - USER_MODE reads of the Contact / Person Account before the service is called
-docs/security/appexchange-security-review-readiness.md F-10; FP-3 sharing census</t>
+Every top-level class in the package declares a sharing keyword, and each `without sharing` declaration carries its rationale in the class header (this one at :38-47). The staff-facing entry points re-read the donor under the staff user's own sharing before this class acts (DonorPortalAdminController.cls:156 and :175, USER_MODE; hardened 2026-09-25).</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -19849,7 +19849,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>36949d12</t>
+          <t>a4b2d3f1</t>
         </is>
       </c>
     </row>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
